--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -856,6 +856,2521 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>prueba</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>paula.o@gmail.com</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>991016824</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ernesto</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ingrid.maisan.g@gmail.com</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>945031112</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alicia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Seba</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>979545618</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>prueba@prueba.cl</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ji</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Jq</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>953267504</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Josefa</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Alonso</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>928200489</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>9580241536</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Clara</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Anais</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.coom</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>927277950</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ámbar</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>989562453</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Raquel</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>815403536</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lucia</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Marcos</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>976754878</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Magdiel</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>978789067</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Clemente</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Teresa</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>958658554</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Clara</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>976765654</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tania</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dalilara2016@gmail.com</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>941344034</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>carlossanhuuezA@gmail.com</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>93787156</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Polet</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jazmin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Leonor</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Caraleya</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>967849754</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Joshua</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Loiza</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>99886765</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tiare</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Yerson</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Cristal</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>928200489</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Antonella</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>waldohenrriquezssve@gmail.com</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gladys</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Noa</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Silvia</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>bastiquinteros@gmail.com</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>9999999</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bastian</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>98968523</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jaqueline</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Flor</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>934548767</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cristobal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Julieta</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>wilsoncabreramendez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Génesis</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Tiare</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>elisanchez776655@gmail.com</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>zalasarcuevasyorge@gmail.com</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>944589034</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Jovina</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Karla</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>939368209</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ibania</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>954673457</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Exequiel</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>javiercarrilloestopa@gmail.com</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>949741443</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Yesica</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ester</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Silvio</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>967578767</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>980805635</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Cristóbal</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Erick</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>973454876</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ángel</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>9908067515</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Miriam</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Saira</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>995941796</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>953498907</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gladys</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>claudioguitiguti@gmail.com</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Claudio</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>97737356</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Matías</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ignacia</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fabiolavenegas23@gmail.com</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fabiola</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Solange</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>eliasalfnnsocastro@gmail.com</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>975758452</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Rodolfo</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>934567544</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Anita</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ámbar</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>johans.ericson@gmail.com</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>931716589</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Johan</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Silvia</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>997876645</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Paola</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Esteban</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Josue</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>970757425</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Margarira</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ernesto</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>eloizachavezgppl.m@gmail.com</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>993546278</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Eloiza</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Moisés</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>catalinareyersbbass@gmail.com</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ronald</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>996543278</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gorgue</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>998839939</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nadia</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Tamara</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>997546431</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ángel</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Matilda</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>996356236</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Yerson</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pilar</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>998675436</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4234345643</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Tania</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Berzavet</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>99818176</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Mili</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>976454871</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Matías</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Luciana</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>921401715</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Karla</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tatiana</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>940456345</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Danae</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Yeison</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>934545514</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Luciana</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Gregorio</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>9580161782</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Vladimir</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>955645766</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Anais</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>987675557</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>997887675</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>937676808</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Johao</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>997372722</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Enrique</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ingrid</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>951514567</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Alexa</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Erick</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>920672255</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>978934165</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>carolina</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>fernanda</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>mauricio</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:P125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -402,17 +402,37 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>comuna</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>arreglo_flexible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>participacion</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>numero_hijos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>correlativo_empresa</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rut_encuestador</t>
         </is>
       </c>
     </row>
@@ -432,18 +452,36 @@
           <t>ayleen</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J2">
+        <v>7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L2">
-        <v>1</v>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>108566507</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -477,18 +515,36 @@
           <t>Richard</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J3">
+        <v>7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L3">
-        <v>1</v>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -517,18 +573,36 @@
           <t>Isidora</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J4">
+        <v>7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L4">
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N4">
         <v>2</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10659808-8</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -537,18 +611,36 @@
           <t>Freddy</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J5">
+        <v>7</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L5">
-        <v>1</v>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>108566507</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -567,18 +659,36 @@
           <t>Juan</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J6">
+        <v>7</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L6">
-        <v>1</v>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>108566507</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -607,18 +717,36 @@
           <t>Mauricio</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J7">
+        <v>7</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L7">
-        <v>1</v>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10659808-8</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -637,18 +765,36 @@
           <t>Jose Chiuca</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J8">
+        <v>7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L8">
-        <v>1</v>
+          <t>Cerro navia</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>108566507</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -672,18 +818,36 @@
           <t>Norma</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J9">
+        <v>7</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L9">
-        <v>1</v>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10659808-8</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -727,18 +891,36 @@
           <t>Arwen</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J10">
+        <v>7</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L10">
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N10">
         <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10659808-8</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -762,18 +944,36 @@
           <t>Miguel</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J11">
+        <v>7</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L11">
-        <v>1</v>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>108566507</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -802,18 +1002,36 @@
           <t>Francisco</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J12">
+        <v>7</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L12">
-        <v>1</v>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10659808-8</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -842,18 +1060,36 @@
           <t>David</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J13">
+        <v>7</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L13">
-        <v>1</v>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -882,18 +1118,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J14">
+        <v>10</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L14">
-        <v>1</v>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>99999</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -922,18 +1176,36 @@
           <t>Lorena</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J15">
+        <v>6</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L15">
-        <v>1</v>
+          <t>Villa alemana</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Colegio asd</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -957,18 +1229,36 @@
           <t>Seba</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J16">
+        <v>7</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L16">
-        <v>1</v>
+          <t>San miguel</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>12657696k</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -997,18 +1287,36 @@
           <t>Roberto</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J17">
+        <v>10</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L17">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17">
         <v>2</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>174571635</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1032,18 +1340,36 @@
           <t>Jq</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J18">
+        <v>7</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L18">
-        <v>1</v>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>11730633k</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1072,18 +1398,36 @@
           <t>Alonso</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J19">
+        <v>10</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1107,18 +1451,36 @@
           <t>Elizabeth</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J20">
+        <v>10</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L20">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>222191440</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1152,18 +1514,36 @@
           <t>Cristian</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J21">
+        <v>10</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L21">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21">
         <v>2</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1187,18 +1567,36 @@
           <t>Ámbar</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J22">
+        <v>10</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L22">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>222101440</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1227,18 +1625,36 @@
           <t>Gerardo</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J23">
+        <v>10</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L23">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1267,18 +1683,36 @@
           <t>Marcos</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J24">
+        <v>10</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1302,18 +1736,36 @@
           <t>Elena</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J25">
+        <v>10</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L25">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>222191440</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1347,18 +1799,36 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J26">
+        <v>10</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L26">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1382,18 +1852,36 @@
           <t>Clara</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J27">
+        <v>10</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L27">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N27">
         <v>2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>222191440</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1422,18 +1910,36 @@
           <t>Jorge</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J28">
+        <v>10</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>166042149</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1457,18 +1963,36 @@
           <t>Patricia</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J29">
+        <v>10</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L29">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N29">
         <v>2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>222191440</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1507,18 +2031,36 @@
           <t>Ricardo</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J30">
+        <v>10</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30">
         <v>2</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1542,18 +2084,36 @@
           <t>Loiza</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J31">
+        <v>10</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L31">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N31">
         <v>2</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1587,18 +2147,36 @@
           <t>Cristal</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J32">
+        <v>10</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L32">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N32">
         <v>2</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1622,18 +2200,36 @@
           <t>Antonella</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J33">
+        <v>10</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L33">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N33">
         <v>2</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1662,18 +2258,36 @@
           <t>Silvia</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J34">
+        <v>10</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L34">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1697,18 +2311,36 @@
           <t>Michelle</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J35">
+        <v>7</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35">
-        <v>1</v>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>195294283</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1742,18 +2374,36 @@
           <t>Oscar</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J36">
+        <v>10</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L36">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1777,18 +2427,36 @@
           <t>Julieta</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J37">
+        <v>10</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L37">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N37">
         <v>2</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1817,18 +2485,36 @@
           <t>Tiare</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J38">
+        <v>10</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L38">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1852,18 +2538,36 @@
           <t>Martina</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J39">
+        <v>10</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L39">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N39">
         <v>2</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1897,18 +2601,36 @@
           <t>Elias</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J40">
+        <v>10</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L40">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1932,18 +2654,36 @@
           <t>Ibania</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J41">
+        <v>10</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L41">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1967,18 +2707,36 @@
           <t>Isabella</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J42">
+        <v>10</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L42">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2012,18 +2770,36 @@
           <t>Silvio</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J43">
+        <v>10</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L43">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2047,18 +2823,36 @@
           <t>Cecilia</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J44">
+        <v>10</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L44">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N44">
         <v>2</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2087,18 +2881,36 @@
           <t>Erick</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J45">
+        <v>10</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L45">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2122,18 +2934,36 @@
           <t>Angela</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J46">
+        <v>10</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L46">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N46">
         <v>2</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -2167,18 +2997,36 @@
           <t>Tom</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J47">
+        <v>10</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L47">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N47">
         <v>2</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -2207,18 +3055,36 @@
           <t>Sergio</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J48">
+        <v>10</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L48">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -2242,18 +3108,36 @@
           <t>Alexis</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J49">
+        <v>10</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L49">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -2277,18 +3161,36 @@
           <t>Claudio</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J50">
+        <v>10</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L50">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -2312,18 +3214,36 @@
           <t>Ignacia</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J51">
+        <v>10</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L51">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N51">
         <v>2</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -2347,18 +3267,36 @@
           <t>Solange</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J52">
+        <v>10</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L52">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -2382,18 +3320,36 @@
           <t>Patricia</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J53">
+        <v>10</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L53">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N53">
         <v>2</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -2422,18 +3378,36 @@
           <t>Ámbar</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J54">
+        <v>10</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L54">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>222191440</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -2457,18 +3431,36 @@
           <t>Silvia</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J55">
+        <v>10</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L55">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N55">
         <v>2</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -2497,18 +3489,36 @@
           <t>Josue</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J56">
+        <v>10</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L56">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -2532,18 +3542,36 @@
           <t>Ernesto</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J57">
+        <v>10</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L57">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -2567,18 +3595,36 @@
           <t>Moisés</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J58">
+        <v>10</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L58">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N58">
         <v>2</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -2602,18 +3648,36 @@
           <t>Ronald</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J59">
+        <v>10</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L59">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N59">
         <v>4</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -2642,18 +3706,36 @@
           <t>Pamela</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J60">
+        <v>10</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L60">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -2677,18 +3759,36 @@
           <t>Tamara</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J61">
+        <v>10</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L61">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N61">
         <v>2</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -2712,18 +3812,36 @@
           <t>Matilda</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J62">
+        <v>10</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L62">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -2747,18 +3865,36 @@
           <t>Pilar</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J63">
+        <v>10</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L63">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -2782,18 +3918,36 @@
           <t>Pamela</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J64">
+        <v>10</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L64">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -2822,18 +3976,36 @@
           <t>Berzavet</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J65">
+        <v>10</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L65">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -2857,18 +4029,36 @@
           <t>Mili</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J66">
+        <v>10</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L66">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -2892,18 +4082,36 @@
           <t>Luciana</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J67">
+        <v>10</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L67">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N67">
         <v>2</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2927,18 +4135,36 @@
           <t>Tatiana</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J68">
+        <v>10</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L68">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -2962,18 +4188,36 @@
           <t>Yeison</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J69">
+        <v>10</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L69">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -2997,18 +4241,36 @@
           <t>Gregorio</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J70">
+        <v>10</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L70">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N70">
         <v>2</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -3032,18 +4294,36 @@
           <t>Vladimir</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J71">
+        <v>10</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L71">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -3067,18 +4347,36 @@
           <t>Laura</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J72">
+        <v>10</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L72">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N72">
         <v>2</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -3107,18 +4405,36 @@
           <t>Anais</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J73">
+        <v>10</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L73">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -3142,18 +4458,36 @@
           <t>Laura</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J74">
+        <v>10</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L74">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N74">
         <v>2</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -3177,18 +4511,36 @@
           <t>Valentina</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J75">
+        <v>10</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L75">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N75">
         <v>2</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -3212,18 +4564,36 @@
           <t>Johao</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J76">
+        <v>10</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L76">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -3247,18 +4617,36 @@
           <t>Ingrid</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J77">
+        <v>10</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L77">
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N77">
         <v>2</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -3287,18 +4675,36 @@
           <t>Nicolas</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J78">
+        <v>10</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L78">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -3317,18 +4723,36 @@
           <t>Francisca</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="J79">
+        <v>10</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L79">
-        <v>1</v>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N79">
+        <v>1</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -3357,18 +4781,2546 @@
           <t>mauricio</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
+      <c r="J80">
+        <v>10</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L80">
-        <v>1</v>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>abakit@gmail.com</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>977088866</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Maximiliano</t>
+        </is>
+      </c>
+      <c r="J81">
+        <v>7</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>michelmancillas@gmail.com</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>988593923</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Ines</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="J82">
+        <v>7</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>157937626</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>arieldiazfre@gmail.com</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>977018177</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="J83">
+        <v>7</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Conchali</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N83">
+        <v>1</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>994978404</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="J84">
+        <v>10</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>982418462</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>mariana</t>
+        </is>
+      </c>
+      <c r="J85">
+        <v>10</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>chillan viejo</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>m.mullermir@gmail.com</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>971718432</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Constanza</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="J86">
+        <v>7</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>franciscasanchezquiroz@gmail.com</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>951584771</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Eluney</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="J87">
+        <v>7</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N87">
+        <v>2</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>157937626</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>auroorellana68@gmail.com</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>976519997</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Carla</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="J88">
+        <v>7</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N88">
+        <v>1</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>938810230</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Elizsbeth</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="J89">
+        <v>10</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>luis.esteban.s@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>942946271</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Hija 1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Hija 2</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="J90">
+        <v>10</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N90">
+        <v>2</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>984329888</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>paola</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Bastian</t>
+        </is>
+      </c>
+      <c r="J91">
+        <v>10</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>chillan viejo</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>carolapaz.castro@gmail.com</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>20136920</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="J92">
+        <v>7</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>lucnom468@gmail.com</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>928458303</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Luciano</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Joaquin</t>
+        </is>
+      </c>
+      <c r="J93">
+        <v>7</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>157937626</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>tatiana.ramirezcastillo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>944602651</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="J94">
+        <v>7</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nocorreo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>974732653</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Magdiel</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="J95">
+        <v>10</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>982828218</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Damari</t>
+        </is>
+      </c>
+      <c r="J96">
+        <v>10</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N96">
+        <v>1</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>valentinaquiroz023@gmail.com</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>984471136</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Karla</t>
+        </is>
+      </c>
+      <c r="J97">
+        <v>7</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>juanma61@gmail.com</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>962526951</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Juan Manuel</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>daniela</t>
+        </is>
+      </c>
+      <c r="J98">
+        <v>10</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>galvarezvergara@gmail.com</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>966218450</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="J99">
+        <v>7</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Nocorreo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>927612131</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Yesenia</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Genesis</t>
+        </is>
+      </c>
+      <c r="J100">
+        <v>10</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N100">
+        <v>2</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Carlo</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Esposa</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Julieat</t>
+        </is>
+      </c>
+      <c r="J101">
+        <v>9</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N101">
+        <v>1</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>999999999-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Nocorreo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>966758872</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Josefa</t>
+        </is>
+      </c>
+      <c r="J102">
+        <v>10</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>989608350</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>matias</t>
+        </is>
+      </c>
+      <c r="J103">
+        <v>10</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>chiillan</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>930269484</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Polet</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="J104">
+        <v>10</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N104">
+        <v>1</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>fmareporta@gmail.com</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>926041527</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fredy</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="J105">
+        <v>7</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Catalina.rodriguez19ls@gmail.com</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>965943824</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>catalina</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="J106">
+        <v>10</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>chillan viejo</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>964637622</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Dalia</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="J107">
+        <v>10</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>sergiohuentecura@walmart.com</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>998504157</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Vivisns</t>
+        </is>
+      </c>
+      <c r="J108">
+        <v>7</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>muller.miranda.p@gmail.com</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>974655125</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="J109">
+        <v>7</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>joou2099@gmail.com</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>99862967</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>María José</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="J110">
+        <v>7</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>157937626</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>elizabeth59@gmail.com</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>963883202</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="J111">
+        <v>7</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>, puente alto</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>988385483</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ariela</t>
+        </is>
+      </c>
+      <c r="J112">
+        <v>10</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>mirtha.isabel@live.com</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>982606305</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="J113">
+        <v>7</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>954480844</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="J114">
+        <v>10</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>sebastiaan@autlok.cl</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>953623742</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Sebastián</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Alison</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Bruno</t>
+        </is>
+      </c>
+      <c r="J115">
+        <v>7</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>marcelomc@gmail.com</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>987063422</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Marcelo</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="J116">
+        <v>7</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N116">
+        <v>2</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>margaritarodriguezmedrano@gmail.com</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>931920603</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="J117">
+        <v>7</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N117">
+        <v>1</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>931920603</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>carmenvet2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>981420174</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="J118">
+        <v>7</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>geli.villan@gmail.com</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>996094505</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Belen</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="J119">
+        <v>7</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>3558</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>andreacatalan22@gmail.com</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>987806375</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>León</t>
+        </is>
+      </c>
+      <c r="J120">
+        <v>7</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N120">
+        <v>1</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>157937626</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>natalisha_5@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>976219351</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Maria jesus</t>
+        </is>
+      </c>
+      <c r="J121">
+        <v>7</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N121">
+        <v>1</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>mariateresaojeda278@gmail.com</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>929442799</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Augusto</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="J122">
+        <v>7</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Aletorresosorio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>974349092</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Santino</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="J123">
+        <v>7</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>delcastillo4007@gmail.com</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>56988692542</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="J124">
+        <v>7</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>germanrodriguez1978@gmail.com</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>990027704</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="J125">
+        <v>7</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -52,11 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -351,8 +355,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X197"/>
+  <dimension ref="A1:Y285"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
@@ -475,6 +482,11 @@
           <t>rut_encuestador</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_aplicacion</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -530,6 +542,9 @@
           <t>108566507</t>
         </is>
       </c>
+      <c r="Y2" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -615,6 +630,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y3" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,6 +708,9 @@
           <t>10659808-8</t>
         </is>
       </c>
+      <c r="Y4" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -745,6 +766,9 @@
           <t>108566507</t>
         </is>
       </c>
+      <c r="Y5" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -820,6 +844,9 @@
           <t>10659808-8</t>
         </is>
       </c>
+      <c r="Y6" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -875,6 +902,9 @@
           <t>108566507</t>
         </is>
       </c>
+      <c r="Y7" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -940,6 +970,9 @@
           <t>10659808-8</t>
         </is>
       </c>
+      <c r="Y8" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1045,6 +1078,9 @@
           <t>10659808-8</t>
         </is>
       </c>
+      <c r="Y9" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1115,6 +1151,9 @@
           <t>108566507</t>
         </is>
       </c>
+      <c r="Y10" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1190,6 +1229,9 @@
           <t>10659808-8</t>
         </is>
       </c>
+      <c r="Y11" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1265,6 +1307,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y12" s="2">
+        <v>46121</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1345,6 +1390,9 @@
           <t>175682163</t>
         </is>
       </c>
+      <c r="Y13" s="2">
+        <v>46129</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1425,6 +1473,9 @@
           <t>175682163</t>
         </is>
       </c>
+      <c r="Y14" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1495,6 +1546,9 @@
           <t>12657696k</t>
         </is>
       </c>
+      <c r="Y15" s="2">
+        <v>46129</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1575,6 +1629,9 @@
           <t>174571635</t>
         </is>
       </c>
+      <c r="Y16" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1655,6 +1712,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y17" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1725,6 +1785,9 @@
           <t>222191440</t>
         </is>
       </c>
+      <c r="Y18" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1815,6 +1878,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y19" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1885,6 +1951,9 @@
           <t>222101440</t>
         </is>
       </c>
+      <c r="Y20" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1965,6 +2034,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y21" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2045,6 +2117,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y22" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2115,6 +2190,9 @@
           <t>222191440</t>
         </is>
       </c>
+      <c r="Y23" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2205,6 +2283,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y24" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2275,6 +2356,9 @@
           <t>222191440</t>
         </is>
       </c>
+      <c r="Y25" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2355,6 +2439,9 @@
           <t>166042149</t>
         </is>
       </c>
+      <c r="Y26" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2425,6 +2512,9 @@
           <t>222191440</t>
         </is>
       </c>
+      <c r="Y27" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2525,6 +2615,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y28" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2595,6 +2688,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y29" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2685,6 +2781,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y30" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2755,6 +2854,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y31" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2835,6 +2937,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y32" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2905,6 +3010,9 @@
           <t>195294283</t>
         </is>
       </c>
+      <c r="Y33" s="2">
+        <v>46129</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2995,6 +3103,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y34" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3065,6 +3176,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y35" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3145,6 +3259,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y36" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3215,6 +3332,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y37" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3305,6 +3425,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y38" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3375,6 +3498,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y39" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3445,6 +3571,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y40" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3535,6 +3664,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y41" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3605,6 +3737,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y42" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3685,6 +3820,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y43" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3755,6 +3893,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y44" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3845,6 +3986,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y45" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3925,6 +4069,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y46" s="2">
+        <v>46130</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3995,6 +4142,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y47" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4065,6 +4215,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y48" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4135,6 +4288,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y49" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4205,6 +4361,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y50" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4275,6 +4434,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y51" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4355,6 +4517,9 @@
           <t>222191440</t>
         </is>
       </c>
+      <c r="Y52" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4425,6 +4590,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y53" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4505,6 +4673,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y54" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4575,6 +4746,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y55" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4645,6 +4819,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y56" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4715,6 +4892,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y57" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4795,6 +4975,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y58" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4865,6 +5048,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y59" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4935,6 +5121,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y60" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5005,6 +5194,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y61" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5075,6 +5267,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y62" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5155,6 +5350,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y63" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5225,6 +5423,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y64" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5295,6 +5496,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y65" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5365,6 +5569,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y66" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5435,6 +5642,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y67" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5505,6 +5715,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y68" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5575,6 +5788,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y69" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5645,6 +5861,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y70" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5725,6 +5944,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y71" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5795,6 +6017,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y72" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5865,6 +6090,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y73" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5935,6 +6163,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y74" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6005,6 +6236,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y75" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6085,6 +6319,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y76" s="2">
+        <v>46131</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6145,6 +6382,9 @@
           <t>11875563-4</t>
         </is>
       </c>
+      <c r="Y77" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6225,6 +6465,9 @@
           <t>13377893-4</t>
         </is>
       </c>
+      <c r="Y78" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6305,6 +6548,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y79" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6385,6 +6631,9 @@
           <t>157937626</t>
         </is>
       </c>
+      <c r="Y80" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6445,6 +6694,9 @@
           <t>54452705</t>
         </is>
       </c>
+      <c r="Y81" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6515,6 +6767,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y82" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6575,6 +6830,9 @@
           <t>11875563-4</t>
         </is>
       </c>
+      <c r="Y83" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6645,6 +6903,9 @@
           <t>13377893-4</t>
         </is>
       </c>
+      <c r="Y84" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6725,6 +6986,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y85" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6805,6 +7069,9 @@
           <t>157937626</t>
         </is>
       </c>
+      <c r="Y86" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6885,6 +7152,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y87" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6955,6 +7225,9 @@
           <t>11875563-4</t>
         </is>
       </c>
+      <c r="Y88" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7045,6 +7318,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y89" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7125,6 +7401,9 @@
           <t>13377893-4</t>
         </is>
       </c>
+      <c r="Y90" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7195,6 +7474,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y91" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7275,6 +7557,9 @@
           <t>157937626</t>
         </is>
       </c>
+      <c r="Y92" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7345,6 +7630,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y93" s="2">
+        <v>46125</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7425,6 +7713,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y94" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7485,6 +7776,9 @@
           <t>11875563-4</t>
         </is>
       </c>
+      <c r="Y95" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7555,6 +7849,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y96" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7625,6 +7922,9 @@
           <t>13377893-4</t>
         </is>
       </c>
+      <c r="Y97" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7695,6 +7995,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y98" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7775,6 +8078,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y99" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7845,6 +8151,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y100" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7915,6 +8224,9 @@
           <t>13377893-4</t>
         </is>
       </c>
+      <c r="Y101" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7995,6 +8307,9 @@
           <t>11875563-4</t>
         </is>
       </c>
+      <c r="Y102" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8085,6 +8400,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y103" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8155,6 +8473,9 @@
           <t>13377893-4</t>
         </is>
       </c>
+      <c r="Y104" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8225,6 +8546,9 @@
           <t>11875563-4</t>
         </is>
       </c>
+      <c r="Y105" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8295,6 +8619,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y106" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8365,6 +8692,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y107" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8445,6 +8775,9 @@
           <t>157937626</t>
         </is>
       </c>
+      <c r="Y108" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8525,6 +8858,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y109" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8585,6 +8921,9 @@
           <t>11875563-4</t>
         </is>
       </c>
+      <c r="Y110" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8655,6 +8994,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y111" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8725,6 +9067,9 @@
           <t>11875563-4</t>
         </is>
       </c>
+      <c r="Y112" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8805,6 +9150,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y113" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8895,6 +9243,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y114" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8955,6 +9306,9 @@
           <t>931920603</t>
         </is>
       </c>
+      <c r="Y115" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9035,6 +9389,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y116" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9105,6 +9462,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y117" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9185,6 +9545,9 @@
           <t>157937626</t>
         </is>
       </c>
+      <c r="Y118" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9265,6 +9628,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y119" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9345,6 +9711,9 @@
           <t>175458975</t>
         </is>
       </c>
+      <c r="Y120" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9415,6 +9784,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y121" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9505,6 +9877,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y122" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9595,6 +9970,9 @@
           <t>175458975</t>
         </is>
       </c>
+      <c r="Y123" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9675,6 +10053,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y124" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9745,6 +10126,9 @@
           <t>157937626</t>
         </is>
       </c>
+      <c r="Y125" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9835,6 +10219,9 @@
           <t>191656237</t>
         </is>
       </c>
+      <c r="Y126" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9905,6 +10292,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y127" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9975,6 +10365,9 @@
           <t>175458975</t>
         </is>
       </c>
+      <c r="Y128" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10045,6 +10438,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y129" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10125,6 +10521,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y130" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10195,6 +10594,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y131" s="2">
+        <v>46132</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10275,6 +10677,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y132" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10355,6 +10760,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y133" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10445,6 +10853,9 @@
           <t>157937626</t>
         </is>
       </c>
+      <c r="Y134" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10515,6 +10926,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y135" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10595,6 +11009,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y136" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10675,6 +11092,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y137" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10745,6 +11165,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y138" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10815,6 +11238,9 @@
           <t>184676443</t>
         </is>
       </c>
+      <c r="Y139" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10895,6 +11321,9 @@
           <t>191656237</t>
         </is>
       </c>
+      <c r="Y140" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10965,6 +11394,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y141" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11045,6 +11477,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y142" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11115,6 +11550,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y143" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11185,6 +11623,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y144" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11265,6 +11706,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y145" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11355,6 +11799,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y146" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11445,6 +11892,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y147" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11525,6 +11975,9 @@
           <t>175458975</t>
         </is>
       </c>
+      <c r="Y148" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11615,6 +12068,9 @@
           <t>175458975</t>
         </is>
       </c>
+      <c r="Y149" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11705,6 +12161,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y150" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11775,6 +12234,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y151" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11865,6 +12327,9 @@
           <t>18430249-7</t>
         </is>
       </c>
+      <c r="Y152" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11945,6 +12410,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y153" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12025,6 +12493,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y154" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12085,6 +12556,9 @@
           <t>19864455-2</t>
         </is>
       </c>
+      <c r="Y155" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12165,6 +12639,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y156" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12235,6 +12712,9 @@
           <t>9.602.106-2</t>
         </is>
       </c>
+      <c r="Y157" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12325,6 +12805,9 @@
           <t>98784724</t>
         </is>
       </c>
+      <c r="Y158" s="2">
+        <v>46133</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12395,6 +12878,9 @@
           <t>9.602.106-2</t>
         </is>
       </c>
+      <c r="Y159" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12485,6 +12971,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y160" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12565,6 +13054,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y161" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -12645,6 +13137,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y162" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12735,6 +13230,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y163" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12805,6 +13303,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y164" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -12885,6 +13386,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y165" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12955,6 +13459,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y166" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13045,6 +13552,9 @@
           <t>13377893-4</t>
         </is>
       </c>
+      <c r="Y167" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13115,6 +13625,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y168" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13185,6 +13698,9 @@
           <t>13377893-4</t>
         </is>
       </c>
+      <c r="Y169" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13265,6 +13781,9 @@
           <t>175682163</t>
         </is>
       </c>
+      <c r="Y170" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13345,6 +13864,9 @@
           <t>98784624</t>
         </is>
       </c>
+      <c r="Y171" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13435,6 +13957,9 @@
           <t>175682163</t>
         </is>
       </c>
+      <c r="Y172" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13515,6 +14040,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y173" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -13615,6 +14143,9 @@
           <t>175682163</t>
         </is>
       </c>
+      <c r="Y174" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13685,6 +14216,9 @@
           <t>196369937</t>
         </is>
       </c>
+      <c r="Y175" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -13765,6 +14299,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y176" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -13845,6 +14382,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y177" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -13915,6 +14455,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y178" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -13985,6 +14528,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y179" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14065,6 +14611,9 @@
           <t>106598088</t>
         </is>
       </c>
+      <c r="Y180" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14165,6 +14714,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y181" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14245,6 +14797,9 @@
           <t>16933558-3</t>
         </is>
       </c>
+      <c r="Y182" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14325,6 +14880,9 @@
           <t>157937626</t>
         </is>
       </c>
+      <c r="Y183" s="2">
+        <v>46134</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -14405,6 +14963,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y184" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -14495,6 +15056,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y185" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -14565,6 +15129,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y186" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14645,6 +15212,9 @@
           <t>118755634</t>
         </is>
       </c>
+      <c r="Y187" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14715,6 +15285,9 @@
           <t>16602194</t>
         </is>
       </c>
+      <c r="Y188" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -14795,6 +15368,9 @@
           <t>22219144-0</t>
         </is>
       </c>
+      <c r="Y189" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -14875,6 +15451,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y190" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -14945,6 +15524,9 @@
           <t>118755634</t>
         </is>
       </c>
+      <c r="Y191" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15025,6 +15607,9 @@
           <t>184302497</t>
         </is>
       </c>
+      <c r="Y192" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15095,6 +15680,9 @@
           <t>16288310-0</t>
         </is>
       </c>
+      <c r="Y193" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15175,6 +15763,9 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y194" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15255,6 +15846,9 @@
           <t>12680885-2</t>
         </is>
       </c>
+      <c r="Y195" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15335,16 +15929,19 @@
           <t>166042194</t>
         </is>
       </c>
+      <c r="Y196" s="2">
+        <v>46135</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>pcgutierrezc@gmail.com</t>
+          <t>Nani.kary@hotmail.com</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>942904769</t>
+          <t>944433124</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -15354,7 +15951,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -15364,7 +15961,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -15379,7 +15976,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -15389,7 +15986,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V197">
@@ -15397,13 +15994,7290 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+      <c r="Y197" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>dany12308.ds@gmail.com</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>978360818</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Daniela soto</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Andres moris</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Maks  mori</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V198">
+        <v>1</v>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y198" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>pcgutierrezc@gmail.com</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>942904769</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V199">
+        <v>1</v>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
           <t>808</t>
         </is>
       </c>
-      <c r="X197" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>106598088</t>
         </is>
+      </c>
+      <c r="Y199" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>auka.stamp@gmail.com</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>997643495</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Solange araya</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Chillan viejo</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V200">
+        <v>1</v>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Y200" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>fernandopatitas@yahoo.com</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>973660438</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V201">
+        <v>1</v>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+      <c r="Y201" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>claugca1013@gmail.com</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>928589178</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V202">
+        <v>1</v>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="Y202" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>isrratoyv52@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>990845503</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Misael</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Aliro</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Debora</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V203">
+        <v>2</v>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Y203" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>claudiavazquesmerin@gmail.com</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Roxana</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V204">
+        <v>1</v>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y204" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>guillermo.troncoso93@gmail.com</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>973918278</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V205">
+        <v>2</v>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>1843002497</t>
+        </is>
+      </c>
+      <c r="Y205" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>johanvelazxxx@gmail.com</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>949676545</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Yoseling</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V206">
+        <v>1</v>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y206" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>949576457</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Joaquín</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Mía</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V207">
+        <v>1</v>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="Y207" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>miguelampueromii@gmail.com</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Clara</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V208">
+        <v>2</v>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y208" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>lukastudela05@gmail.com</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>910195697</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Lukas</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V209">
+        <v>1</v>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="Y209" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>972573297</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Augusto</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V210">
+        <v>1</v>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="Y210" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>nacha.salas@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>963061077</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Nayar</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Leonel</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V211">
+        <v>1</v>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Y211" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>gracemcadiz@gmail.com</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>988572454</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Grece</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Antonella</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V212">
+        <v>1</v>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y212" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>vriquelmejofre@gmail.com</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>987002907</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>valentina</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>felipe</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>rosa</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>agustin</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>chhillan</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V213">
+        <v>1</v>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="Y213" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Biancabracho18@gmail.com</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>933281201</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Bianca</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Stefy</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V214">
+        <v>2</v>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>196369937</t>
+        </is>
+      </c>
+      <c r="Y214" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>karen.s.riffo.j@gmail.com</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>957125546</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Trinidad</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V215">
+        <v>1</v>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="Y215" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>acartesfica@gmail.com</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>945343457</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Alvaro</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V216">
+        <v>2</v>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y216" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>franciscobucareyallen@gmail.com</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>931741859</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V217">
+        <v>1</v>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="Y217" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>gabriela.gtp624@gmail.com</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>996205432</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Gabriela</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V218">
+        <v>1</v>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y218" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>maryventas2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V219">
+        <v>1</v>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Y219" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>elprincesolukas@gmail.com</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>976221841</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V220">
+        <v>1</v>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="Y220" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>f.gonzareta1@gmail.com</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>979104456</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>andres</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>soledad</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>emilio</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>chhillan</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V221">
+        <v>1</v>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="Y221" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>sergiovenegasanez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>993437459</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V222">
+        <v>1</v>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y222" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>mariase_678@gmail.com</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>921642029</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V223">
+        <v>1</v>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Y223" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>mariajosenavarretes@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>982293205</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Maria jose</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Teodoro</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V224">
+        <v>3</v>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y224" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>a.yparraguirrem@gmail.com</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>932005283</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Albertina</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V225">
+        <v>1</v>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+      <c r="Y225" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>eugeniozuri42@gmail.com</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>+56 9 6814 0489</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Eugenio</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>carmen</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V226">
+        <v>1</v>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="Y226" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>majulio@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>997379563</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Rodolfo</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Yesenia</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V227">
+        <v>1</v>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+      <c r="Y227" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ambarrm96@gmail.com</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>965939613</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Ambar</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Juan pablo</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Julieta</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Casablanca</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V228">
+        <v>1</v>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Y228" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>dfariasrivera@gmail.com</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>982851923</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Padre</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Madre</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Quilpue</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V229">
+        <v>1</v>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Y229" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>araujowilmer04@gmail.com</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>999283136</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Wilmer</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Esposa</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Madre</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V230">
+        <v>1</v>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y230" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>tatanperezperse@gmail.com</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>9590890789</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Gerson</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Flor</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Erna</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V231">
+        <v>2</v>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y231" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>genesiszepeda12@gmail.com</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>950361715</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>génesis</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>luciano</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>santiago</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V232">
+        <v>1</v>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>154374043</t>
+        </is>
+      </c>
+      <c r="Y232" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>eladiohuen@gmail.com</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>978826209</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Eladio</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Paz</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V233">
+        <v>1</v>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+      <c r="Y233" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Posooriovidea@gmail.com</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>949446992</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V234">
+        <v>1</v>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+      <c r="Y234" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>mcamilaurriaga@gmail.com</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>989083830</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V235">
+        <v>1</v>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y235" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>967890567</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V236">
+        <v>1</v>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y236" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>santambrogio.fiorella@gmail.com</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>941402437</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Fiorella</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Mariano</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>Villa alemana</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V237">
+        <v>1</v>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Y237" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>fernanda.as@outlook.cl</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>945517953</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Antonela</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V238">
+        <v>2</v>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+      <c r="Y238" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>jarariquelme62@gmail.com</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>876784337</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V239">
+        <v>1</v>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y239" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>verajerez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>767728480</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Ingrid</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Hernan</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V240">
+        <v>1</v>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y240" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>manuelillo670@yahoo.com</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>984082972</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Karla</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Macarena</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V241">
+        <v>1</v>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+      <c r="Y241" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>fabiola.bialobrozky.g@gmail.con</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Fabiola</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Amador</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Lidia</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Camilo</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V242">
+        <v>1</v>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Y242" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>javiercorretzer@gmail.com</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>9876765437</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V243">
+        <v>1</v>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y243" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>cejarjavezraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>9676783245</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Yoseling</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Anita</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V244">
+        <v>1</v>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y244" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>magditasandoval7@gmail.com</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>927610387</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Trinidad</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V245">
+        <v>1</v>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y245" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>997826645</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Ámbar</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Josefa</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V246">
+        <v>1</v>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="Y246" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>vturchan@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>953247225</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V247">
+        <v>1</v>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>97447632</t>
+        </is>
+      </c>
+      <c r="Y247" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>mt.guajardo@mgscampo.com</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>949252499</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>sandra</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>juan</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>claudia</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V248">
+        <v>1</v>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>108566507</t>
+        </is>
+      </c>
+      <c r="Y248" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>jaramillo.patricia@gmail.com</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>56995392540</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>LaFlorida</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V249">
+        <v>1</v>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>102693531</t>
+        </is>
+      </c>
+      <c r="Y249" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>erika.isab@gmail.com</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>985540525</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Erika</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Emanuel</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Camilo</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V250">
+        <v>1</v>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>157937626</t>
+        </is>
+      </c>
+      <c r="Y250" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>kscm.95.25@gmail.com</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>978674531</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Karla</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Amaro</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V251">
+        <v>1</v>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y251" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>edgo.lagosjara@gmsil.com</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>978409053</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Edgo</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Stefi</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Matilde</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>Chillan viejo</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V252">
+        <v>2</v>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Y252" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>antoniacruz500@yahoo.com</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>988936635</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Fernnado</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Helena</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V253">
+        <v>1</v>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+      <c r="Y253" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>hmejiasm3@gmail.com</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>964743228</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Hellen</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Gael</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V254">
+        <v>2</v>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y254" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>997350546</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Erika</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V255">
+        <v>1</v>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="Y255" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>fdarodriguez.a@gmail.com</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>958644455</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Julieta</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Manu</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V256">
+        <v>1</v>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>19636993-7</t>
+        </is>
+      </c>
+      <c r="Y256" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>carmen.royer@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>938811955</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Josefa</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V257">
+        <v>1</v>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Y257" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>castromunozeliascm@gmail.com</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>9765257995</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Carilina</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Armin</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V258">
+        <v>2</v>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y258" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>tibertomirandamb@gmail.com</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>9852862581</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Jovina</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Yesica</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Johna</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V259">
+        <v>1</v>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y259" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>leonardo2028@gmail.com</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>984652910</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Leonardo</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Liseth</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Liseeth</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V260">
+        <v>8</v>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Y260" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>valentinabeatrizsc99@gmail.com</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>+56 9 9891 7524</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>beatriz</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V261">
+        <v>1</v>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="Y261" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>marcela_poblete_rubio@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>971373365</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V262">
+        <v>2</v>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>19636993-7</t>
+        </is>
+      </c>
+      <c r="Y262" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>marysepulveda412@gmail.com</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>981460272</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Maricel</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Renato</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V263">
+        <v>1</v>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y263" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>danielagutizerr@gmail.com</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>8671765578</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V264">
+        <v>1</v>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y264" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>maribelnegron@gmail.com</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>986533690</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Maribel</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Baro</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Belen</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V265">
+        <v>1</v>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="Y265" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>tatiana308@yahoo.com</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>973660438</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Tatiana</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V266">
+        <v>2</v>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>157937626</t>
+        </is>
+      </c>
+      <c r="Y266" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>carlos_valdes_mu@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>991959534</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Esposa</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Augus</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V267">
+        <v>2</v>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y267" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>teresa.yev3nes20@gmail.com</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>977577642</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Teresa</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V268">
+        <v>1</v>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Y268" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>sugerdes@gmail.com</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>+569 86485061</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Carlos Martin</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Leonor Martin</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Bastian Martin</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Amparo Martin</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V269">
+        <v>1</v>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>203982356</t>
+        </is>
+      </c>
+      <c r="Y269" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>paolarias2026@gmsil.com</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>978578934</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Paola</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V270">
+        <v>1</v>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Y270" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ivette.gonzalez5@gmail.com</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>929382154</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Ivette</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Jacinta</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V271">
+        <v>1</v>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Y271" s="2">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Maca.arevalo.neculhueque@gmail.com</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>953333723</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Macarena</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V272">
+        <v>1</v>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>19636993-7</t>
+        </is>
+      </c>
+      <c r="Y272" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>slagos@gmail.com</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>937613580</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>sergio</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>tomás</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V273">
+        <v>1</v>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>7893</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="Y273" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>mariaesparza@liceomartabrunet.cl</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>954172922</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Maria jose esparza</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Antonella</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V274">
+        <v>1</v>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y274" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>kamifelice.2@gmsil.com</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>948632874</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>camila</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>nicola</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V275">
+        <v>1</v>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>7893</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="Y275" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>anam@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>987944995</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>María jose</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Belén</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V276">
+        <v>1</v>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Y276" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>angelinavilla_@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>962746104</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>angelina</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>roberto</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V277">
+        <v>1</v>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="Y277" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>marangel1973@gmail.com</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>964071656</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Luciano</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V278">
+        <v>1</v>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>7893</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="Y278" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Johanaravanal.etc@gmail.com</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>979469759</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Johana ravanal</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Juan pablo</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V279">
+        <v>1</v>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Y279" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>alejandromonardez12@gmail.com</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>945620506</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>María José</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>María José</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V280">
+        <v>1</v>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="Y280" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>995255569</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V281">
+        <v>1</v>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Y281" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>daniejara1309@gmail.com</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>951968972</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>daniela</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V282">
+        <v>1</v>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>7893</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="Y282" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>gerardogutierrezcarrasco89@gmail.com</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>947329839</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V283">
+        <v>1</v>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Y283" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>carloscastillo1@gmail.com</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>966528490</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>erna</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>julieta</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V284">
+        <v>1</v>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="Y284" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>988681015</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Angelica</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V285">
+        <v>1</v>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Y285" s="2">
+        <v>46136</v>
       </c>
     </row>
   </sheetData>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC514"/>
+  <dimension ref="A1:AC553"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -51343,12 +51343,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>ignaciotorrestt@gmail.com</t>
+          <t>dc_pozas@hotmail.com</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>56966543446</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -51358,7 +51358,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Ignacio</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -51368,7 +51368,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Leslie</t>
+          <t>Daniela</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -51378,12 +51378,12 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="R501" t="inlineStr">
@@ -51393,17 +51393,17 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="T501" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U501" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V501">
@@ -51411,47 +51411,47 @@
       </c>
       <c r="W501" t="inlineStr">
         <is>
-          <t>0376-4</t>
+          <t>encuestador datodinamico</t>
         </is>
       </c>
       <c r="X501" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y501" t="inlineStr">
         <is>
-          <t>17250376-4</t>
+          <t>21668032-4</t>
         </is>
       </c>
       <c r="Z501" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AA501" t="inlineStr">
         <is>
-          <t>2026-04-28 18:19:54</t>
+          <t>2026-04-28 17:27:30</t>
         </is>
       </c>
       <c r="AB501" t="inlineStr">
         <is>
-          <t>2026-04-28 18:47:14</t>
+          <t>2026-04-29 17:12:01</t>
         </is>
       </c>
       <c r="AC501" t="inlineStr">
         <is>
-          <t>2026-04-28 18:47:12</t>
+          <t>2026-04-29 17:12:01</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>osoriomardonescd@gmail.com</t>
+          <t>ignaciotorrestt@gmail.com</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>949486563</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -51461,7 +51461,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Ignacio</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -51471,7 +51471,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Pareja</t>
+          <t>Leslie</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -51481,7 +51481,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Hija de mi pareja</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -51489,24 +51489,14 @@
           <t>Mujer</t>
         </is>
       </c>
-      <c r="J502" t="inlineStr">
-        <is>
-          <t>Hijo</t>
-        </is>
-      </c>
-      <c r="K502" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
       <c r="R502" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="T502" t="inlineStr">
@@ -51524,7 +51514,7 @@
       </c>
       <c r="W502" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0376-4</t>
         </is>
       </c>
       <c r="X502" t="inlineStr">
@@ -51534,7 +51524,7 @@
       </c>
       <c r="Y502" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>17250376-4</t>
         </is>
       </c>
       <c r="Z502" s="2">
@@ -51542,29 +51532,29 @@
       </c>
       <c r="AA502" t="inlineStr">
         <is>
-          <t>2026-04-28 18:23:50</t>
+          <t>2026-04-28 18:19:54</t>
         </is>
       </c>
       <c r="AB502" t="inlineStr">
         <is>
-          <t>2026-04-28 19:02:45</t>
+          <t>2026-04-28 18:47:14</t>
         </is>
       </c>
       <c r="AC502" t="inlineStr">
         <is>
-          <t>2026-04-28 19:02:42</t>
+          <t>2026-04-28 18:47:12</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>leticiasotomora88@gmail.com</t>
+          <t>osoriomardonescd@gmail.com</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>965426023</t>
+          <t>949486563</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -51574,31 +51564,41 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Leticia</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Esposo</t>
+          <t>Pareja</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Hija de mi pareja</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
           <t>Hombre</t>
         </is>
       </c>
@@ -51619,7 +51619,7 @@
       </c>
       <c r="U503" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V503">
@@ -51645,29 +51645,29 @@
       </c>
       <c r="AA503" t="inlineStr">
         <is>
-          <t>2026-04-28 19:18:57</t>
+          <t>2026-04-28 18:23:50</t>
         </is>
       </c>
       <c r="AB503" t="inlineStr">
         <is>
-          <t>2026-04-28 20:06:29</t>
+          <t>2026-04-28 19:02:45</t>
         </is>
       </c>
       <c r="AC503" t="inlineStr">
         <is>
-          <t>2026-04-28 20:06:27</t>
+          <t>2026-04-28 19:02:42</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>alejandra.n24@gmail.com</t>
+          <t>leticiasotomora88@gmail.com</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>976648332</t>
+          <t>965426023</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -51677,7 +51677,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Leticia</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -51687,7 +51687,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Esposo</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -51697,7 +51697,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -51705,16 +51705,6 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="J504" t="inlineStr">
-        <is>
-          <t>Mateo</t>
-        </is>
-      </c>
-      <c r="K504" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
       <c r="R504" t="inlineStr">
         <is>
           <t>Ñuble</t>
@@ -51732,7 +51722,7 @@
       </c>
       <c r="U504" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V504">
@@ -51758,74 +51748,94 @@
       </c>
       <c r="AA504" t="inlineStr">
         <is>
-          <t>2026-04-28 20:30:15</t>
+          <t>2026-04-28 19:18:57</t>
         </is>
       </c>
       <c r="AB504" t="inlineStr">
         <is>
-          <t>2026-04-28 20:56:13</t>
+          <t>2026-04-28 20:06:29</t>
         </is>
       </c>
       <c r="AC504" t="inlineStr">
         <is>
-          <t>2026-04-28 20:56:12</t>
+          <t>2026-04-28 20:06:27</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>c.urreatorres@gmail.com</t>
+          <t>alejandra.n24@gmail.com</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>944476648</t>
+          <t>976648332</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Carlos urrea</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Patricia soto</t>
+          <t>Sergio</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="R505" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>San miguel</t>
+          <t>Chillan</t>
         </is>
       </c>
       <c r="T505" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U505" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V505">
@@ -51833,7 +51843,7 @@
       </c>
       <c r="W505" t="inlineStr">
         <is>
-          <t>Camila Urrea</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="X505" t="inlineStr">
@@ -51843,7 +51853,7 @@
       </c>
       <c r="Y505" t="inlineStr">
         <is>
-          <t>194219067</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="Z505" s="2">
@@ -51851,29 +51861,29 @@
       </c>
       <c r="AA505" t="inlineStr">
         <is>
-          <t>2026-04-28 21:18:33</t>
+          <t>2026-04-28 20:30:15</t>
         </is>
       </c>
       <c r="AB505" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:36</t>
+          <t>2026-04-28 20:56:13</t>
         </is>
       </c>
       <c r="AC505" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:35</t>
+          <t>2026-04-28 20:56:12</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>brenda.cast88@gmail.com</t>
+          <t>c.urreatorres@gmail.com</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>948544198</t>
+          <t>944476648</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -51883,11 +51893,21 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Carlos urrea</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Patricia soto</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
           <t>Mujer</t>
         </is>
       </c>
@@ -51898,7 +51918,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>San miguel</t>
         </is>
       </c>
       <c r="T506" t="inlineStr">
@@ -51916,7 +51936,7 @@
       </c>
       <c r="W506" t="inlineStr">
         <is>
-          <t>0376-5</t>
+          <t>Camila Urrea</t>
         </is>
       </c>
       <c r="X506" t="inlineStr">
@@ -51926,47 +51946,47 @@
       </c>
       <c r="Y506" t="inlineStr">
         <is>
-          <t>17250376-4</t>
+          <t>194219067</t>
         </is>
       </c>
       <c r="Z506" s="2">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="AA506" t="inlineStr">
         <is>
-          <t>2026-04-29 10:07:17</t>
+          <t>2026-04-28 21:18:33</t>
         </is>
       </c>
       <c r="AB506" t="inlineStr">
         <is>
-          <t>2026-04-29 10:55:09</t>
+          <t>2026-04-28 22:29:36</t>
         </is>
       </c>
       <c r="AC506" t="inlineStr">
         <is>
-          <t>2026-04-29 10:55:09</t>
+          <t>2026-04-28 22:29:35</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>carla.segura.osses@gmail.com</t>
+          <t>brenda.cast88@gmail.com</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>965349941</t>
+          <t>948544198</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -51974,26 +51994,6 @@
           <t>Mujer</t>
         </is>
       </c>
-      <c r="F507" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="G507" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="H507" t="inlineStr">
-        <is>
-          <t>Diana</t>
-        </is>
-      </c>
-      <c r="I507" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
       <c r="R507" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -52001,12 +52001,12 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="T507" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U507" t="inlineStr">
@@ -52019,7 +52019,7 @@
       </c>
       <c r="W507" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0376-5</t>
         </is>
       </c>
       <c r="X507" t="inlineStr">
@@ -52029,7 +52029,7 @@
       </c>
       <c r="Y507" t="inlineStr">
         <is>
-          <t>19313240-5</t>
+          <t>17250376-4</t>
         </is>
       </c>
       <c r="Z507" s="2">
@@ -52037,29 +52037,29 @@
       </c>
       <c r="AA507" t="inlineStr">
         <is>
-          <t>2026-04-29 10:30:54</t>
+          <t>2026-04-29 10:07:17</t>
         </is>
       </c>
       <c r="AB507" t="inlineStr">
         <is>
-          <t>2026-04-29 11:06:08</t>
+          <t>2026-04-29 10:55:09</t>
         </is>
       </c>
       <c r="AC507" t="inlineStr">
         <is>
-          <t>2026-04-29 11:06:08</t>
+          <t>2026-04-29 10:55:09</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>elianamunozcelis@gmail.com</t>
+          <t>carla.segura.osses@gmail.com</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>965349941</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -52069,7 +52069,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Eliana</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -52079,7 +52079,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -52089,7 +52089,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Diana</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -52104,17 +52104,17 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="T508" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U508" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V508">
@@ -52132,7 +52132,7 @@
       </c>
       <c r="Y508" t="inlineStr">
         <is>
-          <t>19313205</t>
+          <t>19313240-5</t>
         </is>
       </c>
       <c r="Z508" s="2">
@@ -52140,29 +52140,29 @@
       </c>
       <c r="AA508" t="inlineStr">
         <is>
-          <t>2026-04-29 10:35:09</t>
+          <t>2026-04-29 10:30:54</t>
         </is>
       </c>
       <c r="AB508" t="inlineStr">
         <is>
-          <t>2026-04-29 11:16:39</t>
+          <t>2026-04-29 11:06:08</t>
         </is>
       </c>
       <c r="AC508" t="inlineStr">
         <is>
-          <t>2026-04-29 11:16:39</t>
+          <t>2026-04-29 11:06:08</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>andreaferretticory@gmail.com</t>
+          <t>elianamunozcelis@gmail.com</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>998431958</t>
+          <t>999999</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -52172,7 +52172,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Andrea Ferretti Abarca</t>
+          <t>Eliana</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -52182,42 +52182,42 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Gabriela Jara Ferretti</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Esteban Jara Ferretti</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="R509" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="T509" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="U509" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="V509">
@@ -52225,7 +52225,7 @@
       </c>
       <c r="W509" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X509" t="inlineStr">
@@ -52235,7 +52235,7 @@
       </c>
       <c r="Y509" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>19313205</t>
         </is>
       </c>
       <c r="Z509" s="2">
@@ -52243,29 +52243,29 @@
       </c>
       <c r="AA509" t="inlineStr">
         <is>
-          <t>2026-04-29 10:59:12</t>
+          <t>2026-04-29 10:35:09</t>
         </is>
       </c>
       <c r="AB509" t="inlineStr">
         <is>
-          <t>2026-04-29 11:32:24</t>
+          <t>2026-04-29 11:16:39</t>
         </is>
       </c>
       <c r="AC509" t="inlineStr">
         <is>
-          <t>2026-04-29 11:32:24</t>
+          <t>2026-04-29 11:16:39</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>luisgonzalezcaro@gmail.com</t>
+          <t>andreaferretticory@gmail.com</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>958898163</t>
+          <t>998431958</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -52275,22 +52275,42 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Andrea Ferretti Abarca</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Gabriela Jara Ferretti</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Esteban Jara Ferretti</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
           <t>Hombre</t>
         </is>
       </c>
       <c r="R510" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="T510" t="inlineStr">
@@ -52300,7 +52320,7 @@
       </c>
       <c r="U510" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V510">
@@ -52308,7 +52328,7 @@
       </c>
       <c r="W510" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>11</t>
         </is>
       </c>
       <c r="X510" t="inlineStr">
@@ -52318,7 +52338,7 @@
       </c>
       <c r="Y510" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="Z510" s="2">
@@ -52326,29 +52346,29 @@
       </c>
       <c r="AA510" t="inlineStr">
         <is>
-          <t>2026-04-29 10:59:49</t>
+          <t>2026-04-29 10:59:12</t>
         </is>
       </c>
       <c r="AB510" t="inlineStr">
         <is>
-          <t>2026-04-29 11:49:32</t>
+          <t>2026-04-29 11:32:24</t>
         </is>
       </c>
       <c r="AC510" t="inlineStr">
         <is>
-          <t>2026-04-29 11:49:32</t>
+          <t>2026-04-29 11:32:24</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>jesa.antonia@gmail.com</t>
+          <t>luisgonzalezcaro@gmail.com</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>939460277</t>
+          <t>958898163</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -52358,7 +52378,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -52366,24 +52386,14 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>Jesa</t>
-        </is>
-      </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
       <c r="R511" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>Estacion central</t>
+          <t>Chillan</t>
         </is>
       </c>
       <c r="T511" t="inlineStr">
@@ -52401,7 +52411,7 @@
       </c>
       <c r="W511" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="X511" t="inlineStr">
@@ -52411,7 +52421,7 @@
       </c>
       <c r="Y511" t="inlineStr">
         <is>
-          <t>19313240-5</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="Z511" s="2">
@@ -52419,29 +52429,29 @@
       </c>
       <c r="AA511" t="inlineStr">
         <is>
-          <t>2026-04-29 11:09:33</t>
+          <t>2026-04-29 10:59:49</t>
         </is>
       </c>
       <c r="AB511" t="inlineStr">
         <is>
-          <t>2026-04-29 11:34:48</t>
+          <t>2026-04-29 11:49:32</t>
         </is>
       </c>
       <c r="AC511" t="inlineStr">
         <is>
-          <t>2026-04-29 11:34:48</t>
+          <t>2026-04-29 11:49:32</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>nane.guaiquil@gmail.com</t>
+          <t>jesa.antonia@gmail.com</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>939460277</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -52451,17 +52461,17 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Valeria</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Antonia</t>
+          <t>Jesa</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -52476,17 +52486,17 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>San miguel</t>
+          <t>Estacion central</t>
         </is>
       </c>
       <c r="T512" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U512" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V512">
@@ -52494,17 +52504,17 @@
       </c>
       <c r="W512" t="inlineStr">
         <is>
-          <t>0376-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X512" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y512" t="inlineStr">
         <is>
-          <t>17250376-4</t>
+          <t>19313240-5</t>
         </is>
       </c>
       <c r="Z512" s="2">
@@ -52512,29 +52522,29 @@
       </c>
       <c r="AA512" t="inlineStr">
         <is>
-          <t>2026-04-29 11:34:46</t>
+          <t>2026-04-29 11:09:33</t>
         </is>
       </c>
       <c r="AB512" t="inlineStr">
         <is>
-          <t>2026-04-29 12:21:08</t>
+          <t>2026-04-29 11:34:48</t>
         </is>
       </c>
       <c r="AC512" t="inlineStr">
         <is>
-          <t>2026-04-29 12:21:08</t>
+          <t>2026-04-29 11:34:48</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>rechaza@gmail.com</t>
+          <t>nane.guaiquil@gmail.com</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>990186049</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -52544,7 +52554,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>leonor</t>
+          <t>Valeria</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -52554,22 +52564,22 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Antonia</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="R513" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>CHILLAN</t>
+          <t>San miguel</t>
         </is>
       </c>
       <c r="T513" t="inlineStr">
@@ -52587,17 +52597,17 @@
       </c>
       <c r="W513" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>0376-6</t>
         </is>
       </c>
       <c r="X513" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y513" t="inlineStr">
         <is>
-          <t>8.464.650-4</t>
+          <t>17250376-4</t>
         </is>
       </c>
       <c r="Z513" s="2">
@@ -52605,29 +52615,29 @@
       </c>
       <c r="AA513" t="inlineStr">
         <is>
-          <t>2026-04-29 11:51:58</t>
+          <t>2026-04-29 11:34:46</t>
         </is>
       </c>
       <c r="AB513" t="inlineStr">
         <is>
-          <t>2026-04-29 12:18:52</t>
+          <t>2026-04-29 12:21:08</t>
         </is>
       </c>
       <c r="AC513" t="inlineStr">
         <is>
-          <t>2026-04-29 12:18:52</t>
+          <t>2026-04-29 12:21:08</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>anasepulveda6@gmail.com</t>
+          <t>rechaza@gmail.com</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>952370460</t>
+          <t>990186049</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -52637,7 +52647,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>leonor</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -52647,32 +52657,22 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Maitr</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="H514" t="inlineStr">
-        <is>
-          <t>Coni</t>
-        </is>
-      </c>
-      <c r="I514" t="inlineStr">
-        <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="R514" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>Lo prado</t>
+          <t>CHILLAN</t>
         </is>
       </c>
       <c r="T514" t="inlineStr">
@@ -52690,7 +52690,7 @@
       </c>
       <c r="W514" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="X514" t="inlineStr">
@@ -52700,7 +52700,7 @@
       </c>
       <c r="Y514" t="inlineStr">
         <is>
-          <t>19313240-5</t>
+          <t>8.464.650-4</t>
         </is>
       </c>
       <c r="Z514" s="2">
@@ -52708,17 +52708,4134 @@
       </c>
       <c r="AA514" t="inlineStr">
         <is>
+          <t>2026-04-29 11:51:58</t>
+        </is>
+      </c>
+      <c r="AB514" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:18:52</t>
+        </is>
+      </c>
+      <c r="AC514" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>anasepulveda6@gmail.com</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>952370460</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Maitr</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Coni</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>Lo prado</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V515">
+        <v>1</v>
+      </c>
+      <c r="W515" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y515" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z515" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA515" t="inlineStr">
+        <is>
           <t>2026-04-29 11:55:22</t>
         </is>
       </c>
-      <c r="AB514" t="inlineStr">
+      <c r="AB515" t="inlineStr">
         <is>
           <t>2026-04-29 12:15:23</t>
         </is>
       </c>
-      <c r="AC514" t="inlineStr">
+      <c r="AC515" t="inlineStr">
         <is>
           <t>2026-04-29 12:15:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>bernaalehandravargas@ggmail.com</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>989197601</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Alejanda</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>Cerro navia</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V516">
+        <v>1</v>
+      </c>
+      <c r="W516" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y516" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z516" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA516" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:29:37</t>
+        </is>
+      </c>
+      <c r="AB516" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:52:55</t>
+        </is>
+      </c>
+      <c r="AC516" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>962351653</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Mirta</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V517">
+        <v>1</v>
+      </c>
+      <c r="W517" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Z517" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA517" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:35:38</t>
+        </is>
+      </c>
+      <c r="AB517" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:13:59</t>
+        </is>
+      </c>
+      <c r="AC517" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:13:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>yasna.pinela@gmail.com</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>941386941</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Yasna</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Alen</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V518">
+        <v>1</v>
+      </c>
+      <c r="W518" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z518" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA518" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:04:18</t>
+        </is>
+      </c>
+      <c r="AB518" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:28:52</t>
+        </is>
+      </c>
+      <c r="AC518" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:28:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>patriciocayun1960@gmail.com</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>981243211</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Marcelo</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Tania</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>Patricio antonio</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V519">
+        <v>1</v>
+      </c>
+      <c r="W519" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z519" s="2">
+        <v>45382</v>
+      </c>
+      <c r="AA519" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:09:58</t>
+        </is>
+      </c>
+      <c r="AB519" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:09:02</t>
+        </is>
+      </c>
+      <c r="AC519" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:09:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>camilawork41@gmail.con</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>937628622</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Maximiliano</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V520">
+        <v>1</v>
+      </c>
+      <c r="W520" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y520" t="inlineStr">
+        <is>
+          <t>19313205</t>
+        </is>
+      </c>
+      <c r="Z520" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA520" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:17:06</t>
+        </is>
+      </c>
+      <c r="AB520" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:50:39</t>
+        </is>
+      </c>
+      <c r="AC520" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:50:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>quintana.carcamo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>942703307</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Valeska</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Antonia</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>San joaquin</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V521">
+        <v>1</v>
+      </c>
+      <c r="W521" t="inlineStr">
+        <is>
+          <t>0376-7</t>
+        </is>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y521" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z521" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA521" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:39:56</t>
+        </is>
+      </c>
+      <c r="AB521" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:25:40</t>
+        </is>
+      </c>
+      <c r="AC521" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:25:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>nancyinfanteh@gmail.com</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>940951842</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Adrián Luengo González</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Adrián Luengo Infantes</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>Nicolás Luengo Infantes</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V522">
+        <v>1</v>
+      </c>
+      <c r="W522" t="inlineStr">
+        <is>
+          <t>76016305-8</t>
+        </is>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y522" t="inlineStr">
+        <is>
+          <t>16250303-0</t>
+        </is>
+      </c>
+      <c r="Z522" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA522" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:00:21</t>
+        </is>
+      </c>
+      <c r="AB522" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:43:33</t>
+        </is>
+      </c>
+      <c r="AC522" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>942130983</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Isaías</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T523" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V523">
+        <v>2</v>
+      </c>
+      <c r="W523" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y523" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Z523" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA523" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:38:36</t>
+        </is>
+      </c>
+      <c r="AB523" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:15:24</t>
+        </is>
+      </c>
+      <c r="AC523" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:15:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>974449247</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Nicolle</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V524">
+        <v>1</v>
+      </c>
+      <c r="W524" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y524" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Z524" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA524" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:31:39</t>
+        </is>
+      </c>
+      <c r="AB524" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:04:03</t>
+        </is>
+      </c>
+      <c r="AC524" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:04:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>claudiogonzalezalarcon@gmail.com</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>944343105</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Claudio</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>Alondra</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="T525" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V525">
+        <v>1</v>
+      </c>
+      <c r="W525" t="inlineStr">
+        <is>
+          <t>0376-8</t>
+        </is>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y525" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z525" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA525" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:01:31</t>
+        </is>
+      </c>
+      <c r="AB525" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:36:41</t>
+        </is>
+      </c>
+      <c r="AC525" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:36:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>carlasolisvaldes@gmail.com</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>942846179</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Carla</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>Alondra</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V526">
+        <v>2</v>
+      </c>
+      <c r="W526" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y526" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z526" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA526" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:06:38</t>
+        </is>
+      </c>
+      <c r="AB526" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:30:48</t>
+        </is>
+      </c>
+      <c r="AC526" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:30:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>981498294</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Josefa</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>Dominique</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V527">
+        <v>2</v>
+      </c>
+      <c r="W527" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y527" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Z527" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA527" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:18:08</t>
+        </is>
+      </c>
+      <c r="AB527" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:50:35</t>
+        </is>
+      </c>
+      <c r="AC527" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:50:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>javierapdt@gmail.com</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>9999999</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Nahuel</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V528">
+        <v>2</v>
+      </c>
+      <c r="W528" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y528" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z528" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA528" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:36:00</t>
+        </is>
+      </c>
+      <c r="AB528" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:59:47</t>
+        </is>
+      </c>
+      <c r="AC528" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:59:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>964801415</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Sandea</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T529" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V529">
+        <v>1</v>
+      </c>
+      <c r="W529" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y529" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Z529" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA529" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:01:10</t>
+        </is>
+      </c>
+      <c r="AB529" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:40:01</t>
+        </is>
+      </c>
+      <c r="AC529" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:40:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>cristobalblu@gmail.com</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>954674516</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Cristobal</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V530">
+        <v>1</v>
+      </c>
+      <c r="W530" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y530" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z530" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA530" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:05:05</t>
+        </is>
+      </c>
+      <c r="AB530" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:22:56</t>
+        </is>
+      </c>
+      <c r="AC530" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:22:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>estelaromero.ak@gmail.com</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>967971809</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Estela</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Rosemary</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V531">
+        <v>2</v>
+      </c>
+      <c r="W531" t="inlineStr">
+        <is>
+          <t>9270-2</t>
+        </is>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y531" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z531" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA531" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:15:13</t>
+        </is>
+      </c>
+      <c r="AB531" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:49:19</t>
+        </is>
+      </c>
+      <c r="AC531" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:49:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>eliza.vidal.infante@live.cl</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>56942663568</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>luis</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Eliza</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V532">
+        <v>1</v>
+      </c>
+      <c r="W532" t="inlineStr">
+        <is>
+          <t>encuestador datodinamico</t>
+        </is>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y532" t="inlineStr">
+        <is>
+          <t>216680324</t>
+        </is>
+      </c>
+      <c r="Z532" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA532" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:17:09</t>
+        </is>
+      </c>
+      <c r="AB532" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:05:48</t>
+        </is>
+      </c>
+      <c r="AC532" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>nelsoncordero482@gmail.com</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>942842865</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Nelson</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Miriam</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Liss</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V533">
+        <v>2</v>
+      </c>
+      <c r="W533" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y533" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="Z533" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA533" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:38:43</t>
+        </is>
+      </c>
+      <c r="AB533" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:36:05</t>
+        </is>
+      </c>
+      <c r="AC533" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>hernestoalnado@gmail.com</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>940776832</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Ernesto</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>Cerillos</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V534">
+        <v>1</v>
+      </c>
+      <c r="W534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y534" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="Z534" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA534" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:58</t>
+        </is>
+      </c>
+      <c r="AB534" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:23:40</t>
+        </is>
+      </c>
+      <c r="AC534" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:23:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>praticiamoraless67@gmail.com</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>95727627</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V535">
+        <v>1</v>
+      </c>
+      <c r="W535" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y535" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z535" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:47:31</t>
+        </is>
+      </c>
+      <c r="AB535" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:12:20</t>
+        </is>
+      </c>
+      <c r="AC535" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>931931415</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Ximena</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Belén</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V536">
+        <v>1</v>
+      </c>
+      <c r="W536" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y536" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Z536" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA536" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:53:29</t>
+        </is>
+      </c>
+      <c r="AB536" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:27:46</t>
+        </is>
+      </c>
+      <c r="AC536" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:27:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>moisessmith31@gmail.com</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>972778435</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Moises</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V537">
+        <v>1</v>
+      </c>
+      <c r="W537" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y537" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Z537" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA537" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:42:08</t>
+        </is>
+      </c>
+      <c r="AB537" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:08:40</t>
+        </is>
+      </c>
+      <c r="AC537" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:08:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>995827639</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Eugenia</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V538">
+        <v>1</v>
+      </c>
+      <c r="W538" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y538" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="Z538" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA538" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:52:47</t>
+        </is>
+      </c>
+      <c r="AB538" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:41:48</t>
+        </is>
+      </c>
+      <c r="AC538" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:41:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>alex_29.5@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V539">
+        <v>2</v>
+      </c>
+      <c r="W539" t="inlineStr">
+        <is>
+          <t>0376-4</t>
+        </is>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y539" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z539" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA539" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:07:17</t>
+        </is>
+      </c>
+      <c r="AB539" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:52:45</t>
+        </is>
+      </c>
+      <c r="AC539" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:52:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>grisellezapata@gmail.com</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>953281591</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Griselda Del Carmen Zapata Días</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Alejandro Alberto Salinas Zapata</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V540">
+        <v>1</v>
+      </c>
+      <c r="W540" t="inlineStr">
+        <is>
+          <t>76016305-8</t>
+        </is>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y540" t="inlineStr">
+        <is>
+          <t>15221550-9</t>
+        </is>
+      </c>
+      <c r="Z540" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA540" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:18:15</t>
+        </is>
+      </c>
+      <c r="AB540" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:03:29</t>
+        </is>
+      </c>
+      <c r="AC540" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:03:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>roalissetsandoval2@gmail.com</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>973270705</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Lisset</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Florencia</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V541">
+        <v>2</v>
+      </c>
+      <c r="W541" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y541" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Z541" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA541" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:22:36</t>
+        </is>
+      </c>
+      <c r="AB541" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:00:59</t>
+        </is>
+      </c>
+      <c r="AC541" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:00:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>pizarropaulina57@gmail.com</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>942209329</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Paulina Pizarro</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Ágata</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V542">
+        <v>1</v>
+      </c>
+      <c r="W542" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y542" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="Z542" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA542" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:29:59</t>
+        </is>
+      </c>
+      <c r="AB542" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:25:59</t>
+        </is>
+      </c>
+      <c r="AC542" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:25:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>hector.sanmartin1984@gmail.com</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>962561346</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Aida</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V543">
+        <v>1</v>
+      </c>
+      <c r="W543" t="inlineStr">
+        <is>
+          <t>9270-2</t>
+        </is>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y543" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z543" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA543" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:30:26</t>
+        </is>
+      </c>
+      <c r="AB543" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:14:04</t>
+        </is>
+      </c>
+      <c r="AC543" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:14:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>gracelagos.duran@gmail.com</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>56981738051</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Joaquin</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V544">
+        <v>1</v>
+      </c>
+      <c r="W544" t="inlineStr">
+        <is>
+          <t>encuestador datodinamico</t>
+        </is>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y544" t="inlineStr">
+        <is>
+          <t>216680324</t>
+        </is>
+      </c>
+      <c r="Z544" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA544" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:53:12</t>
+        </is>
+      </c>
+      <c r="AB544" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:48:05</t>
+        </is>
+      </c>
+      <c r="AC544" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:48:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Clau.room200@gmail.com</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>971676485</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Amalia</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>Santiago centro</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V545">
+        <v>2</v>
+      </c>
+      <c r="W545" t="inlineStr">
+        <is>
+          <t>9270-2</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y545" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z545" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA545" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:24:39</t>
+        </is>
+      </c>
+      <c r="AB545" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:59:41</t>
+        </is>
+      </c>
+      <c r="AC545" t="inlineStr">
+        <is>
+          <t>2026-04-29 20:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>alonsocuzzi@gmail.com</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>904553956</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Alonso</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>esteban</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>andres</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>maipu</t>
+        </is>
+      </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V546">
+        <v>2</v>
+      </c>
+      <c r="W546" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y546" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="Z546" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA546" t="inlineStr">
+        <is>
+          <t>2026-04-29 21:31:02</t>
+        </is>
+      </c>
+      <c r="AB546" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:03:13</t>
+        </is>
+      </c>
+      <c r="AC546" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:03:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>romanodr1986@gmail.com</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>992240441</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Ramón</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V547">
+        <v>2</v>
+      </c>
+      <c r="W547" t="inlineStr">
+        <is>
+          <t>9270-3</t>
+        </is>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y547" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z547" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA547" t="inlineStr">
+        <is>
+          <t>2026-04-30 07:51:02</t>
+        </is>
+      </c>
+      <c r="AB547" t="inlineStr">
+        <is>
+          <t>2026-04-30 08:54:22</t>
+        </is>
+      </c>
+      <c r="AC547" t="inlineStr">
+        <is>
+          <t>2026-04-30 08:54:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>aidasanmartinvallejos1@gmail.com</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>971008539</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Aida</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V548">
+        <v>1</v>
+      </c>
+      <c r="W548" t="inlineStr">
+        <is>
+          <t>0376-9</t>
+        </is>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y548" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z548" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA548" t="inlineStr">
+        <is>
+          <t>2026-04-30 08:14:06</t>
+        </is>
+      </c>
+      <c r="AB548" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:07:39</t>
+        </is>
+      </c>
+      <c r="AC548" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:07:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>yesenia.ariadne1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>941821708</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Ariadne</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Eduards</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Yessenia</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V549">
+        <v>1</v>
+      </c>
+      <c r="W549" t="inlineStr">
+        <is>
+          <t>9270-3</t>
+        </is>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y549" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z549" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA549" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:13:17</t>
+        </is>
+      </c>
+      <c r="AB549" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:07:14</t>
+        </is>
+      </c>
+      <c r="AC549" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:07:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>sirena.diaz.a@gmail.com</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>973552239</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V550">
+        <v>1</v>
+      </c>
+      <c r="W550" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y550" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Z550" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA550" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:31:49</t>
+        </is>
+      </c>
+      <c r="AB550" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:59:30</t>
+        </is>
+      </c>
+      <c r="AC550" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:59:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>pailahualcristian@gmail.com</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>993578356</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V551">
+        <v>1</v>
+      </c>
+      <c r="W551" t="inlineStr">
+        <is>
+          <t>0376-10</t>
+        </is>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y551" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z551" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA551" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:51:07</t>
+        </is>
+      </c>
+      <c r="AB551" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:26:11</t>
+        </is>
+      </c>
+      <c r="AC551" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:26:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>erikayr3@gmail.com</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>945216601</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Erika Sagredo</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Martina Sagredo</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V552">
+        <v>1</v>
+      </c>
+      <c r="W552" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y552" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z552" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA552" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:54:41</t>
+        </is>
+      </c>
+      <c r="AB552" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:18:59</t>
+        </is>
+      </c>
+      <c r="AC552" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>fran.jorquera.valdivia@gmail.com</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>987006605</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Facundo</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V553">
+        <v>1</v>
+      </c>
+      <c r="W553" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y553" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z553" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA553" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:18:23</t>
+        </is>
+      </c>
+      <c r="AB553" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:57:10</t>
+        </is>
+      </c>
+      <c r="AC553" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:57:10</t>
         </is>
       </c>
     </row>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC553"/>
+  <dimension ref="A1:AC581"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -45239,6 +45239,16 @@
           <t>Hombre</t>
         </is>
       </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Ninoska</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R442" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -56543,12 +56553,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>pailahualcristian@gmail.com</t>
+          <t>caricerpa@hotmail.com</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>993578356</t>
+          <t>956414467</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -56558,17 +56568,17 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -56578,7 +56588,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -56586,6 +56596,16 @@
           <t>Mujer</t>
         </is>
       </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R551" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -56593,7 +56613,7 @@
       </c>
       <c r="S551" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="T551" t="inlineStr">
@@ -56611,17 +56631,17 @@
       </c>
       <c r="W551" t="inlineStr">
         <is>
-          <t>0376-10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="X551" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y551" t="inlineStr">
         <is>
-          <t>17250376-4</t>
+          <t>13081719-k</t>
         </is>
       </c>
       <c r="Z551" s="2">
@@ -56629,29 +56649,29 @@
       </c>
       <c r="AA551" t="inlineStr">
         <is>
-          <t>2026-04-30 09:51:07</t>
+          <t>2026-04-30 09:46:05</t>
         </is>
       </c>
       <c r="AB551" t="inlineStr">
         <is>
-          <t>2026-04-30 10:26:11</t>
+          <t>2026-04-30 11:38:10</t>
         </is>
       </c>
       <c r="AC551" t="inlineStr">
         <is>
-          <t>2026-04-30 10:26:11</t>
+          <t>2026-04-30 11:38:10</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>erikayr3@gmail.com</t>
+          <t>pailahualcristian@gmail.com</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>945216601</t>
+          <t>993578356</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -56661,21 +56681,31 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Erika Sagredo</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Martina Sagredo</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
           <t>Mujer</t>
         </is>
       </c>
@@ -56691,7 +56721,7 @@
       </c>
       <c r="T552" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U552" t="inlineStr">
@@ -56704,17 +56734,17 @@
       </c>
       <c r="W552" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0376-10</t>
         </is>
       </c>
       <c r="X552" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y552" t="inlineStr">
         <is>
-          <t>13081719-k</t>
+          <t>17250376-4</t>
         </is>
       </c>
       <c r="Z552" s="2">
@@ -56722,29 +56752,29 @@
       </c>
       <c r="AA552" t="inlineStr">
         <is>
-          <t>2026-04-30 09:54:41</t>
+          <t>2026-04-30 09:51:07</t>
         </is>
       </c>
       <c r="AB552" t="inlineStr">
         <is>
-          <t>2026-04-30 10:18:59</t>
+          <t>2026-04-30 10:26:11</t>
         </is>
       </c>
       <c r="AC552" t="inlineStr">
         <is>
-          <t>2026-04-30 10:18:59</t>
+          <t>2026-04-30 10:26:11</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>fran.jorquera.valdivia@gmail.com</t>
+          <t>erikayr3@gmail.com</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>987006605</t>
+          <t>945216601</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -56754,7 +56784,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>Valeria</t>
+          <t>Erika Sagredo</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -56764,7 +56794,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Martina Sagredo</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -56772,16 +56802,6 @@
           <t>Mujer</t>
         </is>
       </c>
-      <c r="H553" t="inlineStr">
-        <is>
-          <t>Facundo</t>
-        </is>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
       <c r="R553" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -56789,7 +56809,7 @@
       </c>
       <c r="S553" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="T553" t="inlineStr">
@@ -56807,7 +56827,7 @@
       </c>
       <c r="W553" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="X553" t="inlineStr">
@@ -56825,17 +56845,3111 @@
       </c>
       <c r="AA553" t="inlineStr">
         <is>
+          <t>2026-04-30 09:54:41</t>
+        </is>
+      </c>
+      <c r="AB553" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:18:59</t>
+        </is>
+      </c>
+      <c r="AC553" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>fran.jorquera.valdivia@gmail.com</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>987006605</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Facundo</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V554">
+        <v>1</v>
+      </c>
+      <c r="W554" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y554" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z554" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA554" t="inlineStr">
+        <is>
           <t>2026-04-30 10:18:23</t>
         </is>
       </c>
-      <c r="AB553" t="inlineStr">
+      <c r="AB554" t="inlineStr">
         <is>
           <t>2026-04-30 10:57:10</t>
         </is>
       </c>
-      <c r="AC553" t="inlineStr">
+      <c r="AC554" t="inlineStr">
         <is>
           <t>2026-04-30 10:57:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>ivarro112370@gmail.com</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>999641492</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>Qulicura</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V555">
+        <v>1</v>
+      </c>
+      <c r="W555" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y555" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+      <c r="Z555" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA555" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:38:42</t>
+        </is>
+      </c>
+      <c r="AB555" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:02:23</t>
+        </is>
+      </c>
+      <c r="AC555" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:02:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>momentosprint.correo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>958278791</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Byron</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V556">
+        <v>1</v>
+      </c>
+      <c r="W556" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y556" t="inlineStr">
+        <is>
+          <t>17244539k</t>
+        </is>
+      </c>
+      <c r="Z556" s="2">
+        <v>46141</v>
+      </c>
+      <c r="AA556" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:59:32</t>
+        </is>
+      </c>
+      <c r="AB556" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:41:34</t>
+        </is>
+      </c>
+      <c r="AC556" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:41:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>c.camila.aguilera@gmail.com</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>979521340</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Camila Aguilera</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Sonia del Carmen</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Daniel Enrique</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>Gabriel Alonso</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V557">
+        <v>1</v>
+      </c>
+      <c r="W557" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y557" t="inlineStr">
+        <is>
+          <t>13081719-K</t>
+        </is>
+      </c>
+      <c r="Z557" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA557" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:38:10</t>
+        </is>
+      </c>
+      <c r="AB557" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:12:44</t>
+        </is>
+      </c>
+      <c r="AC557" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:12:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>maathii.lol@gmail.com</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>966712998</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Estrella</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V558">
+        <v>2</v>
+      </c>
+      <c r="W558" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y558" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="Z558" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA558" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:38:20</t>
+        </is>
+      </c>
+      <c r="AB558" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:14:16</t>
+        </is>
+      </c>
+      <c r="AC558" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:14:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>cathypg13@gmail.com</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>69897495</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Catherine gonzalez</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Rayen</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V559">
+        <v>1</v>
+      </c>
+      <c r="W559" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y559" t="inlineStr">
+        <is>
+          <t>13081718k</t>
+        </is>
+      </c>
+      <c r="Z559" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA559" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:38:21</t>
+        </is>
+      </c>
+      <c r="AB559" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:36:59</t>
+        </is>
+      </c>
+      <c r="AC559" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:36:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>974015077</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Yerelin</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Bastian</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V560">
+        <v>1</v>
+      </c>
+      <c r="W560" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y560" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z560" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA560" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:57:21</t>
+        </is>
+      </c>
+      <c r="AB560" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:31:09</t>
+        </is>
+      </c>
+      <c r="AC560" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:31:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>carloszuiga851@yahoo.com</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>944018826</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Leticia</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V561">
+        <v>1</v>
+      </c>
+      <c r="W561" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y561" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+      <c r="Z561" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA561" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:05:02</t>
+        </is>
+      </c>
+      <c r="AB561" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:29:32</t>
+        </is>
+      </c>
+      <c r="AC561" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:29:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>amanda.guerra.barria@gmail.com</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>Rafaella</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V562">
+        <v>1</v>
+      </c>
+      <c r="W562" t="inlineStr">
+        <is>
+          <t>0376-11</t>
+        </is>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y562" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z562" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA562" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:05:16</t>
+        </is>
+      </c>
+      <c r="AB562" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:41:21</t>
+        </is>
+      </c>
+      <c r="AC562" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:41:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>danissamanriquez38@gmail.com</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>968164021</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>Danissa</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V563">
+        <v>1</v>
+      </c>
+      <c r="W563" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y563" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z563" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA563" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:41:58</t>
+        </is>
+      </c>
+      <c r="AB563" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:27:56</t>
+        </is>
+      </c>
+      <c r="AC563" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:27:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>jm.gonzalez046@gmail.com</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>968503698</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Jose Gonzalez</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Roxana Arévalo</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Claudia Arévalo</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>Agustina González</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V564">
+        <v>1</v>
+      </c>
+      <c r="W564" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y564" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z564" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA564" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:53:34</t>
+        </is>
+      </c>
+      <c r="AB564" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:39:20</t>
+        </is>
+      </c>
+      <c r="AC564" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:39:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>alejandragomez@gmial.com</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>967583643</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>estela</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>maipu</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V565">
+        <v>1</v>
+      </c>
+      <c r="W565" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y565" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="Z565" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA565" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:14:19</t>
+        </is>
+      </c>
+      <c r="AB565" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:51:55</t>
+        </is>
+      </c>
+      <c r="AC565" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:51:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>920726862</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Marisol</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Yoselin</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V566">
+        <v>1</v>
+      </c>
+      <c r="W566" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y566" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z566" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA566" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:40:45</t>
+        </is>
+      </c>
+      <c r="AB566" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:19:50</t>
+        </is>
+      </c>
+      <c r="AC566" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:19:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Mauriciopalacioxx@gmail.com</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>965644737</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V567">
+        <v>2</v>
+      </c>
+      <c r="W567" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X567" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y567" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="Z567" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA567" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:52:13</t>
+        </is>
+      </c>
+      <c r="AB567" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:50:07</t>
+        </is>
+      </c>
+      <c r="AC567" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:50:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>oyarzun.cristian.m@gmail.com</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>56968498437</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Flor</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>Lo prado</t>
+        </is>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V568">
+        <v>1</v>
+      </c>
+      <c r="W568" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X568" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y568" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z568" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA568" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:53:40</t>
+        </is>
+      </c>
+      <c r="AB568" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:42:54</t>
+        </is>
+      </c>
+      <c r="AC568" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>javiii.sp88@gmail.com</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>934535857</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Constanza</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V569">
+        <v>1</v>
+      </c>
+      <c r="W569" t="inlineStr">
+        <is>
+          <t>0376-12</t>
+        </is>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y569" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z569" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA569" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:56:27</t>
+        </is>
+      </c>
+      <c r="AB569" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:54:12</t>
+        </is>
+      </c>
+      <c r="AC569" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:54:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>veritolopez1966@gmail.com</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>982696981</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Verónica</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V570">
+        <v>1</v>
+      </c>
+      <c r="W570" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X570" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y570" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="Z570" s="2">
+        <v>46135</v>
+      </c>
+      <c r="AA570" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:45:33</t>
+        </is>
+      </c>
+      <c r="AB570" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:22:16</t>
+        </is>
+      </c>
+      <c r="AC570" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:22:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>eugeniavelez1@gmail.com</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>945385634</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Eugenia</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>Isabela</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V571">
+        <v>1</v>
+      </c>
+      <c r="W571" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X571" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y571" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="Z571" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA571" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:52:38</t>
+        </is>
+      </c>
+      <c r="AB571" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:37:39</t>
+        </is>
+      </c>
+      <c r="AC571" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:37:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>valeriavalenzuelajerez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>56058087</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Valeria-  javier-José Tomas- Amapola</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Jose tomas</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>Amapola</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V572">
+        <v>1</v>
+      </c>
+      <c r="W572" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y572" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z572" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA572" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:54:26</t>
+        </is>
+      </c>
+      <c r="AB572" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:26:31</t>
+        </is>
+      </c>
+      <c r="AC572" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:26:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>lardypailahual@gmail.com</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>940612507</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Maylen</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Lardy</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V573">
+        <v>3</v>
+      </c>
+      <c r="W573" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y573" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z573" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA573" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:17:08</t>
+        </is>
+      </c>
+      <c r="AB573" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:05:07</t>
+        </is>
+      </c>
+      <c r="AC573" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:05:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>emilianosinfuenmtes@gmail.com</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>956545787</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Emiliano</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V574">
+        <v>1</v>
+      </c>
+      <c r="W574" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y574" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="Z574" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA574" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:38:30</t>
+        </is>
+      </c>
+      <c r="AB574" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:13:54</t>
+        </is>
+      </c>
+      <c r="AC574" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:13:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>damaris.gonzalez.g@gmail.con</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>944444056</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Damaris</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Mariano</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V575">
+        <v>1</v>
+      </c>
+      <c r="W575" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y575" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z575" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA575" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:01:39</t>
+        </is>
+      </c>
+      <c r="AB575" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:17:23</t>
+        </is>
+      </c>
+      <c r="AC575" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:17:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>rociopaz1@gmail.com</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>950337522</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Rocío</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V576">
+        <v>2</v>
+      </c>
+      <c r="W576" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y576" t="inlineStr">
+        <is>
+          <t>2115605-6</t>
+        </is>
+      </c>
+      <c r="Z576" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA576" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:17:42</t>
+        </is>
+      </c>
+      <c r="AB576" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:06:45</t>
+        </is>
+      </c>
+      <c r="AC576" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>chikititamia@gmail.com</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Tamara</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Hernan</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>Cerro navia</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V577">
+        <v>1</v>
+      </c>
+      <c r="W577" t="inlineStr">
+        <is>
+          <t>0376-13</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y577" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z577" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA577" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:20:18</t>
+        </is>
+      </c>
+      <c r="AB577" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:04:47</t>
+        </is>
+      </c>
+      <c r="AC577" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:04:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>mariana1994.cr@gmail.com</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>930692205</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Danilo</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V578">
+        <v>1</v>
+      </c>
+      <c r="W578" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y578" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z578" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA578" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:32:01</t>
+        </is>
+      </c>
+      <c r="AB578" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:02:57</t>
+        </is>
+      </c>
+      <c r="AC578" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>gloria.parada@gmail.com</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>996725715</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Leonardo</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V579">
+        <v>2</v>
+      </c>
+      <c r="W579" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y579" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z579" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA579" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:36:02</t>
+        </is>
+      </c>
+      <c r="AB579" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:18:25</t>
+        </is>
+      </c>
+      <c r="AC579" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:18:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>bustamantepatricioharling@gmail.com</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>950257224</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>Quinta normal</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V580">
+        <v>1</v>
+      </c>
+      <c r="W580" t="inlineStr">
+        <is>
+          <t>0376-14</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y580" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z580" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA580" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:37:17</t>
+        </is>
+      </c>
+      <c r="AB580" t="inlineStr">
+        <is>
+          <t>2026-04-30 18:11:49</t>
+        </is>
+      </c>
+      <c r="AC580" t="inlineStr">
+        <is>
+          <t>2026-04-30 18:11:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>975626206</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Steven</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Anuar</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Delu</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>María Angela</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V581">
+        <v>2</v>
+      </c>
+      <c r="W581" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y581" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z581" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA581" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:51:58</t>
+        </is>
+      </c>
+      <c r="AB581" t="inlineStr">
+        <is>
+          <t>2026-04-30 18:40:33</t>
+        </is>
+      </c>
+      <c r="AC581" t="inlineStr">
+        <is>
+          <t>2026-04-30 18:40:31</t>
         </is>
       </c>
     </row>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC581"/>
+  <dimension ref="A1:AC651"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -59953,6 +59953,7536 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>sabarcallanos@gmail.com</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>56949063048</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Luciano</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Gastón</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V582">
+        <v>2</v>
+      </c>
+      <c r="W582" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y582" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z582" s="2">
+        <v>46387</v>
+      </c>
+      <c r="AA582" t="inlineStr">
+        <is>
+          <t>2026-04-30 18:13:01</t>
+        </is>
+      </c>
+      <c r="AB582" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:10:11</t>
+        </is>
+      </c>
+      <c r="AC582" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>aibarrvalenzuela@gmail.com</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>997764635</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Facundo</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V583">
+        <v>1</v>
+      </c>
+      <c r="W583" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y583" t="inlineStr">
+        <is>
+          <t>13081719-K</t>
+        </is>
+      </c>
+      <c r="Z583" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA583" t="inlineStr">
+        <is>
+          <t>2026-04-30 18:14:40</t>
+        </is>
+      </c>
+      <c r="AB583" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:08:56</t>
+        </is>
+      </c>
+      <c r="AC583" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:08:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>jenniferferreira.to@gmail.com</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>56926055586</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Jennifer Ferreira</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Jacqueline Zamorano</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Joaquín ferreira</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>Catalina ferreira</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Máximo Olivera ferreira</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V584">
+        <v>1</v>
+      </c>
+      <c r="W584" t="inlineStr">
+        <is>
+          <t>Correlativo 16</t>
+        </is>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y584" t="inlineStr">
+        <is>
+          <t>13081719-K</t>
+        </is>
+      </c>
+      <c r="Z584" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA584" t="inlineStr">
+        <is>
+          <t>2026-04-30 18:34:43</t>
+        </is>
+      </c>
+      <c r="AB584" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:34:47</t>
+        </is>
+      </c>
+      <c r="AC584" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:34:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>darlingrebolledo827@gmail.com</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>930872103</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>Darling</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>La cisterna</t>
+        </is>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V585">
+        <v>1</v>
+      </c>
+      <c r="W585" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="X585" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y585" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z585" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA585" t="inlineStr">
+        <is>
+          <t>2026-04-30 18:52:49</t>
+        </is>
+      </c>
+      <c r="AB585" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:36:26</t>
+        </is>
+      </c>
+      <c r="AC585" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:36:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>roxanaguzman.22@gmail.com</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>959695604</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Roxana</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Constanza</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Claudio</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V586">
+        <v>1</v>
+      </c>
+      <c r="W586" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X586" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y586" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Z586" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA586" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:07:04</t>
+        </is>
+      </c>
+      <c r="AB586" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:40:12</t>
+        </is>
+      </c>
+      <c r="AC586" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:40:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>lc7975122@gmail.com</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>993075164</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Marina</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Tamar</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V587">
+        <v>1</v>
+      </c>
+      <c r="W587" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="X587" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y587" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z587" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA587" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:50:45</t>
+        </is>
+      </c>
+      <c r="AB587" t="inlineStr">
+        <is>
+          <t>2026-04-30 20:31:21</t>
+        </is>
+      </c>
+      <c r="AC587" t="inlineStr">
+        <is>
+          <t>2026-04-30 20:31:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>mcastillolira172@gmail.com</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>933391827</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Francisca castillo</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>María José castillo toro</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>Catari castillo toro</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>Matías castillo toro</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>Pte alto</t>
+        </is>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V588">
+        <v>1</v>
+      </c>
+      <c r="W588" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="X588" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y588" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z588" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA588" t="inlineStr">
+        <is>
+          <t>2026-04-30 20:00:03</t>
+        </is>
+      </c>
+      <c r="AB588" t="inlineStr">
+        <is>
+          <t>2026-04-30 20:48:08</t>
+        </is>
+      </c>
+      <c r="AC588" t="inlineStr">
+        <is>
+          <t>2026-04-30 20:48:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>mateo.manriquez1975@gmail.com</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>954600152</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Nicol</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V589">
+        <v>1</v>
+      </c>
+      <c r="W589" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="X589" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y589" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="Z589" s="2">
+        <v>46138</v>
+      </c>
+      <c r="AA589" t="inlineStr">
+        <is>
+          <t>2026-04-30 21:02:39</t>
+        </is>
+      </c>
+      <c r="AB589" t="inlineStr">
+        <is>
+          <t>2026-04-30 21:40:35</t>
+        </is>
+      </c>
+      <c r="AC589" t="inlineStr">
+        <is>
+          <t>2026-04-30 21:40:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>emilypascal301018@gmail.com</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>999590002</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Sussana</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Jorje</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>Leonardo</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>Jlrge rey</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V590">
+        <v>1</v>
+      </c>
+      <c r="W590" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y590" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="Z590" s="2">
+        <v>46142</v>
+      </c>
+      <c r="AA590" t="inlineStr">
+        <is>
+          <t>2026-04-30 21:21:56</t>
+        </is>
+      </c>
+      <c r="AB590" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:15:53</t>
+        </is>
+      </c>
+      <c r="AC590" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:15:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>gersongutierrez1992@gmail.comb</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>976734691</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Gerson</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Anahis</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Pabla</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>Judith</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>Mariano</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V591">
+        <v>1</v>
+      </c>
+      <c r="W591" t="inlineStr">
+        <is>
+          <t>9270-5</t>
+        </is>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y591" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z591" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA591" t="inlineStr">
+        <is>
+          <t>2026-05-01 08:12:46</t>
+        </is>
+      </c>
+      <c r="AB591" t="inlineStr">
+        <is>
+          <t>2026-05-01 09:14:05</t>
+        </is>
+      </c>
+      <c r="AC591" t="inlineStr">
+        <is>
+          <t>2026-05-01 09:14:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>orregomoreno2000@gmail.com</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>972315151</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Darío</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>Carla</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V592">
+        <v>1</v>
+      </c>
+      <c r="W592" t="inlineStr">
+        <is>
+          <t>9270-5</t>
+        </is>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y592" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z592" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA592" t="inlineStr">
+        <is>
+          <t>2026-05-01 09:29:21</t>
+        </is>
+      </c>
+      <c r="AB592" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:14:18</t>
+        </is>
+      </c>
+      <c r="AC592" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:14:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>alejandra.alarcon.n86@gmail.com</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>95627755</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Cristobal</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V593">
+        <v>1</v>
+      </c>
+      <c r="W593" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y593" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z593" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA593" t="inlineStr">
+        <is>
+          <t>2026-05-01 09:53:38</t>
+        </is>
+      </c>
+      <c r="AB593" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:24:50</t>
+        </is>
+      </c>
+      <c r="AC593" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:24:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>mar.valle1989@gmail.com</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Mariela</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V594">
+        <v>1</v>
+      </c>
+      <c r="W594" t="inlineStr">
+        <is>
+          <t>0376-15</t>
+        </is>
+      </c>
+      <c r="X594" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y594" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z594" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA594" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:04:40</t>
+        </is>
+      </c>
+      <c r="AB594" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:52:01</t>
+        </is>
+      </c>
+      <c r="AC594" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:52:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Alanveliz2005@gmail.com</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>933125624</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Sayen</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Esteban</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>Regina</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V595">
+        <v>1</v>
+      </c>
+      <c r="W595" t="inlineStr">
+        <is>
+          <t>9270-5</t>
+        </is>
+      </c>
+      <c r="X595" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y595" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z595" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA595" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:30:42</t>
+        </is>
+      </c>
+      <c r="AB595" t="inlineStr">
+        <is>
+          <t>2026-05-01 11:05:17</t>
+        </is>
+      </c>
+      <c r="AC595" t="inlineStr">
+        <is>
+          <t>2026-05-01 11:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>986272995</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Analia</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Marianela</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Juana</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V596">
+        <v>1</v>
+      </c>
+      <c r="W596" t="inlineStr">
+        <is>
+          <t>9270-5</t>
+        </is>
+      </c>
+      <c r="X596" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y596" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z596" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA596" t="inlineStr">
+        <is>
+          <t>2026-05-01 14:04:45</t>
+        </is>
+      </c>
+      <c r="AB596" t="inlineStr">
+        <is>
+          <t>2026-05-01 15:13:08</t>
+        </is>
+      </c>
+      <c r="AC596" t="inlineStr">
+        <is>
+          <t>2026-05-01 15:13:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>feli.rt@live.cl</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>939653590</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V597">
+        <v>1</v>
+      </c>
+      <c r="W597" t="inlineStr">
+        <is>
+          <t>0376-15</t>
+        </is>
+      </c>
+      <c r="X597" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y597" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z597" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA597" t="inlineStr">
+        <is>
+          <t>2026-05-01 15:59:59</t>
+        </is>
+      </c>
+      <c r="AB597" t="inlineStr">
+        <is>
+          <t>2026-05-01 16:55:27</t>
+        </is>
+      </c>
+      <c r="AC597" t="inlineStr">
+        <is>
+          <t>2026-05-01 16:55:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>fabiolaburdiles75@gmail.com</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Fabiola</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Ariel</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Christopher</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>Amaru</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S598" t="inlineStr">
+        <is>
+          <t>Santiago centro</t>
+        </is>
+      </c>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V598">
+        <v>1</v>
+      </c>
+      <c r="W598" t="inlineStr">
+        <is>
+          <t>9270-6</t>
+        </is>
+      </c>
+      <c r="X598" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y598" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z598" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA598" t="inlineStr">
+        <is>
+          <t>2026-05-01 16:33:06</t>
+        </is>
+      </c>
+      <c r="AB598" t="inlineStr">
+        <is>
+          <t>2026-05-01 17:21:27</t>
+        </is>
+      </c>
+      <c r="AC598" t="inlineStr">
+        <is>
+          <t>2026-05-01 17:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>sdd.1314@gmail.com</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>947181570</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Benhamin</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V599">
+        <v>1</v>
+      </c>
+      <c r="W599" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="X599" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y599" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="Z599" s="2">
+        <v>46143</v>
+      </c>
+      <c r="AA599" t="inlineStr">
+        <is>
+          <t>2026-05-01 18:49:26</t>
+        </is>
+      </c>
+      <c r="AB599" t="inlineStr">
+        <is>
+          <t>2026-05-01 19:52:31</t>
+        </is>
+      </c>
+      <c r="AC599" t="inlineStr">
+        <is>
+          <t>2026-05-01 19:52:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>967067991</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Ramón</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Negmi</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>Juana</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V600">
+        <v>1</v>
+      </c>
+      <c r="W600" t="inlineStr">
+        <is>
+          <t>9270-7</t>
+        </is>
+      </c>
+      <c r="X600" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y600" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z600" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA600" t="inlineStr">
+        <is>
+          <t>2026-05-02 07:45:06</t>
+        </is>
+      </c>
+      <c r="AB600" t="inlineStr">
+        <is>
+          <t>2026-05-02 08:24:45</t>
+        </is>
+      </c>
+      <c r="AC600" t="inlineStr">
+        <is>
+          <t>2026-05-02 08:24:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>herrerajaviera950@gmail.com</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>El monte</t>
+        </is>
+      </c>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V601">
+        <v>2</v>
+      </c>
+      <c r="W601" t="inlineStr">
+        <is>
+          <t>9270-7</t>
+        </is>
+      </c>
+      <c r="X601" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y601" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z601" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA601" t="inlineStr">
+        <is>
+          <t>2026-05-02 08:36:15</t>
+        </is>
+      </c>
+      <c r="AB601" t="inlineStr">
+        <is>
+          <t>2026-05-02 09:19:49</t>
+        </is>
+      </c>
+      <c r="AC601" t="inlineStr">
+        <is>
+          <t>2026-05-02 09:19:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>susanaopazo2018@gmail.com</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>926394000</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Abelardo</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V602">
+        <v>1</v>
+      </c>
+      <c r="W602" t="inlineStr">
+        <is>
+          <t>9270-7</t>
+        </is>
+      </c>
+      <c r="X602" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y602" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z602" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA602" t="inlineStr">
+        <is>
+          <t>2026-05-02 09:55:21</t>
+        </is>
+      </c>
+      <c r="AB602" t="inlineStr">
+        <is>
+          <t>2026-05-02 10:28:13</t>
+        </is>
+      </c>
+      <c r="AC602" t="inlineStr">
+        <is>
+          <t>2026-05-02 10:28:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>anitacayun@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>983218190</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Ana Marcela</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Toto</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V603">
+        <v>1</v>
+      </c>
+      <c r="W603" t="inlineStr">
+        <is>
+          <t>9270-8</t>
+        </is>
+      </c>
+      <c r="X603" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y603" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z603" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA603" t="inlineStr">
+        <is>
+          <t>2026-05-02 11:52:51</t>
+        </is>
+      </c>
+      <c r="AB603" t="inlineStr">
+        <is>
+          <t>2026-05-02 12:23:50</t>
+        </is>
+      </c>
+      <c r="AC603" t="inlineStr">
+        <is>
+          <t>2026-05-02 12:23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>eduranmachuca@gmail.com</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>999025218</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Estefani</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V604">
+        <v>1</v>
+      </c>
+      <c r="W604" t="inlineStr">
+        <is>
+          <t>9270-8</t>
+        </is>
+      </c>
+      <c r="X604" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y604" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z604" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA604" t="inlineStr">
+        <is>
+          <t>2026-05-02 12:50:32</t>
+        </is>
+      </c>
+      <c r="AB604" t="inlineStr">
+        <is>
+          <t>2026-05-02 13:33:01</t>
+        </is>
+      </c>
+      <c r="AC604" t="inlineStr">
+        <is>
+          <t>2026-05-02 13:33:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>danielacurin02@gmail.com</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>999005364</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Marly</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>Conchali</t>
+        </is>
+      </c>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V605">
+        <v>1</v>
+      </c>
+      <c r="W605" t="inlineStr">
+        <is>
+          <t>9270-8</t>
+        </is>
+      </c>
+      <c r="X605" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y605" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z605" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA605" t="inlineStr">
+        <is>
+          <t>2026-05-02 13:58:59</t>
+        </is>
+      </c>
+      <c r="AB605" t="inlineStr">
+        <is>
+          <t>2026-05-02 14:44:19</t>
+        </is>
+      </c>
+      <c r="AC605" t="inlineStr">
+        <is>
+          <t>2026-05-02 14:44:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>matuskath_19@gmail.com</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>995818679</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Dairilys</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V606">
+        <v>1</v>
+      </c>
+      <c r="W606" t="inlineStr">
+        <is>
+          <t>0376-15</t>
+        </is>
+      </c>
+      <c r="X606" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y606" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z606" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA606" t="inlineStr">
+        <is>
+          <t>2026-05-02 14:30:14</t>
+        </is>
+      </c>
+      <c r="AB606" t="inlineStr">
+        <is>
+          <t>2026-05-02 15:21:39</t>
+        </is>
+      </c>
+      <c r="AC606" t="inlineStr">
+        <is>
+          <t>2026-05-02 15:21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>eabarca.araya@gmail.com</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>99005360</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Eliecer</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Karina</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Gina</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>Cristina</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V607">
+        <v>2</v>
+      </c>
+      <c r="W607" t="inlineStr">
+        <is>
+          <t>9270-8</t>
+        </is>
+      </c>
+      <c r="X607" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y607" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z607" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA607" t="inlineStr">
+        <is>
+          <t>2026-05-02 15:06:58</t>
+        </is>
+      </c>
+      <c r="AB607" t="inlineStr">
+        <is>
+          <t>2026-05-02 15:43:06</t>
+        </is>
+      </c>
+      <c r="AC607" t="inlineStr">
+        <is>
+          <t>2026-05-02 15:43:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>sofiacontreras@gmail.com</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>967668325</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V608">
+        <v>1</v>
+      </c>
+      <c r="W608" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X608" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y608" t="inlineStr">
+        <is>
+          <t>2115605-6</t>
+        </is>
+      </c>
+      <c r="Z608" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA608" t="inlineStr">
+        <is>
+          <t>2026-05-02 15:43:51</t>
+        </is>
+      </c>
+      <c r="AB608" t="inlineStr">
+        <is>
+          <t>2026-05-02 16:34:48</t>
+        </is>
+      </c>
+      <c r="AC608" t="inlineStr">
+        <is>
+          <t>2026-05-02 16:34:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>aida.sv@educacionvillarrica.cl</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Aida</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>Amaro</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V609">
+        <v>1</v>
+      </c>
+      <c r="W609" t="inlineStr">
+        <is>
+          <t>0376-16</t>
+        </is>
+      </c>
+      <c r="X609" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y609" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z609" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA609" t="inlineStr">
+        <is>
+          <t>2026-05-02 15:49:13</t>
+        </is>
+      </c>
+      <c r="AB609" t="inlineStr">
+        <is>
+          <t>2026-05-02 16:46:13</t>
+        </is>
+      </c>
+      <c r="AC609" t="inlineStr">
+        <is>
+          <t>2026-05-02 16:46:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>diego.zunigas@gmail.com</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>999005360</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Anahi</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V610">
+        <v>2</v>
+      </c>
+      <c r="W610" t="inlineStr">
+        <is>
+          <t>9270-8</t>
+        </is>
+      </c>
+      <c r="X610" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y610" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z610" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA610" t="inlineStr">
+        <is>
+          <t>2026-05-02 16:25:51</t>
+        </is>
+      </c>
+      <c r="AB610" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:24:56</t>
+        </is>
+      </c>
+      <c r="AC610" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:24:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>lissetteaaron@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>972310992</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Melania</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Eilim</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Matilde</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>Lareina</t>
+        </is>
+      </c>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V611">
+        <v>1</v>
+      </c>
+      <c r="W611" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="X611" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y611" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="Z611" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA611" t="inlineStr">
+        <is>
+          <t>2026-05-02 16:34:26</t>
+        </is>
+      </c>
+      <c r="AB611" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:35:42</t>
+        </is>
+      </c>
+      <c r="AC611" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:35:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>catherinepanales@gmail.com</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>950448265</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V612">
+        <v>1</v>
+      </c>
+      <c r="W612" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X612" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y612" t="inlineStr">
+        <is>
+          <t>2115605-6</t>
+        </is>
+      </c>
+      <c r="Z612" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA612" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:08:22</t>
+        </is>
+      </c>
+      <c r="AB612" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:55:00</t>
+        </is>
+      </c>
+      <c r="AC612" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:55:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>guerra3110@gmail.com</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>94284510</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Rsteban</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Gissel</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>Maximiliano</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>Puernte alto</t>
+        </is>
+      </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V613">
+        <v>1</v>
+      </c>
+      <c r="W613" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="X613" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y613" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="Z613" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA613" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:36:06</t>
+        </is>
+      </c>
+      <c r="AB613" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:32:23</t>
+        </is>
+      </c>
+      <c r="AC613" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:32:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>lemc1997@gmail.com</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>Cochali</t>
+        </is>
+      </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V614">
+        <v>1</v>
+      </c>
+      <c r="W614" t="inlineStr">
+        <is>
+          <t>9270-9</t>
+        </is>
+      </c>
+      <c r="X614" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y614" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z614" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA614" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:56:16</t>
+        </is>
+      </c>
+      <c r="AB614" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:33:13</t>
+        </is>
+      </c>
+      <c r="AC614" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:33:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>noentrega@gmail.com</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>989282899</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Silvia</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Edson</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Hugo</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>Ignacia</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V615">
+        <v>1</v>
+      </c>
+      <c r="W615" t="inlineStr">
+        <is>
+          <t>0376-16</t>
+        </is>
+      </c>
+      <c r="X615" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y615" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z615" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA615" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:24:01</t>
+        </is>
+      </c>
+      <c r="AB615" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:56:50</t>
+        </is>
+      </c>
+      <c r="AC615" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:56:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>evelyn22@gmail.com</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>9999999</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Alexia</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>Luciana</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V616">
+        <v>1</v>
+      </c>
+      <c r="W616" t="inlineStr">
+        <is>
+          <t>9270-8</t>
+        </is>
+      </c>
+      <c r="X616" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y616" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z616" s="2">
+        <v>46144</v>
+      </c>
+      <c r="AA616" t="inlineStr">
+        <is>
+          <t>2026-05-02 19:09:46</t>
+        </is>
+      </c>
+      <c r="AB616" t="inlineStr">
+        <is>
+          <t>2026-05-02 19:42:27</t>
+        </is>
+      </c>
+      <c r="AC616" t="inlineStr">
+        <is>
+          <t>2026-05-02 19:42:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>yessenia_andrea@live.cl</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>972369971</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Yessenia</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>Santiago centro</t>
+        </is>
+      </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V617">
+        <v>1</v>
+      </c>
+      <c r="W617" t="inlineStr">
+        <is>
+          <t>9270-9</t>
+        </is>
+      </c>
+      <c r="X617" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y617" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z617" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA617" t="inlineStr">
+        <is>
+          <t>2026-05-03 09:33:51</t>
+        </is>
+      </c>
+      <c r="AB617" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:19:03</t>
+        </is>
+      </c>
+      <c r="AC617" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:19:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>verticalfuy@gmail.com</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>966859242</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Cristobal</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V618">
+        <v>1</v>
+      </c>
+      <c r="W618" t="inlineStr">
+        <is>
+          <t>0376-17</t>
+        </is>
+      </c>
+      <c r="X618" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y618" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z618" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA618" t="inlineStr">
+        <is>
+          <t>2026-05-03 09:34:30</t>
+        </is>
+      </c>
+      <c r="AB618" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:18:59</t>
+        </is>
+      </c>
+      <c r="AC618" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>nicolas.riquelmedv1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>932416962</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Anahi</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>Mariola</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V619">
+        <v>3</v>
+      </c>
+      <c r="W619" t="inlineStr">
+        <is>
+          <t>9270-9</t>
+        </is>
+      </c>
+      <c r="X619" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y619" t="inlineStr">
+        <is>
+          <t>179592701</t>
+        </is>
+      </c>
+      <c r="Z619" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA619" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:30:22</t>
+        </is>
+      </c>
+      <c r="AB619" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:53:09</t>
+        </is>
+      </c>
+      <c r="AC619" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:53:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>marveloveliz89@gmail.com</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>948969899</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Marcelo</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Remigio</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V620">
+        <v>1</v>
+      </c>
+      <c r="W620" t="inlineStr">
+        <is>
+          <t>0376-17</t>
+        </is>
+      </c>
+      <c r="X620" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y620" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z620" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA620" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:31:25</t>
+        </is>
+      </c>
+      <c r="AB620" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:59:23</t>
+        </is>
+      </c>
+      <c r="AC620" t="inlineStr">
+        <is>
+          <t>2026-05-03 10:59:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>cristina_barria27@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Cristina</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>Cerro navia</t>
+        </is>
+      </c>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V621">
+        <v>1</v>
+      </c>
+      <c r="W621" t="inlineStr">
+        <is>
+          <t>0376-18</t>
+        </is>
+      </c>
+      <c r="X621" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y621" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z621" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA621" t="inlineStr">
+        <is>
+          <t>2026-05-03 11:29:04</t>
+        </is>
+      </c>
+      <c r="AB621" t="inlineStr">
+        <is>
+          <t>2026-05-03 11:57:14</t>
+        </is>
+      </c>
+      <c r="AC621" t="inlineStr">
+        <is>
+          <t>2026-05-03 11:57:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>alicia.venegas2013@gmail.com</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>933716046</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Alicia Venegas</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Rodrigo Morales</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Julián Morales</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>Catalina Morales</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Monserrat Morales</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V622">
+        <v>2</v>
+      </c>
+      <c r="W622" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X622" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y622" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z622" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA622" t="inlineStr">
+        <is>
+          <t>2026-05-03 12:17:09</t>
+        </is>
+      </c>
+      <c r="AB622" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:37:03</t>
+        </is>
+      </c>
+      <c r="AC622" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:37:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>somogu.morales@gmail.com</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>983754591</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Negmi</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V623">
+        <v>1</v>
+      </c>
+      <c r="W623" t="inlineStr">
+        <is>
+          <t>9270-10</t>
+        </is>
+      </c>
+      <c r="X623" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y623" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z623" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA623" t="inlineStr">
+        <is>
+          <t>2026-05-03 12:27:32</t>
+        </is>
+      </c>
+      <c r="AB623" t="inlineStr">
+        <is>
+          <t>2026-05-03 12:46:33</t>
+        </is>
+      </c>
+      <c r="AC623" t="inlineStr">
+        <is>
+          <t>2026-05-03 12:46:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>fidel.luna.n@gmail.com</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>978651220</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Fidel</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>San bernardo</t>
+        </is>
+      </c>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V624">
+        <v>1</v>
+      </c>
+      <c r="W624" t="inlineStr">
+        <is>
+          <t>0376-19</t>
+        </is>
+      </c>
+      <c r="X624" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y624" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="Z624" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA624" t="inlineStr">
+        <is>
+          <t>2026-05-03 13:34:10</t>
+        </is>
+      </c>
+      <c r="AB624" t="inlineStr">
+        <is>
+          <t>2026-05-03 14:00:01</t>
+        </is>
+      </c>
+      <c r="AC624" t="inlineStr">
+        <is>
+          <t>2026-05-03 14:00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>sebastianaviles26@gmail.com</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>952289083</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>Adolfo</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V625">
+        <v>2</v>
+      </c>
+      <c r="W625" t="inlineStr">
+        <is>
+          <t>9270-10</t>
+        </is>
+      </c>
+      <c r="X625" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y625" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z625" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA625" t="inlineStr">
+        <is>
+          <t>2026-05-03 16:17:46</t>
+        </is>
+      </c>
+      <c r="AB625" t="inlineStr">
+        <is>
+          <t>2026-05-03 16:43:22</t>
+        </is>
+      </c>
+      <c r="AC625" t="inlineStr">
+        <is>
+          <t>2026-05-03 16:43:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>dorellanae@outlook.cl</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>986857731</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V626">
+        <v>1</v>
+      </c>
+      <c r="W626" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X626" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y626" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z626" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA626" t="inlineStr">
+        <is>
+          <t>2026-05-03 17:02:02</t>
+        </is>
+      </c>
+      <c r="AB626" t="inlineStr">
+        <is>
+          <t>2026-05-03 17:30:14</t>
+        </is>
+      </c>
+      <c r="AC626" t="inlineStr">
+        <is>
+          <t>2026-05-03 17:30:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>gisellesymmes@gmail.com</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>99685538</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Geselles</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>Deivis</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr">
+        <is>
+          <t>Cerro navia</t>
+        </is>
+      </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V627">
+        <v>1</v>
+      </c>
+      <c r="W627" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X627" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y627" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z627" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA627" t="inlineStr">
+        <is>
+          <t>2026-05-03 17:30:39</t>
+        </is>
+      </c>
+      <c r="AB627" t="inlineStr">
+        <is>
+          <t>2026-05-03 18:04:27</t>
+        </is>
+      </c>
+      <c r="AC627" t="inlineStr">
+        <is>
+          <t>2026-05-03 18:04:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>beatrizvenegas1996@icloud.com</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>959234254</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Beatriz</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Marisol</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S628" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V628">
+        <v>1</v>
+      </c>
+      <c r="W628" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X628" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y628" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Z628" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA628" t="inlineStr">
+        <is>
+          <t>2026-05-03 17:38:22</t>
+        </is>
+      </c>
+      <c r="AB628" t="inlineStr">
+        <is>
+          <t>2026-05-03 18:13:25</t>
+        </is>
+      </c>
+      <c r="AC628" t="inlineStr">
+        <is>
+          <t>2026-05-03 18:13:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>elischwarz@gmail.com</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Issac</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S629" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V629">
+        <v>2</v>
+      </c>
+      <c r="W629" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X629" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y629" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z629" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA629" t="inlineStr">
+        <is>
+          <t>2026-05-03 18:05:41</t>
+        </is>
+      </c>
+      <c r="AB629" t="inlineStr">
+        <is>
+          <t>2026-05-03 18:51:27</t>
+        </is>
+      </c>
+      <c r="AC629" t="inlineStr">
+        <is>
+          <t>2026-05-03 18:51:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>maximoandres26@gmail.com</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>982013274</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Paloma</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S630" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T630" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V630">
+        <v>2</v>
+      </c>
+      <c r="W630" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X630" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y630" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Z630" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA630" t="inlineStr">
+        <is>
+          <t>2026-05-03 18:24:44</t>
+        </is>
+      </c>
+      <c r="AB630" t="inlineStr">
+        <is>
+          <t>2026-05-03 19:06:25</t>
+        </is>
+      </c>
+      <c r="AC630" t="inlineStr">
+        <is>
+          <t>2026-05-03 19:06:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>monica.hernandez.hernandez.95@gmail.com</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>975368707</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S631" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T631" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V631">
+        <v>1</v>
+      </c>
+      <c r="W631" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X631" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y631" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Z631" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA631" t="inlineStr">
+        <is>
+          <t>2026-05-03 19:14:49</t>
+        </is>
+      </c>
+      <c r="AB631" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:11:02</t>
+        </is>
+      </c>
+      <c r="AC631" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>xi.alvarado.cid@gmail.com</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>98818942</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Ximena</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S632" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T632" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V632">
+        <v>1</v>
+      </c>
+      <c r="W632" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X632" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y632" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z632" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA632" t="inlineStr">
+        <is>
+          <t>2026-05-03 19:17:09</t>
+        </is>
+      </c>
+      <c r="AB632" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:03:14</t>
+        </is>
+      </c>
+      <c r="AC632" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:03:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>nancyfierro@utr.net</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>9999999</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S633" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="T633" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V633">
+        <v>1</v>
+      </c>
+      <c r="W633" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X633" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y633" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="Z633" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA633" t="inlineStr">
+        <is>
+          <t>2026-05-03 19:20:17</t>
+        </is>
+      </c>
+      <c r="AB633" t="inlineStr">
+        <is>
+          <t>2026-05-03 19:44:43</t>
+        </is>
+      </c>
+      <c r="AC633" t="inlineStr">
+        <is>
+          <t>2026-05-03 19:44:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>green_lovebillie@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>999015014</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>José Luis</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Aynara</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>Amaya</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S634" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="T634" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U634" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V634">
+        <v>2</v>
+      </c>
+      <c r="W634" t="inlineStr">
+        <is>
+          <t>9270-11</t>
+        </is>
+      </c>
+      <c r="X634" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y634" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z634" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA634" t="inlineStr">
+        <is>
+          <t>2026-05-03 19:50:06</t>
+        </is>
+      </c>
+      <c r="AB634" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:22:33</t>
+        </is>
+      </c>
+      <c r="AC634" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:22:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>ivantrujiloni@gmail.com</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>963093238ñ</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Renato</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S635" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T635" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V635">
+        <v>1</v>
+      </c>
+      <c r="W635" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="X635" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y635" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="Z635" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA635" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:14:11</t>
+        </is>
+      </c>
+      <c r="AB635" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:48:41</t>
+        </is>
+      </c>
+      <c r="AC635" t="inlineStr">
+        <is>
+          <t>2026-05-03 20:48:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>pelipelepin@gmail.com</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>995282874</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Ignacia</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S636" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="T636" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V636">
+        <v>1</v>
+      </c>
+      <c r="W636" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X636" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y636" t="inlineStr">
+        <is>
+          <t>19.313.240-5</t>
+        </is>
+      </c>
+      <c r="Z636" s="2">
+        <v>46145</v>
+      </c>
+      <c r="AA636" t="inlineStr">
+        <is>
+          <t>2026-05-03 22:37:06</t>
+        </is>
+      </c>
+      <c r="AB636" t="inlineStr">
+        <is>
+          <t>2026-05-03 23:05:32</t>
+        </is>
+      </c>
+      <c r="AC636" t="inlineStr">
+        <is>
+          <t>2026-05-03 23:05:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>vassallg@gmail.com</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>93625 5545</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S637" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T637" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V637">
+        <v>2</v>
+      </c>
+      <c r="W637" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X637" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y637" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="Z637" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA637" t="inlineStr">
+        <is>
+          <t>2026-05-04 09:25:36</t>
+        </is>
+      </c>
+      <c r="AB637" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:30:11</t>
+        </is>
+      </c>
+      <c r="AC637" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:30:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>eduacu0818@gmail.com</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>961821304</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Georgina</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S638" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="T638" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V638">
+        <v>1</v>
+      </c>
+      <c r="W638" t="inlineStr">
+        <is>
+          <t>9270-12</t>
+        </is>
+      </c>
+      <c r="X638" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y638" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z638" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA638" t="inlineStr">
+        <is>
+          <t>2026-05-04 12:38:50</t>
+        </is>
+      </c>
+      <c r="AB638" t="inlineStr">
+        <is>
+          <t>2026-05-04 13:15:56</t>
+        </is>
+      </c>
+      <c r="AC638" t="inlineStr">
+        <is>
+          <t>2026-05-04 13:15:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>yesicapep1983@gmail.com</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>954218851</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Yessica</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>Sayen</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V639">
+        <v>1</v>
+      </c>
+      <c r="W639" t="inlineStr">
+        <is>
+          <t>9270-12</t>
+        </is>
+      </c>
+      <c r="X639" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y639" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z639" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA639" t="inlineStr">
+        <is>
+          <t>2026-05-04 13:40:10</t>
+        </is>
+      </c>
+      <c r="AB639" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:16:15</t>
+        </is>
+      </c>
+      <c r="AC639" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>luisbaezfigueroa@gmail.com</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>937871604</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Baltazar</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>Peñalolen</t>
+        </is>
+      </c>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V640">
+        <v>1</v>
+      </c>
+      <c r="W640" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="X640" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y640" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="Z640" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA640" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:50:18</t>
+        </is>
+      </c>
+      <c r="AB640" t="inlineStr">
+        <is>
+          <t>2026-05-04 15:41:05</t>
+        </is>
+      </c>
+      <c r="AC640" t="inlineStr">
+        <is>
+          <t>2026-05-04 15:41:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>javierasanchezarenas@gmail.com</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>936812663</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Jesus</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Luciano</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S641" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="T641" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V641">
+        <v>1</v>
+      </c>
+      <c r="W641" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="X641" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y641" t="inlineStr">
+        <is>
+          <t>13081719-K</t>
+        </is>
+      </c>
+      <c r="Z641" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA641" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:50:45</t>
+        </is>
+      </c>
+      <c r="AB641" t="inlineStr">
+        <is>
+          <t>2026-05-04 15:50:01</t>
+        </is>
+      </c>
+      <c r="AC641" t="inlineStr">
+        <is>
+          <t>2026-05-04 15:50:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>fsilva@cconace.cl</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>963494269</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Simona</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="T642" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V642">
+        <v>1</v>
+      </c>
+      <c r="W642" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="X642" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y642" t="inlineStr">
+        <is>
+          <t>14155088-8</t>
+        </is>
+      </c>
+      <c r="Z642" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA642" t="inlineStr">
+        <is>
+          <t>2026-05-04 15:59:34</t>
+        </is>
+      </c>
+      <c r="AB642" t="inlineStr">
+        <is>
+          <t>2026-05-04 16:35:23</t>
+        </is>
+      </c>
+      <c r="AC642" t="inlineStr">
+        <is>
+          <t>2026-05-04 16:35:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>catalivaldes@gmail.com</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>965714935</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Catalina Valdés Jara</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Manuel Rodríguez</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Facundo Rodriguez Valdés</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S643" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T643" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U643" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V643">
+        <v>1</v>
+      </c>
+      <c r="W643" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X643" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y643" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z643" s="2">
+        <v>-254814</v>
+      </c>
+      <c r="AA643" t="inlineStr">
+        <is>
+          <t>2026-05-04 17:09:28</t>
+        </is>
+      </c>
+      <c r="AB643" t="inlineStr">
+        <is>
+          <t>2026-05-04 17:57:08</t>
+        </is>
+      </c>
+      <c r="AC643" t="inlineStr">
+        <is>
+          <t>2026-05-04 17:57:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>cgonzalwzcort@gmaim.com</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>963569346</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Loreto</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>Cristobal</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S644" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="T644" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V644">
+        <v>1</v>
+      </c>
+      <c r="W644" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="X644" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y644" t="inlineStr">
+        <is>
+          <t>14155088-8</t>
+        </is>
+      </c>
+      <c r="Z644" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA644" t="inlineStr">
+        <is>
+          <t>2026-05-04 17:16:01</t>
+        </is>
+      </c>
+      <c r="AB644" t="inlineStr">
+        <is>
+          <t>2026-05-04 18:12:32</t>
+        </is>
+      </c>
+      <c r="AC644" t="inlineStr">
+        <is>
+          <t>2026-05-04 18:12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>jannytellezortiz317@gmail.com</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>952345189</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Stefania</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>Agatha</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T645" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V645">
+        <v>1</v>
+      </c>
+      <c r="W645" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="X645" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y645" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="Z645" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA645" t="inlineStr">
+        <is>
+          <t>2026-05-04 18:26:43</t>
+        </is>
+      </c>
+      <c r="AB645" t="inlineStr">
+        <is>
+          <t>2026-05-04 19:29:39</t>
+        </is>
+      </c>
+      <c r="AC645" t="inlineStr">
+        <is>
+          <t>2026-05-04 19:29:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>heribertomanrriquez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>933625491</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Heriberto</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Esposa</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Hijastra</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="T646" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V646">
+        <v>1</v>
+      </c>
+      <c r="W646" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="X646" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y646" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="Z646" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA646" t="inlineStr">
+        <is>
+          <t>2026-05-04 19:48:48</t>
+        </is>
+      </c>
+      <c r="AB646" t="inlineStr">
+        <is>
+          <t>2026-05-04 20:48:11</t>
+        </is>
+      </c>
+      <c r="AC646" t="inlineStr">
+        <is>
+          <t>2026-05-04 20:48:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>richar.nuevotj@gmail.com</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>940062159</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Denisse</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Danisa</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V647">
+        <v>1</v>
+      </c>
+      <c r="W647" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="X647" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y647" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="Z647" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA647" t="inlineStr">
+        <is>
+          <t>2026-05-04 21:00:02</t>
+        </is>
+      </c>
+      <c r="AB647" t="inlineStr">
+        <is>
+          <t>2026-05-04 21:51:50</t>
+        </is>
+      </c>
+      <c r="AC647" t="inlineStr">
+        <is>
+          <t>2026-05-04 21:51:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>iacm.cl@gmail.com</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>997127020</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Isabel canales martinez</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Emiliana Gutiérrez canales</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S648" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T648" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V648">
+        <v>1</v>
+      </c>
+      <c r="W648" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X648" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y648" t="inlineStr">
+        <is>
+          <t>13285715-6</t>
+        </is>
+      </c>
+      <c r="Z648" s="2">
+        <v>46146</v>
+      </c>
+      <c r="AA648" t="inlineStr">
+        <is>
+          <t>2026-05-05 07:58:21</t>
+        </is>
+      </c>
+      <c r="AB648" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:12:18</t>
+        </is>
+      </c>
+      <c r="AC648" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:12:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>nicolas.soto.soto@outlook.com</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>965668134</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Nicolas Soto</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Emily Soto Pradenas</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S649" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T649" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V649">
+        <v>1</v>
+      </c>
+      <c r="W649" t="inlineStr">
+        <is>
+          <t>0367</t>
+        </is>
+      </c>
+      <c r="X649" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y649" t="inlineStr">
+        <is>
+          <t>20241036-7</t>
+        </is>
+      </c>
+      <c r="Z649" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA649" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:31:58</t>
+        </is>
+      </c>
+      <c r="AB649" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:19:53</t>
+        </is>
+      </c>
+      <c r="AC649" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:19:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>fvenegas1512@gmail.com</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>56987737635</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S650" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="T650" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V650">
+        <v>2</v>
+      </c>
+      <c r="W650" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="X650" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y650" t="inlineStr">
+        <is>
+          <t>19172396-1</t>
+        </is>
+      </c>
+      <c r="Z650" s="2">
+        <v>45658</v>
+      </c>
+      <c r="AA650" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:43:31</t>
+        </is>
+      </c>
+      <c r="AB650" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:13:07</t>
+        </is>
+      </c>
+      <c r="AC650" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:13:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>vergararojash@gmail.com</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>931124228</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>Anibal</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S651" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T651" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V651">
+        <v>2</v>
+      </c>
+      <c r="W651" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X651" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y651" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="Z651" s="2">
+        <v>45292</v>
+      </c>
+      <c r="AA651" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:51:12</t>
+        </is>
+      </c>
+      <c r="AB651" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:19:27</t>
+        </is>
+      </c>
+      <c r="AC651" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:19:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC651"/>
+  <dimension ref="A1:AC676"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -66745,12 +66745,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>jannytellezortiz317@gmail.com</t>
+          <t>ineliadelcarmenjj@gmail.com</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>952345189</t>
+          <t>976570566</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -66760,7 +66760,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Alejandra</t>
+          <t>Inelia Jorquera Jorquera</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
@@ -66770,7 +66770,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Andres Lopez</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -66778,26 +66778,6 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="H645" t="inlineStr">
-        <is>
-          <t>Stefania</t>
-        </is>
-      </c>
-      <c r="I645" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="J645" t="inlineStr">
-        <is>
-          <t>Agatha</t>
-        </is>
-      </c>
-      <c r="K645" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
       <c r="R645" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -66805,7 +66785,7 @@
       </c>
       <c r="S645" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="T645" t="inlineStr">
@@ -66823,7 +66803,7 @@
       </c>
       <c r="W645" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="X645" t="inlineStr">
@@ -66833,37 +66813,37 @@
       </c>
       <c r="Y645" t="inlineStr">
         <is>
-          <t>105033206</t>
+          <t>205682856</t>
         </is>
       </c>
       <c r="Z645" s="2">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="AA645" t="inlineStr">
         <is>
-          <t>2026-05-04 18:26:43</t>
+          <t>2026-05-04 18:24:42</t>
         </is>
       </c>
       <c r="AB645" t="inlineStr">
         <is>
-          <t>2026-05-04 19:29:39</t>
+          <t>2026-05-05 12:31:42</t>
         </is>
       </c>
       <c r="AC645" t="inlineStr">
         <is>
-          <t>2026-05-04 19:29:36</t>
+          <t>2026-05-05 12:31:42</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>heribertomanrriquez@gmail.com</t>
+          <t>jannytellezortiz317@gmail.com</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>933625491</t>
+          <t>952345189</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -66873,27 +66853,27 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Heriberto</t>
+          <t>Alejandra</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Esposa</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Hijastra</t>
+          <t>Stefania</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -66903,7 +66883,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>Hija</t>
+          <t>Agatha</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
@@ -66918,12 +66898,12 @@
       </c>
       <c r="S646" t="inlineStr">
         <is>
-          <t>Valparaiso</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="T646" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U646" t="inlineStr">
@@ -66954,29 +66934,29 @@
       </c>
       <c r="AA646" t="inlineStr">
         <is>
-          <t>2026-05-04 19:48:48</t>
+          <t>2026-05-04 18:26:43</t>
         </is>
       </c>
       <c r="AB646" t="inlineStr">
         <is>
-          <t>2026-05-04 20:48:11</t>
+          <t>2026-05-04 19:29:39</t>
         </is>
       </c>
       <c r="AC646" t="inlineStr">
         <is>
-          <t>2026-05-04 20:48:11</t>
+          <t>2026-05-04 19:29:36</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>richar.nuevotj@gmail.com</t>
+          <t>heribertomanrriquez@gmail.com</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>940062159</t>
+          <t>933625491</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -66986,7 +66966,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Heriberto</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -66996,7 +66976,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Denisse</t>
+          <t>Esposa</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -67006,7 +66986,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Danisa</t>
+          <t>Hijastra</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -67014,19 +66994,29 @@
           <t>Mujer</t>
         </is>
       </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R647" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="S647" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="T647" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U647" t="inlineStr">
@@ -67039,17 +67029,17 @@
       </c>
       <c r="W647" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="X647" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y647" t="inlineStr">
         <is>
-          <t>105318464</t>
+          <t>105033206</t>
         </is>
       </c>
       <c r="Z647" s="2">
@@ -67057,29 +67047,29 @@
       </c>
       <c r="AA647" t="inlineStr">
         <is>
-          <t>2026-05-04 21:00:02</t>
+          <t>2026-05-04 19:48:48</t>
         </is>
       </c>
       <c r="AB647" t="inlineStr">
         <is>
-          <t>2026-05-04 21:51:50</t>
+          <t>2026-05-04 20:48:11</t>
         </is>
       </c>
       <c r="AC647" t="inlineStr">
         <is>
-          <t>2026-05-04 21:51:50</t>
+          <t>2026-05-04 20:48:11</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>iacm.cl@gmail.com</t>
+          <t>richar.nuevotj@gmail.com</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>997127020</t>
+          <t>940062159</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -67089,17 +67079,17 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Isabel canales martinez</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Emiliana Gutiérrez canales</t>
+          <t>Denisse</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -67107,6 +67097,16 @@
           <t>Mujer</t>
         </is>
       </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Danisa</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R648" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -67124,7 +67124,7 @@
       </c>
       <c r="U648" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V648">
@@ -67132,17 +67132,17 @@
       </c>
       <c r="W648" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="X648" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y648" t="inlineStr">
         <is>
-          <t>13285715-6</t>
+          <t>105318464</t>
         </is>
       </c>
       <c r="Z648" s="2">
@@ -67150,29 +67150,29 @@
       </c>
       <c r="AA648" t="inlineStr">
         <is>
-          <t>2026-05-05 07:58:21</t>
+          <t>2026-05-04 21:00:02</t>
         </is>
       </c>
       <c r="AB648" t="inlineStr">
         <is>
-          <t>2026-05-05 09:12:18</t>
+          <t>2026-05-04 21:51:50</t>
         </is>
       </c>
       <c r="AC648" t="inlineStr">
         <is>
-          <t>2026-05-05 09:12:18</t>
+          <t>2026-05-04 21:51:50</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>nicolas.soto.soto@outlook.com</t>
+          <t>iacm.cl@gmail.com</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>965668134</t>
+          <t>997127020</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -67182,17 +67182,17 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Nicolas Soto</t>
+          <t>Isabel canales martinez</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Emily Soto Pradenas</t>
+          <t>Emiliana Gutiérrez canales</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -67202,22 +67202,22 @@
       </c>
       <c r="R649" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S649" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="T649" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U649" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V649">
@@ -67225,7 +67225,7 @@
       </c>
       <c r="W649" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>19</t>
         </is>
       </c>
       <c r="X649" t="inlineStr">
@@ -67235,37 +67235,37 @@
       </c>
       <c r="Y649" t="inlineStr">
         <is>
-          <t>20241036-7</t>
+          <t>13285715-6</t>
         </is>
       </c>
       <c r="Z649" s="2">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="AA649" t="inlineStr">
         <is>
-          <t>2026-05-05 11:31:58</t>
+          <t>2026-05-05 07:58:21</t>
         </is>
       </c>
       <c r="AB649" t="inlineStr">
         <is>
-          <t>2026-05-05 12:19:53</t>
+          <t>2026-05-05 09:12:18</t>
         </is>
       </c>
       <c r="AC649" t="inlineStr">
         <is>
-          <t>2026-05-05 12:19:53</t>
+          <t>2026-05-05 09:12:18</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>fvenegas1512@gmail.com</t>
+          <t>nicolas.soto.soto@outlook.com</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>56987737635</t>
+          <t>965668134</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -67275,7 +67275,7 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Franco</t>
+          <t>Nicolas Soto</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
@@ -67285,7 +67285,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Alejandra</t>
+          <t>Emily Soto Pradenas</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -67293,34 +67293,14 @@
           <t>Mujer</t>
         </is>
       </c>
-      <c r="H650" t="inlineStr">
-        <is>
-          <t>Sergio</t>
-        </is>
-      </c>
-      <c r="I650" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="J650" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="K650" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
       <c r="R650" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="S650" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="T650" t="inlineStr">
@@ -67334,11 +67314,11 @@
         </is>
       </c>
       <c r="V650">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W650" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="X650" t="inlineStr">
@@ -67348,37 +67328,37 @@
       </c>
       <c r="Y650" t="inlineStr">
         <is>
-          <t>19172396-1</t>
+          <t>20241036-7</t>
         </is>
       </c>
       <c r="Z650" s="2">
-        <v>45658</v>
+        <v>46147</v>
       </c>
       <c r="AA650" t="inlineStr">
         <is>
-          <t>2026-05-05 11:43:31</t>
+          <t>2026-05-05 11:31:58</t>
         </is>
       </c>
       <c r="AB650" t="inlineStr">
         <is>
-          <t>2026-05-05 12:13:07</t>
+          <t>2026-05-05 12:19:53</t>
         </is>
       </c>
       <c r="AC650" t="inlineStr">
         <is>
-          <t>2026-05-05 12:13:07</t>
+          <t>2026-05-05 12:19:53</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>vergararojash@gmail.com</t>
+          <t>fvenegas1512@gmail.com</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>931124228</t>
+          <t>56987737635</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -67388,37 +67368,37 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Franco</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Hector</t>
+          <t>Alejandra</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Sergio</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>Anibal</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -67433,12 +67413,12 @@
       </c>
       <c r="S651" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="T651" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U651" t="inlineStr">
@@ -67451,35 +67431,2700 @@
       </c>
       <c r="W651" t="inlineStr">
         <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="X651" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y651" t="inlineStr">
+        <is>
+          <t>19172396-1</t>
+        </is>
+      </c>
+      <c r="Z651" s="2">
+        <v>45658</v>
+      </c>
+      <c r="AA651" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:43:31</t>
+        </is>
+      </c>
+      <c r="AB651" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:13:07</t>
+        </is>
+      </c>
+      <c r="AC651" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:13:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>vergararojash@gmail.com</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>931124228</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>Anibal</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T652" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V652">
+        <v>2</v>
+      </c>
+      <c r="W652" t="inlineStr">
+        <is>
           <t>897</t>
         </is>
       </c>
-      <c r="X651" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>Empresa con sello 40 horas</t>
         </is>
       </c>
-      <c r="Y651" t="inlineStr">
+      <c r="Y652" t="inlineStr">
         <is>
           <t>175458975</t>
         </is>
       </c>
-      <c r="Z651" s="2">
+      <c r="Z652" s="2">
         <v>45292</v>
       </c>
-      <c r="AA651" t="inlineStr">
+      <c r="AA652" t="inlineStr">
         <is>
           <t>2026-05-05 11:51:12</t>
         </is>
       </c>
-      <c r="AB651" t="inlineStr">
+      <c r="AB652" t="inlineStr">
         <is>
           <t>2026-05-05 12:19:27</t>
         </is>
       </c>
-      <c r="AC651" t="inlineStr">
+      <c r="AC652" t="inlineStr">
         <is>
           <t>2026-05-05 12:19:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>gmobenavides10@gmail.com</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>957469697</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Mabel</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>Patrcio</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R653" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S653" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="T653" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V653">
+        <v>1</v>
+      </c>
+      <c r="W653" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="X653" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y653" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="Z653" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA653" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:04:14</t>
+        </is>
+      </c>
+      <c r="AB653" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:50:58</t>
+        </is>
+      </c>
+      <c r="AC653" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:50:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>mceciliabarrientos@gmail.com</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>991780315</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>María Cecilia</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr">
+        <is>
+          <t>La reina</t>
+        </is>
+      </c>
+      <c r="T654" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V654">
+        <v>1</v>
+      </c>
+      <c r="W654" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="X654" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y654" t="inlineStr">
+        <is>
+          <t>213099035</t>
+        </is>
+      </c>
+      <c r="Z654" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA654" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:06:06</t>
+        </is>
+      </c>
+      <c r="AB654" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:47:04</t>
+        </is>
+      </c>
+      <c r="AC654" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:47:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>kathi@live.cl</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>95729 7667</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S655" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T655" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V655">
+        <v>1</v>
+      </c>
+      <c r="W655" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X655" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y655" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z655" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA655" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:32:25</t>
+        </is>
+      </c>
+      <c r="AB655" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:11:15</t>
+        </is>
+      </c>
+      <c r="AC655" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>sarybb83@gmail.com</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>977339289</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Sara Alvear</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Diego Plaza</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Catalina Plaza</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>Pedro Plaza</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S656" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T656" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V656">
+        <v>1</v>
+      </c>
+      <c r="W656" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="X656" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y656" t="inlineStr">
+        <is>
+          <t>20568285-6</t>
+        </is>
+      </c>
+      <c r="Z656" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA656" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:33:35</t>
+        </is>
+      </c>
+      <c r="AB656" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:11:24</t>
+        </is>
+      </c>
+      <c r="AC656" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:11:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>camilita1603@gmail.com</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>949034499</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Bastian</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S657" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="T657" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U657" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V657">
+        <v>2</v>
+      </c>
+      <c r="W657" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="X657" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y657" t="inlineStr">
+        <is>
+          <t>213099035</t>
+        </is>
+      </c>
+      <c r="Z657" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA657" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:05:36</t>
+        </is>
+      </c>
+      <c r="AB657" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:37:26</t>
+        </is>
+      </c>
+      <c r="AC657" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:37:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>sebastianlovayen@outlook.com</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>933533329</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Sebastian Alund</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Fabiana Cantilo</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S658" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T658" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V658">
+        <v>1</v>
+      </c>
+      <c r="W658" t="inlineStr">
+        <is>
+          <t>0367</t>
+        </is>
+      </c>
+      <c r="X658" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y658" t="inlineStr">
+        <is>
+          <t>202410367</t>
+        </is>
+      </c>
+      <c r="Z658" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA658" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:51:20</t>
+        </is>
+      </c>
+      <c r="AB658" t="inlineStr">
+        <is>
+          <t>2026-05-05 17:55:22</t>
+        </is>
+      </c>
+      <c r="AC658" t="inlineStr">
+        <is>
+          <t>2026-05-05 17:55:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>darlingrebolledo827@gmail.com</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>930872103</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>La cisterna</t>
+        </is>
+      </c>
+      <c r="T659" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V659">
+        <v>1</v>
+      </c>
+      <c r="W659" t="inlineStr">
+        <is>
+          <t>9270-3</t>
+        </is>
+      </c>
+      <c r="X659" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y659" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z659" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA659" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:56:39</t>
+        </is>
+      </c>
+      <c r="AB659" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:23:47</t>
+        </is>
+      </c>
+      <c r="AC659" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:23:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Aylinrojas337@gmail.com</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>958716914</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Aylin</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T660" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V660">
+        <v>2</v>
+      </c>
+      <c r="W660" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X660" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y660" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z660" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA660" t="inlineStr">
+        <is>
+          <t>2026-05-05 15:24:53</t>
+        </is>
+      </c>
+      <c r="AB660" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:42:35</t>
+        </is>
+      </c>
+      <c r="AC660" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:42:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>mmejias1973@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S661" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T661" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U661" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V661">
+        <v>2</v>
+      </c>
+      <c r="W661" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="X661" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y661" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="Z661" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA661" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:48:02</t>
+        </is>
+      </c>
+      <c r="AB661" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:46:01</t>
+        </is>
+      </c>
+      <c r="AC661" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:46:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>carina1616.1987@gmail.com</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>982130913</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Carina</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Maximiliano</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Fabricio</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S662" t="inlineStr">
+        <is>
+          <t>La pintana</t>
+        </is>
+      </c>
+      <c r="T662" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V662">
+        <v>2</v>
+      </c>
+      <c r="W662" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="X662" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y662" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="Z662" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA662" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:31:06</t>
+        </is>
+      </c>
+      <c r="AB662" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:14:52</t>
+        </is>
+      </c>
+      <c r="AC662" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>antosanchezas841@gmail.com</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Antonia</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S663" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V663">
+        <v>1</v>
+      </c>
+      <c r="W663" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X663" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y663" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z663" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA663" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:53:17</t>
+        </is>
+      </c>
+      <c r="AB663" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:07:22</t>
+        </is>
+      </c>
+      <c r="AC663" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:07:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>felipearturo@inacapmail.com</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Hirina</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S664" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="T664" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V664">
+        <v>1</v>
+      </c>
+      <c r="W664" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X664" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y664" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z664" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA664" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:10:24</t>
+        </is>
+      </c>
+      <c r="AB664" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:28:44</t>
+        </is>
+      </c>
+      <c r="AC664" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:28:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>jeanette.olmedo77@gmail.com</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>985093029</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Jeanette</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Dania</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V665">
+        <v>1</v>
+      </c>
+      <c r="W665" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X665" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y665" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="Z665" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA665" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:41:30</t>
+        </is>
+      </c>
+      <c r="AB665" t="inlineStr">
+        <is>
+          <t>2026-05-05 20:28:46</t>
+        </is>
+      </c>
+      <c r="AC665" t="inlineStr">
+        <is>
+          <t>2026-05-05 20:28:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>camilagutiwerezfaundez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>981782193</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Camila Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Ángel Gutiérrez</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Sandra Faúndez</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>Alejandra Gutiérrez</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="T666" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V666">
+        <v>1</v>
+      </c>
+      <c r="W666" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X666" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y666" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z666" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA666" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:44:31</t>
+        </is>
+      </c>
+      <c r="AB666" t="inlineStr">
+        <is>
+          <t>2026-05-05 20:18:47</t>
+        </is>
+      </c>
+      <c r="AC666" t="inlineStr">
+        <is>
+          <t>2026-05-05 20:18:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>romi.barbagelata@gmail.com</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>995902817</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V667">
+        <v>1</v>
+      </c>
+      <c r="W667" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="X667" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y667" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="Z667" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA667" t="inlineStr">
+        <is>
+          <t>2026-05-05 20:16:39</t>
+        </is>
+      </c>
+      <c r="AB667" t="inlineStr">
+        <is>
+          <t>2026-05-05 20:53:53</t>
+        </is>
+      </c>
+      <c r="AC667" t="inlineStr">
+        <is>
+          <t>2026-05-05 20:53:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>alexanderbenavidesals@gmail.com</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>978850325</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V668">
+        <v>1</v>
+      </c>
+      <c r="W668" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="X668" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y668" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="Z668" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA668" t="inlineStr">
+        <is>
+          <t>2026-05-05 20:50:51</t>
+        </is>
+      </c>
+      <c r="AB668" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:21:26</t>
+        </is>
+      </c>
+      <c r="AC668" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:21:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>margaritaduranc16@gmail.com</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>974476355</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Margarita</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Juan carlos</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Guadalupa</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V669">
+        <v>1</v>
+      </c>
+      <c r="W669" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X669" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y669" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="Z669" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA669" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:05:26</t>
+        </is>
+      </c>
+      <c r="AB669" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:44:40</t>
+        </is>
+      </c>
+      <c r="AC669" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>paulaza@live.cl</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>988562258</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Noelia</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Belen</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V670">
+        <v>2</v>
+      </c>
+      <c r="W670" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X670" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y670" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z670" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA670" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:06:57</t>
+        </is>
+      </c>
+      <c r="AB670" t="inlineStr">
+        <is>
+          <t>2026-05-05 22:18:09</t>
+        </is>
+      </c>
+      <c r="AC670" t="inlineStr">
+        <is>
+          <t>2026-05-05 22:18:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>fernanda.anai.mora@gmail.com</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>998920888</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Marjorie</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>anai</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>lo prado</t>
+        </is>
+      </c>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V671">
+        <v>1</v>
+      </c>
+      <c r="W671" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="X671" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y671" t="inlineStr">
+        <is>
+          <t>10102181-5</t>
+        </is>
+      </c>
+      <c r="Z671" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA671" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:34:25</t>
+        </is>
+      </c>
+      <c r="AB671" t="inlineStr">
+        <is>
+          <t>2026-05-05 22:37:24</t>
+        </is>
+      </c>
+      <c r="AC671" t="inlineStr">
+        <is>
+          <t>2026-05-05 22:37:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>euevelopez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>964946167</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Hernan</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Matilde</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>HUECHURABA</t>
+        </is>
+      </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V672">
+        <v>2</v>
+      </c>
+      <c r="W672" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="X672" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y672" t="inlineStr">
+        <is>
+          <t>17286752-9</t>
+        </is>
+      </c>
+      <c r="Z672" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA672" t="inlineStr">
+        <is>
+          <t>2026-05-05 21:52:52</t>
+        </is>
+      </c>
+      <c r="AB672" t="inlineStr">
+        <is>
+          <t>2026-05-05 22:39:46</t>
+        </is>
+      </c>
+      <c r="AC672" t="inlineStr">
+        <is>
+          <t>2026-05-05 22:39:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>mmejias1973@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V673">
+        <v>1</v>
+      </c>
+      <c r="W673" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="X673" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y673" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="Z673" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA673" t="inlineStr">
+        <is>
+          <t>2026-05-05 22:49:00</t>
+        </is>
+      </c>
+      <c r="AB673" t="inlineStr">
+        <is>
+          <t>2026-05-05 23:29:27</t>
+        </is>
+      </c>
+      <c r="AC673" t="inlineStr">
+        <is>
+          <t>2026-05-05 23:29:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>mmejias1973@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>978350819</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V674">
+        <v>1</v>
+      </c>
+      <c r="W674" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="X674" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y674" t="inlineStr">
+        <is>
+          <t>125238445</t>
+        </is>
+      </c>
+      <c r="Z674" s="2">
+        <v>46147</v>
+      </c>
+      <c r="AA674" t="inlineStr">
+        <is>
+          <t>2026-05-05 23:41:36</t>
+        </is>
+      </c>
+      <c r="AB674" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:06:35</t>
+        </is>
+      </c>
+      <c r="AC674" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:06:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>mariana.pasten.g@gmail.com</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>982353017</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V675">
+        <v>1</v>
+      </c>
+      <c r="W675" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="X675" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y675" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="Z675" s="2">
+        <v>46148</v>
+      </c>
+      <c r="AA675" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:52:53</t>
+        </is>
+      </c>
+      <c r="AB675" t="inlineStr">
+        <is>
+          <t>2026-05-06 10:10:34</t>
+        </is>
+      </c>
+      <c r="AC675" t="inlineStr">
+        <is>
+          <t>2026-05-06 10:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>alvarotorres.ps@gmail.com</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>56966603557</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Alvaro</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Apolonia</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V676">
+        <v>1</v>
+      </c>
+      <c r="W676" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="X676" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y676" t="inlineStr">
+        <is>
+          <t>18.050.509-1</t>
+        </is>
+      </c>
+      <c r="Z676" s="2">
+        <v>46148</v>
+      </c>
+      <c r="AA676" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:44:52</t>
+        </is>
+      </c>
+      <c r="AB676" t="inlineStr">
+        <is>
+          <t>2026-05-06 12:41:06</t>
+        </is>
+      </c>
+      <c r="AC676" t="inlineStr">
+        <is>
+          <t>2026-05-06 12:41:06</t>
         </is>
       </c>
     </row>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC676"/>
+  <dimension ref="A1:AC684"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -70128,6 +70128,800 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>gonzalezpaty.05@gmail.com</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>975272192</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V677">
+        <v>1</v>
+      </c>
+      <c r="W677" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="X677" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y677" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="Z677" s="2">
+        <v>46148</v>
+      </c>
+      <c r="AA677" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:30:42</t>
+        </is>
+      </c>
+      <c r="AB677" t="inlineStr">
+        <is>
+          <t>2026-05-06 20:06:27</t>
+        </is>
+      </c>
+      <c r="AC677" t="inlineStr">
+        <is>
+          <t>2026-05-06 20:06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Mariapaz.h@oscplus.cl</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>971402041</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>María Paz Henriquez.</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V678">
+        <v>1</v>
+      </c>
+      <c r="W678" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="X678" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y678" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="Z678" s="2">
+        <v>46148</v>
+      </c>
+      <c r="AA678" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:47:39</t>
+        </is>
+      </c>
+      <c r="AB678" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:11:06</t>
+        </is>
+      </c>
+      <c r="AC678" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>camiilapaztirapeguiflores@gmail.com</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>992701643</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Camila Tirapegui</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Juan Peña Canales</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Emily Rubio</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T679" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V679">
+        <v>1</v>
+      </c>
+      <c r="W679" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X679" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y679" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z679" s="2">
+        <v>46148</v>
+      </c>
+      <c r="AA679" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:52:23</t>
+        </is>
+      </c>
+      <c r="AB679" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:18:42</t>
+        </is>
+      </c>
+      <c r="AC679" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:18:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>dxmvera@gmail.com</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>dxmvera@gmail.com</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Diana Morales Vera</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Gabriel Poblete</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>valparaiso</t>
+        </is>
+      </c>
+      <c r="T680" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V680">
+        <v>1</v>
+      </c>
+      <c r="W680" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="X680" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y680" t="inlineStr">
+        <is>
+          <t>20568285-6</t>
+        </is>
+      </c>
+      <c r="Z680" s="2">
+        <v>46148</v>
+      </c>
+      <c r="AA680" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:28:19</t>
+        </is>
+      </c>
+      <c r="AB680" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:06:46</t>
+        </is>
+      </c>
+      <c r="AC680" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:06:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>carolina.ore.mo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>56986147685</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="T681" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V681">
+        <v>1</v>
+      </c>
+      <c r="W681" t="inlineStr">
+        <is>
+          <t>6479-01</t>
+        </is>
+      </c>
+      <c r="X681" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y681" t="inlineStr">
+        <is>
+          <t>20806479-7</t>
+        </is>
+      </c>
+      <c r="Z681" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA681" t="inlineStr">
+        <is>
+          <t>2026-05-07 09:01:05</t>
+        </is>
+      </c>
+      <c r="AB681" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:11:48</t>
+        </is>
+      </c>
+      <c r="AC681" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:11:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>francoantoniorios@gmail.com</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>920269626</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V682">
+        <v>1</v>
+      </c>
+      <c r="W682" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="X682" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y682" t="inlineStr">
+        <is>
+          <t>19172396-1</t>
+        </is>
+      </c>
+      <c r="Z682" s="2">
+        <v>45566</v>
+      </c>
+      <c r="AA682" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:02:27</t>
+        </is>
+      </c>
+      <c r="AB682" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:30:29</t>
+        </is>
+      </c>
+      <c r="AC682" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:30:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>jjjsuarez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>56989629748</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Blkys</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Yanethe</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U683" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V683">
+        <v>1</v>
+      </c>
+      <c r="W683" t="inlineStr">
+        <is>
+          <t>6479-02</t>
+        </is>
+      </c>
+      <c r="X683" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y683" t="inlineStr">
+        <is>
+          <t>20806479-7</t>
+        </is>
+      </c>
+      <c r="Z683" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA683" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:15:43</t>
+        </is>
+      </c>
+      <c r="AB683" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:40:47</t>
+        </is>
+      </c>
+      <c r="AC683" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:40:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>vale.indo20@gmail.com</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>948553351</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Valentina Indo</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Maria Paz Hermandez</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="T684" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U684" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V684">
+        <v>1</v>
+      </c>
+      <c r="W684" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X684" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y684" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z684" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA684" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:09:59</t>
+        </is>
+      </c>
+      <c r="AB684" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:41:19</t>
+        </is>
+      </c>
+      <c r="AC684" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:41:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC684"/>
+  <dimension ref="A1:AC702"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -70523,32 +70523,32 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>carolina.ore.mo@gmail.com</t>
+          <t>lvergaracastillo28@gmail.com</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>56986147685</t>
+          <t>+56 9 7103 6642</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Luis vergara Castillo</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Carolina Muñoz Barrientos</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -70558,7 +70558,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Ema</t>
+          <t>Florencia Vergara Muñoz</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -70568,17 +70568,17 @@
       </c>
       <c r="R681" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="S681" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="T681" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U681" t="inlineStr">
@@ -70591,7 +70591,7 @@
       </c>
       <c r="W681" t="inlineStr">
         <is>
-          <t>6479-01</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="X681" t="inlineStr">
@@ -70601,7 +70601,7 @@
       </c>
       <c r="Y681" t="inlineStr">
         <is>
-          <t>20806479-7</t>
+          <t>20568285-6</t>
         </is>
       </c>
       <c r="Z681" s="2">
@@ -70609,29 +70609,29 @@
       </c>
       <c r="AA681" t="inlineStr">
         <is>
-          <t>2026-05-07 09:01:05</t>
+          <t>2026-05-06 18:27:43</t>
         </is>
       </c>
       <c r="AB681" t="inlineStr">
         <is>
-          <t>2026-05-07 10:11:48</t>
+          <t>2026-05-07 15:14:01</t>
         </is>
       </c>
       <c r="AC681" t="inlineStr">
         <is>
-          <t>2026-05-07 10:11:48</t>
+          <t>2026-05-07 15:14:01</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>francoantoniorios@gmail.com</t>
+          <t>carolina.ore.mo@gmail.com</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>920269626</t>
+          <t>56986147685</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -70641,12 +70641,32 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Franco</t>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="R682" t="inlineStr">
@@ -70656,12 +70676,12 @@
       </c>
       <c r="S682" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="T682" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U682" t="inlineStr">
@@ -70674,7 +70694,7 @@
       </c>
       <c r="W682" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>6479-01</t>
         </is>
       </c>
       <c r="X682" t="inlineStr">
@@ -70684,37 +70704,37 @@
       </c>
       <c r="Y682" t="inlineStr">
         <is>
-          <t>19172396-1</t>
+          <t>20806479-7</t>
         </is>
       </c>
       <c r="Z682" s="2">
-        <v>45566</v>
+        <v>46149</v>
       </c>
       <c r="AA682" t="inlineStr">
         <is>
-          <t>2026-05-07 10:02:27</t>
+          <t>2026-05-07 09:01:05</t>
         </is>
       </c>
       <c r="AB682" t="inlineStr">
         <is>
-          <t>2026-05-07 10:30:29</t>
+          <t>2026-05-07 10:11:48</t>
         </is>
       </c>
       <c r="AC682" t="inlineStr">
         <is>
-          <t>2026-05-07 10:30:29</t>
+          <t>2026-05-07 10:11:48</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>jjjsuarez@gmail.com</t>
+          <t>francoantoniorios@gmail.com</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>56989629748</t>
+          <t>920269626</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -70724,7 +70744,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Franco</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -70732,46 +70752,6 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="F683" t="inlineStr">
-        <is>
-          <t>Blkys</t>
-        </is>
-      </c>
-      <c r="G683" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="H683" t="inlineStr">
-        <is>
-          <t>Yanethe</t>
-        </is>
-      </c>
-      <c r="I683" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="J683" t="inlineStr">
-        <is>
-          <t>Miguel</t>
-        </is>
-      </c>
-      <c r="K683" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="L683" t="inlineStr">
-        <is>
-          <t>Sofia</t>
-        </is>
-      </c>
-      <c r="M683" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
       <c r="R683" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -70779,12 +70759,12 @@
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="T683" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U683" t="inlineStr">
@@ -70797,67 +70777,67 @@
       </c>
       <c r="W683" t="inlineStr">
         <is>
-          <t>6479-02</t>
+          <t>396</t>
         </is>
       </c>
       <c r="X683" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y683" t="inlineStr">
         <is>
-          <t>20806479-7</t>
+          <t>19172396-1</t>
         </is>
       </c>
       <c r="Z683" s="2">
-        <v>46149</v>
+        <v>45566</v>
       </c>
       <c r="AA683" t="inlineStr">
         <is>
-          <t>2026-05-07 10:15:43</t>
+          <t>2026-05-07 10:02:27</t>
         </is>
       </c>
       <c r="AB683" t="inlineStr">
         <is>
-          <t>2026-05-07 11:40:47</t>
+          <t>2026-05-07 10:30:29</t>
         </is>
       </c>
       <c r="AC683" t="inlineStr">
         <is>
-          <t>2026-05-07 11:40:47</t>
+          <t>2026-05-07 10:30:29</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>vale.indo20@gmail.com</t>
+          <t>jjjsuarez@gmail.com</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>948553351</t>
+          <t>56989629748</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Valentina Indo</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Maria Paz Hermandez</t>
+          <t>Blkys</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -70865,19 +70845,49 @@
           <t>Mujer</t>
         </is>
       </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Yanethe</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R684" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="T684" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U684" t="inlineStr">
@@ -70890,7 +70900,7 @@
       </c>
       <c r="W684" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6479-02</t>
         </is>
       </c>
       <c r="X684" t="inlineStr">
@@ -70900,7 +70910,7 @@
       </c>
       <c r="Y684" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>20806479-7</t>
         </is>
       </c>
       <c r="Z684" s="2">
@@ -70908,17 +70918,1851 @@
       </c>
       <c r="AA684" t="inlineStr">
         <is>
+          <t>2026-05-07 10:15:43</t>
+        </is>
+      </c>
+      <c r="AB684" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:40:47</t>
+        </is>
+      </c>
+      <c r="AC684" t="inlineStr">
+        <is>
+          <t>2026-05-07 11:40:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>vale.indo20@gmail.com</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>948553351</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Valentina Indo</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Maria Paz Hermandez</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U685" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V685">
+        <v>1</v>
+      </c>
+      <c r="W685" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X685" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y685" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z685" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA685" t="inlineStr">
+        <is>
           <t>2026-05-07 11:09:59</t>
         </is>
       </c>
-      <c r="AB684" t="inlineStr">
+      <c r="AB685" t="inlineStr">
         <is>
           <t>2026-05-07 11:41:19</t>
         </is>
       </c>
-      <c r="AC684" t="inlineStr">
+      <c r="AC685" t="inlineStr">
         <is>
           <t>2026-05-07 11:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>brankar.1981@gmail.com</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>56952277293</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Maricarmen</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Brandon Pino</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>Karen Pino</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Melany medina</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T686" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U686" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V686">
+        <v>1</v>
+      </c>
+      <c r="W686" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="X686" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y686" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z686" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA686" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:52:48</t>
+        </is>
+      </c>
+      <c r="AB686" t="inlineStr">
+        <is>
+          <t>2026-05-07 13:48:55</t>
+        </is>
+      </c>
+      <c r="AC686" t="inlineStr">
+        <is>
+          <t>2026-05-07 13:48:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>randresvalenzuelaj@gmail.com</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>972088563</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Julián</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Ana María</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V687">
+        <v>1</v>
+      </c>
+      <c r="W687" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="X687" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y687" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="Z687" s="2">
+        <v>46138</v>
+      </c>
+      <c r="AA687" t="inlineStr">
+        <is>
+          <t>2026-05-07 13:27:12</t>
+        </is>
+      </c>
+      <c r="AB687" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:00:09</t>
+        </is>
+      </c>
+      <c r="AC687" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:00:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>quirozvillarroelr@gmail.com</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>926428130</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Rosario</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Jasmin</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Msrcelo</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V688">
+        <v>1</v>
+      </c>
+      <c r="W688" t="inlineStr">
+        <is>
+          <t>Correlativo 33</t>
+        </is>
+      </c>
+      <c r="X688" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y688" t="inlineStr">
+        <is>
+          <t>13081719-K</t>
+        </is>
+      </c>
+      <c r="Z688" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA688" t="inlineStr">
+        <is>
+          <t>2026-05-07 14:24:24</t>
+        </is>
+      </c>
+      <c r="AB688" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:19:22</t>
+        </is>
+      </c>
+      <c r="AC688" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:19:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>DAVID.VALDIVIA.R@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>56974040835</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Gracia</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V689">
+        <v>1</v>
+      </c>
+      <c r="W689" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="X689" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y689" t="inlineStr">
+        <is>
+          <t>18050509-1</t>
+        </is>
+      </c>
+      <c r="Z689" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA689" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:43:05</t>
+        </is>
+      </c>
+      <c r="AB689" t="inlineStr">
+        <is>
+          <t>2026-05-07 16:44:36</t>
+        </is>
+      </c>
+      <c r="AC689" t="inlineStr">
+        <is>
+          <t>2026-05-07 16:44:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>gisela.godoy020388@gmail.com</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>999332932</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Roberto Fuentes</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U690" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V690">
+        <v>1</v>
+      </c>
+      <c r="W690" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="X690" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y690" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="Z690" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA690" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:22:03</t>
+        </is>
+      </c>
+      <c r="AB690" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:00:17</t>
+        </is>
+      </c>
+      <c r="AC690" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:00:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>rayensantos@gmail.com</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>947184058</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Rayen / Thomas / Catherine / Josefina</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Josefina</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V691">
+        <v>1</v>
+      </c>
+      <c r="W691" t="inlineStr">
+        <is>
+          <t>CORRELATIVO 34</t>
+        </is>
+      </c>
+      <c r="X691" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y691" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z691" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA691" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:29:28</t>
+        </is>
+      </c>
+      <c r="AB691" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:33:23</t>
+        </is>
+      </c>
+      <c r="AC691" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:33:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>geramiifabiola@gmail.com</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>935123019</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Tomas rozas</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Agustín solano</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V692">
+        <v>1</v>
+      </c>
+      <c r="W692" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="X692" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y692" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="Z692" s="2">
+        <v>44958</v>
+      </c>
+      <c r="AA692" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:56:23</t>
+        </is>
+      </c>
+      <c r="AB692" t="inlineStr">
+        <is>
+          <t>2026-05-07 20:20:57</t>
+        </is>
+      </c>
+      <c r="AC692" t="inlineStr">
+        <is>
+          <t>2026-05-07 20:20:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>vegitomaster@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>961244665</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Verónica</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr">
+        <is>
+          <t>Ventanas</t>
+        </is>
+      </c>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U693" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V693">
+        <v>1</v>
+      </c>
+      <c r="W693" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="X693" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y693" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="Z693" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA693" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:10:54</t>
+        </is>
+      </c>
+      <c r="AB693" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:56:44</t>
+        </is>
+      </c>
+      <c r="AC693" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:56:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>yari.figueroa2010@gmail.com</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>949815493</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Yadira</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>Valparaixo</t>
+        </is>
+      </c>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U694" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V694">
+        <v>1</v>
+      </c>
+      <c r="W694" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="X694" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y694" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="Z694" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA694" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:37:40</t>
+        </is>
+      </c>
+      <c r="AB694" t="inlineStr">
+        <is>
+          <t>2026-05-07 20:48:33</t>
+        </is>
+      </c>
+      <c r="AC694" t="inlineStr">
+        <is>
+          <t>2026-05-07 20:48:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>cosita22-@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>959866246</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Verónica</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>Berta</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V695">
+        <v>1</v>
+      </c>
+      <c r="W695" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="X695" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y695" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="Z695" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA695" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:48:25</t>
+        </is>
+      </c>
+      <c r="AB695" t="inlineStr">
+        <is>
+          <t>2026-05-07 20:22:14</t>
+        </is>
+      </c>
+      <c r="AC695" t="inlineStr">
+        <is>
+          <t>2026-05-07 20:22:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>fabiola.gonzale.villar@gmail.com</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>934837199</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Geramy navarro</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Tomas rozas</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V696">
+        <v>1</v>
+      </c>
+      <c r="W696" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="X696" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y696" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="Z696" s="2">
+        <v>43563</v>
+      </c>
+      <c r="AA696" t="inlineStr">
+        <is>
+          <t>2026-05-07 20:27:02</t>
+        </is>
+      </c>
+      <c r="AB696" t="inlineStr">
+        <is>
+          <t>2026-05-07 21:40:48</t>
+        </is>
+      </c>
+      <c r="AC696" t="inlineStr">
+        <is>
+          <t>2026-05-07 21:40:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>katerine.farias1@iclaud.com</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>951987113</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Katerine</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V697">
+        <v>1</v>
+      </c>
+      <c r="W697" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="X697" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y697" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="Z697" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA697" t="inlineStr">
+        <is>
+          <t>2026-05-07 21:03:51</t>
+        </is>
+      </c>
+      <c r="AB697" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:32:32</t>
+        </is>
+      </c>
+      <c r="AC697" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:32:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>carlaarandacorrea@gmail.com</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>996546036</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Carla</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>Julieta</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>Sabtiago</t>
+        </is>
+      </c>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V698">
+        <v>2</v>
+      </c>
+      <c r="W698" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="X698" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y698" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="Z698" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA698" t="inlineStr">
+        <is>
+          <t>2026-05-08 07:56:58</t>
+        </is>
+      </c>
+      <c r="AB698" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:34:13</t>
+        </is>
+      </c>
+      <c r="AC698" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:34:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>cvalhermosilla@gmail.com</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>97967352</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Claudia Hermosilla</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Amanda Diaz Hermosilla</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Alfonsina Díaz Hermosilla</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V699">
+        <v>1</v>
+      </c>
+      <c r="W699" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X699" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y699" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z699" s="2">
+        <v>46149</v>
+      </c>
+      <c r="AA699" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:45:06</t>
+        </is>
+      </c>
+      <c r="AB699" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:23:29</t>
+        </is>
+      </c>
+      <c r="AC699" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:23:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>barbra.faun@gmail.com</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>56966206968</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Angelo</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Rayen</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Emilio</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V700">
+        <v>2</v>
+      </c>
+      <c r="W700" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="X700" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y700" t="inlineStr">
+        <is>
+          <t>18.050.509-1</t>
+        </is>
+      </c>
+      <c r="Z700" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA700" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:14:54</t>
+        </is>
+      </c>
+      <c r="AB700" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:59</t>
+        </is>
+      </c>
+      <c r="AC700" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>idearriagada@gmail.com</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>935225921</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Ide</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Yohanna</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>TALXA</t>
+        </is>
+      </c>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U701" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V701">
+        <v>1</v>
+      </c>
+      <c r="W701" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="X701" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y701" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="Z701" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA701" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:29:54</t>
+        </is>
+      </c>
+      <c r="AB701" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:02:07</t>
+        </is>
+      </c>
+      <c r="AC701" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:02:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>bele.castro.p@gmail.com</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>989033752</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Belen</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>Concon</t>
+        </is>
+      </c>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V702">
+        <v>1</v>
+      </c>
+      <c r="W702" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X702" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y702" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z702" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA702" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:56:19</t>
+        </is>
+      </c>
+      <c r="AB702" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:50</t>
+        </is>
+      </c>
+      <c r="AC702" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:50</t>
         </is>
       </c>
     </row>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC702"/>
+  <dimension ref="A1:AC722"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -70131,12 +70131,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>gonzalezpaty.05@gmail.com</t>
+          <t>carmendiaz.andrade@gmail.com</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>975272192</t>
+          <t>966927178</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -70146,17 +70146,17 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>Hijo</t>
+          <t>Cristian ortiz</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -70164,24 +70164,54 @@
           <t>Hombre</t>
         </is>
       </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Ofelia dia</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>Deyanira ortiz</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Cristian leon</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
       <c r="R677" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="S677" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Curico</t>
         </is>
       </c>
       <c r="T677" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U677" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V677">
@@ -70189,47 +70219,47 @@
       </c>
       <c r="W677" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>Labofam</t>
         </is>
       </c>
       <c r="X677" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y677" t="inlineStr">
         <is>
-          <t>105033206</t>
+          <t>205094288</t>
         </is>
       </c>
       <c r="Z677" s="2">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="AA677" t="inlineStr">
         <is>
-          <t>2026-05-06 15:30:42</t>
+          <t>2026-05-06 13:49:46</t>
         </is>
       </c>
       <c r="AB677" t="inlineStr">
         <is>
-          <t>2026-05-06 20:06:27</t>
+          <t>2026-05-10 21:51:27</t>
         </is>
       </c>
       <c r="AC677" t="inlineStr">
         <is>
-          <t>2026-05-06 20:06:27</t>
+          <t>2026-05-10 21:51:27</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Mariapaz.h@oscplus.cl</t>
+          <t>gonzalezpaty.05@gmail.com</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>971402041</t>
+          <t>975272192</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -70239,7 +70269,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>María Paz Henriquez.</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -70249,7 +70279,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Hijo</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -70257,24 +70287,14 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="H678" t="inlineStr">
-        <is>
-          <t>Isidora</t>
-        </is>
-      </c>
-      <c r="I678" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
       <c r="R678" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="S678" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="T678" t="inlineStr">
@@ -70284,7 +70304,7 @@
       </c>
       <c r="U678" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V678">
@@ -70292,7 +70312,7 @@
       </c>
       <c r="W678" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="X678" t="inlineStr">
@@ -70302,7 +70322,7 @@
       </c>
       <c r="Y678" t="inlineStr">
         <is>
-          <t>98784624</t>
+          <t>105033206</t>
         </is>
       </c>
       <c r="Z678" s="2">
@@ -70310,39 +70330,39 @@
       </c>
       <c r="AA678" t="inlineStr">
         <is>
-          <t>2026-05-06 15:47:39</t>
+          <t>2026-05-06 15:30:42</t>
         </is>
       </c>
       <c r="AB678" t="inlineStr">
         <is>
-          <t>2026-05-06 16:11:06</t>
+          <t>2026-05-06 20:06:27</t>
         </is>
       </c>
       <c r="AC678" t="inlineStr">
         <is>
-          <t>2026-05-06 16:11:06</t>
+          <t>2026-05-06 20:06:27</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>camiilapaztirapeguiflores@gmail.com</t>
+          <t>Mariapaz.h@oscplus.cl</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>992701643</t>
+          <t>971402041</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Camila Tirapegui</t>
+          <t>María Paz Henriquez.</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
@@ -70352,7 +70372,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Juan Peña Canales</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -70362,7 +70382,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Emily Rubio</t>
+          <t>Isidora</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -70372,17 +70392,17 @@
       </c>
       <c r="R679" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S679" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="T679" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U679" t="inlineStr">
@@ -70395,17 +70415,17 @@
       </c>
       <c r="W679" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>624</t>
         </is>
       </c>
       <c r="X679" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y679" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>98784624</t>
         </is>
       </c>
       <c r="Z679" s="2">
@@ -70413,29 +70433,29 @@
       </c>
       <c r="AA679" t="inlineStr">
         <is>
-          <t>2026-05-06 15:52:23</t>
+          <t>2026-05-06 15:47:39</t>
         </is>
       </c>
       <c r="AB679" t="inlineStr">
         <is>
-          <t>2026-05-06 16:18:42</t>
+          <t>2026-05-06 16:11:06</t>
         </is>
       </c>
       <c r="AC679" t="inlineStr">
         <is>
-          <t>2026-05-06 16:18:42</t>
+          <t>2026-05-06 16:11:06</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>dxmvera@gmail.com</t>
+          <t>camiilapaztirapeguiflores@gmail.com</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>dxmvera@gmail.com</t>
+          <t>992701643</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -70445,7 +70465,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Diana Morales Vera</t>
+          <t>Camila Tirapegui</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -70455,7 +70475,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Gabriel Poblete</t>
+          <t>Juan Peña Canales</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -70463,19 +70483,29 @@
           <t>Hombre</t>
         </is>
       </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>Emily Rubio</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R680" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="S680" t="inlineStr">
         <is>
-          <t>valparaiso</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="T680" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U680" t="inlineStr">
@@ -70488,17 +70518,17 @@
       </c>
       <c r="W680" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X680" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y680" t="inlineStr">
         <is>
-          <t>20568285-6</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="Z680" s="2">
@@ -70506,29 +70536,29 @@
       </c>
       <c r="AA680" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:19</t>
+          <t>2026-05-06 15:52:23</t>
         </is>
       </c>
       <c r="AB680" t="inlineStr">
         <is>
-          <t>2026-05-06 17:06:46</t>
+          <t>2026-05-06 16:18:42</t>
         </is>
       </c>
       <c r="AC680" t="inlineStr">
         <is>
-          <t>2026-05-06 17:06:46</t>
+          <t>2026-05-06 16:18:42</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>lvergaracastillo28@gmail.com</t>
+          <t>dxmvera@gmail.com</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>+56 9 7103 6642</t>
+          <t>dxmvera@gmail.com</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -70538,32 +70568,22 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Luis vergara Castillo</t>
+          <t>Diana Morales Vera</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Carolina Muñoz Barrientos</t>
+          <t>Gabriel Poblete</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="H681" t="inlineStr">
-        <is>
-          <t>Florencia Vergara Muñoz</t>
-        </is>
-      </c>
-      <c r="I681" t="inlineStr">
-        <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="R681" t="inlineStr">
@@ -70573,12 +70593,12 @@
       </c>
       <c r="S681" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>valparaiso</t>
         </is>
       </c>
       <c r="T681" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U681" t="inlineStr">
@@ -70605,53 +70625,53 @@
         </is>
       </c>
       <c r="Z681" s="2">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="AA681" t="inlineStr">
         <is>
-          <t>2026-05-06 18:27:43</t>
+          <t>2026-05-06 16:28:19</t>
         </is>
       </c>
       <c r="AB681" t="inlineStr">
         <is>
-          <t>2026-05-07 15:14:01</t>
+          <t>2026-05-06 17:06:46</t>
         </is>
       </c>
       <c r="AC681" t="inlineStr">
         <is>
-          <t>2026-05-07 15:14:01</t>
+          <t>2026-05-06 17:06:46</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>carolina.ore.mo@gmail.com</t>
+          <t>lvergaracastillo28@gmail.com</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>56986147685</t>
+          <t>+56 9 7103 6642</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Luis vergara Castillo</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Carolina Muñoz Barrientos</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
@@ -70661,7 +70681,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Ema</t>
+          <t>Florencia Vergara Muñoz</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -70671,17 +70691,17 @@
       </c>
       <c r="R682" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="S682" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="T682" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U682" t="inlineStr">
@@ -70694,7 +70714,7 @@
       </c>
       <c r="W682" t="inlineStr">
         <is>
-          <t>6479-01</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="X682" t="inlineStr">
@@ -70704,7 +70724,7 @@
       </c>
       <c r="Y682" t="inlineStr">
         <is>
-          <t>20806479-7</t>
+          <t>20568285-6</t>
         </is>
       </c>
       <c r="Z682" s="2">
@@ -70712,29 +70732,29 @@
       </c>
       <c r="AA682" t="inlineStr">
         <is>
-          <t>2026-05-07 09:01:05</t>
+          <t>2026-05-06 18:27:43</t>
         </is>
       </c>
       <c r="AB682" t="inlineStr">
         <is>
-          <t>2026-05-07 10:11:48</t>
+          <t>2026-05-07 15:14:01</t>
         </is>
       </c>
       <c r="AC682" t="inlineStr">
         <is>
-          <t>2026-05-07 10:11:48</t>
+          <t>2026-05-07 15:14:01</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>francoantoniorios@gmail.com</t>
+          <t>carolina.ore.mo@gmail.com</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>920269626</t>
+          <t>56986147685</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -70744,12 +70764,32 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Franco</t>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="R683" t="inlineStr">
@@ -70759,12 +70799,12 @@
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="T683" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U683" t="inlineStr">
@@ -70777,7 +70817,7 @@
       </c>
       <c r="W683" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>6479-01</t>
         </is>
       </c>
       <c r="X683" t="inlineStr">
@@ -70787,37 +70827,37 @@
       </c>
       <c r="Y683" t="inlineStr">
         <is>
-          <t>19172396-1</t>
+          <t>20806479-7</t>
         </is>
       </c>
       <c r="Z683" s="2">
-        <v>45566</v>
+        <v>46149</v>
       </c>
       <c r="AA683" t="inlineStr">
         <is>
-          <t>2026-05-07 10:02:27</t>
+          <t>2026-05-07 09:01:05</t>
         </is>
       </c>
       <c r="AB683" t="inlineStr">
         <is>
-          <t>2026-05-07 10:30:29</t>
+          <t>2026-05-07 10:11:48</t>
         </is>
       </c>
       <c r="AC683" t="inlineStr">
         <is>
-          <t>2026-05-07 10:30:29</t>
+          <t>2026-05-07 10:11:48</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>jjjsuarez@gmail.com</t>
+          <t>francoantoniorios@gmail.com</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>56989629748</t>
+          <t>920269626</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -70827,7 +70867,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Franco</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -70835,46 +70875,6 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="F684" t="inlineStr">
-        <is>
-          <t>Blkys</t>
-        </is>
-      </c>
-      <c r="G684" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="H684" t="inlineStr">
-        <is>
-          <t>Yanethe</t>
-        </is>
-      </c>
-      <c r="I684" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="J684" t="inlineStr">
-        <is>
-          <t>Miguel</t>
-        </is>
-      </c>
-      <c r="K684" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="L684" t="inlineStr">
-        <is>
-          <t>Sofia</t>
-        </is>
-      </c>
-      <c r="M684" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
       <c r="R684" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -70882,12 +70882,12 @@
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="T684" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U684" t="inlineStr">
@@ -70900,67 +70900,67 @@
       </c>
       <c r="W684" t="inlineStr">
         <is>
-          <t>6479-02</t>
+          <t>396</t>
         </is>
       </c>
       <c r="X684" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y684" t="inlineStr">
         <is>
-          <t>20806479-7</t>
+          <t>19172396-1</t>
         </is>
       </c>
       <c r="Z684" s="2">
-        <v>46149</v>
+        <v>45566</v>
       </c>
       <c r="AA684" t="inlineStr">
         <is>
-          <t>2026-05-07 10:15:43</t>
+          <t>2026-05-07 10:02:27</t>
         </is>
       </c>
       <c r="AB684" t="inlineStr">
         <is>
-          <t>2026-05-07 11:40:47</t>
+          <t>2026-05-07 10:30:29</t>
         </is>
       </c>
       <c r="AC684" t="inlineStr">
         <is>
-          <t>2026-05-07 11:40:47</t>
+          <t>2026-05-07 10:30:29</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>vale.indo20@gmail.com</t>
+          <t>jjjsuarez@gmail.com</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>948553351</t>
+          <t>56989629748</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Valentina Indo</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Maria Paz Hermandez</t>
+          <t>Blkys</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -70968,19 +70968,49 @@
           <t>Mujer</t>
         </is>
       </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Yanethe</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R685" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S685" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="T685" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U685" t="inlineStr">
@@ -70993,7 +71023,7 @@
       </c>
       <c r="W685" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6479-02</t>
         </is>
       </c>
       <c r="X685" t="inlineStr">
@@ -71003,7 +71033,7 @@
       </c>
       <c r="Y685" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>20806479-7</t>
         </is>
       </c>
       <c r="Z685" s="2">
@@ -71011,39 +71041,39 @@
       </c>
       <c r="AA685" t="inlineStr">
         <is>
-          <t>2026-05-07 11:09:59</t>
+          <t>2026-05-07 10:15:43</t>
         </is>
       </c>
       <c r="AB685" t="inlineStr">
         <is>
-          <t>2026-05-07 11:41:19</t>
+          <t>2026-05-07 11:40:47</t>
         </is>
       </c>
       <c r="AC685" t="inlineStr">
         <is>
-          <t>2026-05-07 11:41:19</t>
+          <t>2026-05-07 11:40:47</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>brankar.1981@gmail.com</t>
+          <t>vale.indo20@gmail.com</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>56952277293</t>
+          <t>948553351</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Maricarmen</t>
+          <t>Valentina Indo</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -71053,62 +71083,32 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>Brandon Pino</t>
+          <t>Maria Paz Hermandez</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="H686" t="inlineStr">
-        <is>
-          <t>Karen Pino</t>
-        </is>
-      </c>
-      <c r="I686" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="J686" t="inlineStr">
-        <is>
-          <t>Melany medina</t>
-        </is>
-      </c>
-      <c r="K686" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="L686" t="inlineStr">
-        <is>
-          <t>Andres</t>
-        </is>
-      </c>
-      <c r="M686" t="inlineStr">
-        <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="R686" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="T686" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U686" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V686">
@@ -71116,7 +71116,7 @@
       </c>
       <c r="W686" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X686" t="inlineStr">
@@ -71126,7 +71126,7 @@
       </c>
       <c r="Y686" t="inlineStr">
         <is>
-          <t>13081719-k</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="Z686" s="2">
@@ -71134,29 +71134,29 @@
       </c>
       <c r="AA686" t="inlineStr">
         <is>
-          <t>2026-05-07 12:52:48</t>
+          <t>2026-05-07 11:09:59</t>
         </is>
       </c>
       <c r="AB686" t="inlineStr">
         <is>
-          <t>2026-05-07 13:48:55</t>
+          <t>2026-05-07 11:41:19</t>
         </is>
       </c>
       <c r="AC686" t="inlineStr">
         <is>
-          <t>2026-05-07 13:48:55</t>
+          <t>2026-05-07 11:41:19</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>randresvalenzuelaj@gmail.com</t>
+          <t>brankar.1981@gmail.com</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>972088563</t>
+          <t>56952277293</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -71166,22 +71166,52 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Julián</t>
+          <t>Maricarmen</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>Ana María</t>
+          <t>Brandon Pino</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Karen Pino</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Melany medina</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="R687" t="inlineStr">
@@ -71191,7 +71221,7 @@
       </c>
       <c r="S687" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="T687" t="inlineStr">
@@ -71201,7 +71231,7 @@
       </c>
       <c r="U687" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V687">
@@ -71209,47 +71239,47 @@
       </c>
       <c r="W687" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="X687" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y687" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>13081719-k</t>
         </is>
       </c>
       <c r="Z687" s="2">
-        <v>46138</v>
+        <v>46149</v>
       </c>
       <c r="AA687" t="inlineStr">
         <is>
-          <t>2026-05-07 13:27:12</t>
+          <t>2026-05-07 12:52:48</t>
         </is>
       </c>
       <c r="AB687" t="inlineStr">
         <is>
-          <t>2026-05-07 15:00:09</t>
+          <t>2026-05-07 13:48:55</t>
         </is>
       </c>
       <c r="AC687" t="inlineStr">
         <is>
-          <t>2026-05-07 15:00:09</t>
+          <t>2026-05-07 13:48:55</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>quirozvillarroelr@gmail.com</t>
+          <t>randresvalenzuelaj@gmail.com</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>926428130</t>
+          <t>972088563</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -71259,17 +71289,17 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Rosario</t>
+          <t>Julián</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Jasmin</t>
+          <t>Ana María</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -71277,26 +71307,6 @@
           <t>Mujer</t>
         </is>
       </c>
-      <c r="H688" t="inlineStr">
-        <is>
-          <t>Gabriel</t>
-        </is>
-      </c>
-      <c r="I688" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="J688" t="inlineStr">
-        <is>
-          <t>Msrcelo</t>
-        </is>
-      </c>
-      <c r="K688" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
       <c r="R688" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -71304,7 +71314,7 @@
       </c>
       <c r="S688" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="T688" t="inlineStr">
@@ -71322,7 +71332,7 @@
       </c>
       <c r="W688" t="inlineStr">
         <is>
-          <t>Correlativo 33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="X688" t="inlineStr">
@@ -71332,37 +71342,37 @@
       </c>
       <c r="Y688" t="inlineStr">
         <is>
-          <t>13081719-K</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="Z688" s="2">
-        <v>46149</v>
+        <v>46138</v>
       </c>
       <c r="AA688" t="inlineStr">
         <is>
-          <t>2026-05-07 14:24:24</t>
+          <t>2026-05-07 13:27:12</t>
         </is>
       </c>
       <c r="AB688" t="inlineStr">
         <is>
-          <t>2026-05-07 15:19:22</t>
+          <t>2026-05-07 15:00:09</t>
         </is>
       </c>
       <c r="AC688" t="inlineStr">
         <is>
-          <t>2026-05-07 15:19:22</t>
+          <t>2026-05-07 15:00:09</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>DAVID.VALDIVIA.R@GMAIL.COM</t>
+          <t>quirozvillarroelr@gmail.com</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>56974040835</t>
+          <t>926428130</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -71372,17 +71382,17 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Rosario</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Gracia</t>
+          <t>Jasmin</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -71390,6 +71400,26 @@
           <t>Mujer</t>
         </is>
       </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>Msrcelo</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
       <c r="R689" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -71397,7 +71427,7 @@
       </c>
       <c r="S689" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="T689" t="inlineStr">
@@ -71415,17 +71445,17 @@
       </c>
       <c r="W689" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>Correlativo 33</t>
         </is>
       </c>
       <c r="X689" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y689" t="inlineStr">
         <is>
-          <t>18050509-1</t>
+          <t>13081719-K</t>
         </is>
       </c>
       <c r="Z689" s="2">
@@ -71433,29 +71463,29 @@
       </c>
       <c r="AA689" t="inlineStr">
         <is>
-          <t>2026-05-07 15:43:05</t>
+          <t>2026-05-07 14:24:24</t>
         </is>
       </c>
       <c r="AB689" t="inlineStr">
         <is>
-          <t>2026-05-07 16:44:36</t>
+          <t>2026-05-07 15:19:22</t>
         </is>
       </c>
       <c r="AC689" t="inlineStr">
         <is>
-          <t>2026-05-07 16:44:36</t>
+          <t>2026-05-07 15:19:22</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>gisela.godoy020388@gmail.com</t>
+          <t>DAVID.VALDIVIA.R@GMAIL.COM</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>999332932</t>
+          <t>56974040835</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -71465,7 +71495,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Roberto Fuentes</t>
+          <t>David</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -71473,6 +71503,16 @@
           <t>Hombre</t>
         </is>
       </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Gracia</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R690" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -71480,7 +71520,7 @@
       </c>
       <c r="S690" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="T690" t="inlineStr">
@@ -71498,17 +71538,17 @@
       </c>
       <c r="W690" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>091</t>
         </is>
       </c>
       <c r="X690" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y690" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>18050509-1</t>
         </is>
       </c>
       <c r="Z690" s="2">
@@ -71516,29 +71556,29 @@
       </c>
       <c r="AA690" t="inlineStr">
         <is>
-          <t>2026-05-07 17:22:03</t>
+          <t>2026-05-07 15:43:05</t>
         </is>
       </c>
       <c r="AB690" t="inlineStr">
         <is>
-          <t>2026-05-07 18:00:17</t>
+          <t>2026-05-07 16:44:36</t>
         </is>
       </c>
       <c r="AC690" t="inlineStr">
         <is>
-          <t>2026-05-07 18:00:17</t>
+          <t>2026-05-07 16:44:36</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>rayensantos@gmail.com</t>
+          <t>gisela.godoy020388@gmail.com</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>947184058</t>
+          <t>999332932</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -71548,42 +71588,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Rayen / Thomas / Catherine / Josefina</t>
+          <t>Roberto Fuentes</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="F691" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="G691" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="H691" t="inlineStr">
-        <is>
-          <t>Josefina</t>
-        </is>
-      </c>
-      <c r="I691" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="J691" t="inlineStr">
-        <is>
-          <t>Catherine</t>
-        </is>
-      </c>
-      <c r="K691" t="inlineStr">
-        <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="R691" t="inlineStr">
@@ -71593,7 +71603,7 @@
       </c>
       <c r="S691" t="inlineStr">
         <is>
-          <t>La florida</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="T691" t="inlineStr">
@@ -71611,17 +71621,17 @@
       </c>
       <c r="W691" t="inlineStr">
         <is>
-          <t>CORRELATIVO 34</t>
+          <t>34</t>
         </is>
       </c>
       <c r="X691" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y691" t="inlineStr">
         <is>
-          <t>13081719-k</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="Z691" s="2">
@@ -71629,29 +71639,29 @@
       </c>
       <c r="AA691" t="inlineStr">
         <is>
-          <t>2026-05-07 17:29:28</t>
+          <t>2026-05-07 17:22:03</t>
         </is>
       </c>
       <c r="AB691" t="inlineStr">
         <is>
-          <t>2026-05-07 18:33:23</t>
+          <t>2026-05-07 18:00:17</t>
         </is>
       </c>
       <c r="AC691" t="inlineStr">
         <is>
-          <t>2026-05-07 18:33:20</t>
+          <t>2026-05-07 18:00:17</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>geramiifabiola@gmail.com</t>
+          <t>rayensantos@gmail.com</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>935123019</t>
+          <t>947184058</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -71661,7 +71671,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Tomas rozas</t>
+          <t>Rayen / Thomas / Catherine / Josefina</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -71671,7 +71681,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Agustín solano</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -71679,6 +71689,26 @@
           <t>Hombre</t>
         </is>
       </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Josefina</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R692" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
@@ -71686,12 +71716,12 @@
       </c>
       <c r="S692" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>La florida</t>
         </is>
       </c>
       <c r="T692" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U692" t="inlineStr">
@@ -71704,92 +71734,82 @@
       </c>
       <c r="W692" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>CORRELATIVO 34</t>
         </is>
       </c>
       <c r="X692" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y692" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>13081719-k</t>
         </is>
       </c>
       <c r="Z692" s="2">
-        <v>44958</v>
+        <v>46149</v>
       </c>
       <c r="AA692" t="inlineStr">
         <is>
-          <t>2026-05-07 18:56:23</t>
+          <t>2026-05-07 17:29:28</t>
         </is>
       </c>
       <c r="AB692" t="inlineStr">
         <is>
-          <t>2026-05-07 20:20:57</t>
+          <t>2026-05-07 18:33:23</t>
         </is>
       </c>
       <c r="AC692" t="inlineStr">
         <is>
-          <t>2026-05-07 20:20:57</t>
+          <t>2026-05-07 18:33:20</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>vegitomaster@hotmail.com</t>
+          <t>geramiifabiola@gmail.com</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>961244665</t>
+          <t>935123019</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Alejandro</t>
+          <t>Tomas rozas</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>Verónica</t>
+          <t>Agustín solano</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="H693" t="inlineStr">
-        <is>
-          <t>Benjamin</t>
-        </is>
-      </c>
-      <c r="I693" t="inlineStr">
-        <is>
           <t>Hombre</t>
         </is>
       </c>
       <c r="R693" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S693" t="inlineStr">
         <is>
-          <t>Ventanas</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="T693" t="inlineStr">
@@ -71807,67 +71827,67 @@
       </c>
       <c r="W693" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>36</t>
         </is>
       </c>
       <c r="X693" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y693" t="inlineStr">
         <is>
-          <t>160334290</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="Z693" s="2">
-        <v>46149</v>
+        <v>44958</v>
       </c>
       <c r="AA693" t="inlineStr">
         <is>
-          <t>2026-05-07 19:10:54</t>
+          <t>2026-05-07 18:56:23</t>
         </is>
       </c>
       <c r="AB693" t="inlineStr">
         <is>
-          <t>2026-05-07 19:56:44</t>
+          <t>2026-05-07 20:20:57</t>
         </is>
       </c>
       <c r="AC693" t="inlineStr">
         <is>
-          <t>2026-05-07 19:56:42</t>
+          <t>2026-05-07 20:20:57</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>yari.figueroa2010@gmail.com</t>
+          <t>vegitomaster@hotmail.com</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>949815493</t>
+          <t>961244665</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Yadira</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>Scarlet</t>
+          <t>Verónica</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -71875,6 +71895,16 @@
           <t>Mujer</t>
         </is>
       </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
       <c r="R694" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -71882,7 +71912,7 @@
       </c>
       <c r="S694" t="inlineStr">
         <is>
-          <t>Valparaixo</t>
+          <t>Ventanas</t>
         </is>
       </c>
       <c r="T694" t="inlineStr">
@@ -71900,17 +71930,17 @@
       </c>
       <c r="W694" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="X694" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y694" t="inlineStr">
         <is>
-          <t>105033206</t>
+          <t>160334290</t>
         </is>
       </c>
       <c r="Z694" s="2">
@@ -71918,39 +71948,39 @@
       </c>
       <c r="AA694" t="inlineStr">
         <is>
-          <t>2026-05-07 19:37:40</t>
+          <t>2026-05-07 19:10:54</t>
         </is>
       </c>
       <c r="AB694" t="inlineStr">
         <is>
-          <t>2026-05-07 20:48:33</t>
+          <t>2026-05-07 19:56:44</t>
         </is>
       </c>
       <c r="AC694" t="inlineStr">
         <is>
-          <t>2026-05-07 20:48:33</t>
+          <t>2026-05-07 19:56:42</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>cosita22-@hotmail.com</t>
+          <t>yari.figueroa2010@gmail.com</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>959866246</t>
+          <t>949815493</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Verónica</t>
+          <t>Yadira</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
@@ -71960,41 +71990,11 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Scarlet</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="H695" t="inlineStr">
-        <is>
-          <t>Francisca</t>
-        </is>
-      </c>
-      <c r="I695" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="J695" t="inlineStr">
-        <is>
-          <t>Claudia</t>
-        </is>
-      </c>
-      <c r="K695" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="L695" t="inlineStr">
-        <is>
-          <t>Berta</t>
-        </is>
-      </c>
-      <c r="M695" t="inlineStr">
-        <is>
           <t>Mujer</t>
         </is>
       </c>
@@ -72005,12 +72005,12 @@
       </c>
       <c r="S695" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Valparaixo</t>
         </is>
       </c>
       <c r="T695" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U695" t="inlineStr">
@@ -72023,17 +72023,17 @@
       </c>
       <c r="W695" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="X695" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y695" t="inlineStr">
         <is>
-          <t>160334290</t>
+          <t>105033206</t>
         </is>
       </c>
       <c r="Z695" s="2">
@@ -72041,39 +72041,39 @@
       </c>
       <c r="AA695" t="inlineStr">
         <is>
-          <t>2026-05-07 19:48:25</t>
+          <t>2026-05-07 19:37:40</t>
         </is>
       </c>
       <c r="AB695" t="inlineStr">
         <is>
-          <t>2026-05-07 20:22:14</t>
+          <t>2026-05-07 20:48:33</t>
         </is>
       </c>
       <c r="AC695" t="inlineStr">
         <is>
-          <t>2026-05-07 20:22:14</t>
+          <t>2026-05-07 20:48:33</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>fabiola.gonzale.villar@gmail.com</t>
+          <t>cosita22-@hotmail.com</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>934837199</t>
+          <t>959866246</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Geramy navarro</t>
+          <t>Verónica</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -72083,7 +72083,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Tomas rozas</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -72091,14 +72091,44 @@
           <t>Hombre</t>
         </is>
       </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>Berta</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R696" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="S696" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="T696" t="inlineStr">
@@ -72116,47 +72146,47 @@
       </c>
       <c r="W696" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="X696" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="Y696" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>160334290</t>
         </is>
       </c>
       <c r="Z696" s="2">
-        <v>43563</v>
+        <v>46149</v>
       </c>
       <c r="AA696" t="inlineStr">
         <is>
-          <t>2026-05-07 20:27:02</t>
+          <t>2026-05-07 19:48:25</t>
         </is>
       </c>
       <c r="AB696" t="inlineStr">
         <is>
-          <t>2026-05-07 21:40:48</t>
+          <t>2026-05-07 20:22:14</t>
         </is>
       </c>
       <c r="AC696" t="inlineStr">
         <is>
-          <t>2026-05-07 21:40:48</t>
+          <t>2026-05-07 20:22:14</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>katerine.farias1@iclaud.com</t>
+          <t>fabiola.gonzale.villar@gmail.com</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>951987113</t>
+          <t>934837199</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -72166,7 +72196,7 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Katerine</t>
+          <t>Geramy navarro</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -72176,27 +72206,27 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Tomas rozas</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="R697" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S697" t="inlineStr">
         <is>
-          <t>Valparaiso</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="T697" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U697" t="inlineStr">
@@ -72209,7 +72239,7 @@
       </c>
       <c r="W697" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>37</t>
         </is>
       </c>
       <c r="X697" t="inlineStr">
@@ -72219,37 +72249,37 @@
       </c>
       <c r="Y697" t="inlineStr">
         <is>
-          <t>105033206</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="Z697" s="2">
-        <v>46149</v>
+        <v>43563</v>
       </c>
       <c r="AA697" t="inlineStr">
         <is>
-          <t>2026-05-07 21:03:51</t>
+          <t>2026-05-07 20:27:02</t>
         </is>
       </c>
       <c r="AB697" t="inlineStr">
         <is>
-          <t>2026-05-07 22:32:32</t>
+          <t>2026-05-07 21:40:48</t>
         </is>
       </c>
       <c r="AC697" t="inlineStr">
         <is>
-          <t>2026-05-07 22:32:32</t>
+          <t>2026-05-07 21:40:48</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>carlaarandacorrea@gmail.com</t>
+          <t>katerine.farias1@iclaud.com</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>996546036</t>
+          <t>951987113</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -72259,7 +72289,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Katerine</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
@@ -72269,60 +72299,40 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="H698" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="I698" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="J698" t="inlineStr">
-        <is>
-          <t>Julieta</t>
-        </is>
-      </c>
-      <c r="K698" t="inlineStr">
-        <is>
           <t>Mujer</t>
         </is>
       </c>
       <c r="R698" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="S698" t="inlineStr">
         <is>
-          <t>Sabtiago</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="T698" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U698" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V698">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W698" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="X698" t="inlineStr">
@@ -72332,7 +72342,7 @@
       </c>
       <c r="Y698" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>105033206</t>
         </is>
       </c>
       <c r="Z698" s="2">
@@ -72340,29 +72350,29 @@
       </c>
       <c r="AA698" t="inlineStr">
         <is>
-          <t>2026-05-08 07:56:58</t>
+          <t>2026-05-07 21:03:51</t>
         </is>
       </c>
       <c r="AB698" t="inlineStr">
         <is>
-          <t>2026-05-08 08:34:13</t>
+          <t>2026-05-07 22:32:32</t>
         </is>
       </c>
       <c r="AC698" t="inlineStr">
         <is>
-          <t>2026-05-08 08:34:13</t>
+          <t>2026-05-07 22:32:32</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>cvalhermosilla@gmail.com</t>
+          <t>Ta.romero.c@gmail.com</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>97967352</t>
+          <t>957419812</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -72372,7 +72382,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Claudia Hermosilla</t>
+          <t>Tania Romero Carrasco</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -72382,37 +72392,27 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Amanda Diaz Hermosilla</t>
+          <t>Tobías Bascuñan Romero</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="H699" t="inlineStr">
-        <is>
-          <t>Alfonsina Díaz Hermosilla</t>
-        </is>
-      </c>
-      <c r="I699" t="inlineStr">
-        <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="R699" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="S699" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="T699" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U699" t="inlineStr">
@@ -72425,47 +72425,47 @@
       </c>
       <c r="W699" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="X699" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="Y699" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>29568285-6</t>
         </is>
       </c>
       <c r="Z699" s="2">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="AA699" t="inlineStr">
         <is>
-          <t>2026-05-08 10:45:06</t>
+          <t>2026-05-08 00:39:47</t>
         </is>
       </c>
       <c r="AB699" t="inlineStr">
         <is>
-          <t>2026-05-08 11:23:29</t>
+          <t>2026-05-08 23:59:28</t>
         </is>
       </c>
       <c r="AC699" t="inlineStr">
         <is>
-          <t>2026-05-08 11:23:29</t>
+          <t>2026-05-08 23:59:28</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>barbra.faun@gmail.com</t>
+          <t>carlaarandacorrea@gmail.com</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>56966206968</t>
+          <t>996546036</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -72475,7 +72475,7 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -72485,7 +72485,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -72495,32 +72495,32 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Rayen</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Julieta</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="R700" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="S700" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Sabtiago</t>
         </is>
       </c>
       <c r="T700" t="inlineStr">
@@ -72530,7 +72530,7 @@
       </c>
       <c r="U700" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V700">
@@ -72538,7 +72538,7 @@
       </c>
       <c r="W700" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>32</t>
         </is>
       </c>
       <c r="X700" t="inlineStr">
@@ -72548,37 +72548,37 @@
       </c>
       <c r="Y700" t="inlineStr">
         <is>
-          <t>18.050.509-1</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="Z700" s="2">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="AA700" t="inlineStr">
         <is>
-          <t>2026-05-08 11:14:54</t>
+          <t>2026-05-08 07:56:58</t>
         </is>
       </c>
       <c r="AB700" t="inlineStr">
         <is>
-          <t>2026-05-08 12:24:59</t>
+          <t>2026-05-08 08:34:13</t>
         </is>
       </c>
       <c r="AC700" t="inlineStr">
         <is>
-          <t>2026-05-08 12:24:59</t>
+          <t>2026-05-08 08:34:13</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>idearriagada@gmail.com</t>
+          <t>cvalhermosilla@gmail.com</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>935225921</t>
+          <t>97967352</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -72588,7 +72588,7 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Ide</t>
+          <t>Claudia Hermosilla</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -72598,7 +72598,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Yohanna</t>
+          <t>Amanda Diaz Hermosilla</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -72606,6 +72606,16 @@
           <t>Mujer</t>
         </is>
       </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Alfonsina Díaz Hermosilla</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
       <c r="R701" t="inlineStr">
         <is>
           <t>Maule</t>
@@ -72613,7 +72623,7 @@
       </c>
       <c r="S701" t="inlineStr">
         <is>
-          <t>TALXA</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="T701" t="inlineStr">
@@ -72631,7 +72641,7 @@
       </c>
       <c r="W701" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>18</t>
         </is>
       </c>
       <c r="X701" t="inlineStr">
@@ -72641,47 +72651,47 @@
       </c>
       <c r="Y701" t="inlineStr">
         <is>
-          <t>125897401</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="Z701" s="2">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="AA701" t="inlineStr">
         <is>
-          <t>2026-05-08 11:29:54</t>
+          <t>2026-05-08 10:45:06</t>
         </is>
       </c>
       <c r="AB701" t="inlineStr">
         <is>
-          <t>2026-05-08 12:02:07</t>
+          <t>2026-05-08 11:23:29</t>
         </is>
       </c>
       <c r="AC701" t="inlineStr">
         <is>
-          <t>2026-05-08 12:02:07</t>
+          <t>2026-05-08 11:23:29</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>bele.castro.p@gmail.com</t>
+          <t>barbra.faun@gmail.com</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>989033752</t>
+          <t>56966206968</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Belen</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -72691,7 +72701,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -72701,22 +72711,32 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Rayen</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
         <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>Emilio</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
           <t>Hombre</t>
         </is>
       </c>
       <c r="R702" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="S702" t="inlineStr">
         <is>
-          <t>Concon</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="T702" t="inlineStr">
@@ -72730,11 +72750,11 @@
         </is>
       </c>
       <c r="V702">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W702" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>091</t>
         </is>
       </c>
       <c r="X702" t="inlineStr">
@@ -72744,7 +72764,7 @@
       </c>
       <c r="Y702" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>18.050.509-1</t>
         </is>
       </c>
       <c r="Z702" s="2">
@@ -72752,17 +72772,2037 @@
       </c>
       <c r="AA702" t="inlineStr">
         <is>
+          <t>2026-05-08 11:14:54</t>
+        </is>
+      </c>
+      <c r="AB702" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:59</t>
+        </is>
+      </c>
+      <c r="AC702" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>idearriagada@gmail.com</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>935225921</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Ide</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Yohanna</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>TALXA</t>
+        </is>
+      </c>
+      <c r="T703" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V703">
+        <v>1</v>
+      </c>
+      <c r="W703" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="X703" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y703" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="Z703" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA703" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:29:54</t>
+        </is>
+      </c>
+      <c r="AB703" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:02:07</t>
+        </is>
+      </c>
+      <c r="AC703" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:02:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>bele.castro.p@gmail.com</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>989033752</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Belen</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr">
+        <is>
+          <t>Concon</t>
+        </is>
+      </c>
+      <c r="T704" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V704">
+        <v>1</v>
+      </c>
+      <c r="W704" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X704" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y704" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z704" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA704" t="inlineStr">
+        <is>
           <t>2026-05-08 11:56:19</t>
         </is>
       </c>
-      <c r="AB702" t="inlineStr">
+      <c r="AB704" t="inlineStr">
         <is>
           <t>2026-05-08 12:24:50</t>
         </is>
       </c>
-      <c r="AC702" t="inlineStr">
+      <c r="AC704" t="inlineStr">
         <is>
           <t>2026-05-08 12:24:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>daniela.sf.k@gmail.com</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>977687764</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>Luciano</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>Elisa</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>Quilpue</t>
+        </is>
+      </c>
+      <c r="T705" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V705">
+        <v>1</v>
+      </c>
+      <c r="W705" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X705" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y705" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z705" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA705" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:56</t>
+        </is>
+      </c>
+      <c r="AB705" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:39:11</t>
+        </is>
+      </c>
+      <c r="AC705" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:39:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>bravonathaly594@gmail.com</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>933017123</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Nathaly salinas</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr">
+        <is>
+          <t>Pte alto</t>
+        </is>
+      </c>
+      <c r="T706" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V706">
+        <v>2</v>
+      </c>
+      <c r="W706" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="X706" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y706" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z706" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA706" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:38:40</t>
+        </is>
+      </c>
+      <c r="AB706" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:18:20</t>
+        </is>
+      </c>
+      <c r="AC706" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:18:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>josepepeguerra@gmail.com</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>983712962</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="T707" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U707" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V707">
+        <v>2</v>
+      </c>
+      <c r="W707" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X707" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y707" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z707" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA707" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:39:24</t>
+        </is>
+      </c>
+      <c r="AB707" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:01:20</t>
+        </is>
+      </c>
+      <c r="AC707" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:01:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>srodriguezi@inacap.cl</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>9999999999</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Matilde</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S708" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T708" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U708" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V708">
+        <v>2</v>
+      </c>
+      <c r="W708" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X708" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y708" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z708" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA708" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:01:48</t>
+        </is>
+      </c>
+      <c r="AB708" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:19:32</t>
+        </is>
+      </c>
+      <c r="AC708" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:19:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>nicolas.gutierrez3@gmail.com</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>Malono</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S709" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="T709" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U709" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V709">
+        <v>1</v>
+      </c>
+      <c r="W709" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X709" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y709" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z709" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA709" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:27:42</t>
+        </is>
+      </c>
+      <c r="AB709" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:39:55</t>
+        </is>
+      </c>
+      <c r="AC709" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:39:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>valentinacortes6@gmail.com</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>983712962</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>Baltazar</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S710" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T710" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U710" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V710">
+        <v>2</v>
+      </c>
+      <c r="W710" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X710" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y710" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z710" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA710" t="inlineStr">
+        <is>
+          <t>2026-05-08 14:25:01</t>
+        </is>
+      </c>
+      <c r="AB710" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:52:27</t>
+        </is>
+      </c>
+      <c r="AC710" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:52:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>felipe.ortiz.moreno@gmail.com</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>976574742</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="T711" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V711">
+        <v>1</v>
+      </c>
+      <c r="W711" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="X711" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y711" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="Z711" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA711" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:53:04</t>
+        </is>
+      </c>
+      <c r="AB711" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:16:11</t>
+        </is>
+      </c>
+      <c r="AC711" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>noloda@gmail.com</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>976784364</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Juana</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="T712" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V712">
+        <v>1</v>
+      </c>
+      <c r="W712" t="inlineStr">
+        <is>
+          <t>9270-14</t>
+        </is>
+      </c>
+      <c r="X712" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y712" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z712" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA712" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:29:14</t>
+        </is>
+      </c>
+      <c r="AB712" t="inlineStr">
+        <is>
+          <t>2026-05-08 19:15:09</t>
+        </is>
+      </c>
+      <c r="AC712" t="inlineStr">
+        <is>
+          <t>2026-05-08 19:15:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>an.pvaezh@gmail.com</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>999999999999999999</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>ejemplo</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr">
+        <is>
+          <t>valpraiso</t>
+        </is>
+      </c>
+      <c r="T713" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V713">
+        <v>1</v>
+      </c>
+      <c r="W713" t="inlineStr">
+        <is>
+          <t>encuesta de ejemplo</t>
+        </is>
+      </c>
+      <c r="X713" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y713" t="inlineStr">
+        <is>
+          <t>200730720</t>
+        </is>
+      </c>
+      <c r="Z713" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA713" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:49:28</t>
+        </is>
+      </c>
+      <c r="AB713" t="inlineStr">
+        <is>
+          <t>2026-05-08 19:33:52</t>
+        </is>
+      </c>
+      <c r="AC713" t="inlineStr">
+        <is>
+          <t>2026-05-08 19:33:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>patricia.cardenas2178@gmail.com</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>967067925</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Cristian.</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>Nicol</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="T714" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V714">
+        <v>2</v>
+      </c>
+      <c r="W714" t="inlineStr">
+        <is>
+          <t>9270-13</t>
+        </is>
+      </c>
+      <c r="X714" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y714" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z714" s="2">
+        <v>46151</v>
+      </c>
+      <c r="AA714" t="inlineStr">
+        <is>
+          <t>2026-05-09 10:12:41</t>
+        </is>
+      </c>
+      <c r="AB714" t="inlineStr">
+        <is>
+          <t>2026-05-09 10:55:02</t>
+        </is>
+      </c>
+      <c r="AC714" t="inlineStr">
+        <is>
+          <t>2026-05-09 10:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>elmo6067@gmail.com</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>988497131</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Sebastián</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>Ñunoa</t>
+        </is>
+      </c>
+      <c r="T715" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V715">
+        <v>1</v>
+      </c>
+      <c r="W715" t="inlineStr">
+        <is>
+          <t>9270-15</t>
+        </is>
+      </c>
+      <c r="X715" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y715" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z715" s="2">
+        <v>46151</v>
+      </c>
+      <c r="AA715" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:20:55</t>
+        </is>
+      </c>
+      <c r="AB715" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:57:08</t>
+        </is>
+      </c>
+      <c r="AC715" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:57:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Karla.araus.bahamondes@gmail.com</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>56993317805</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Karla Bahamondes</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Emily Moreno Bahamondes</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S716" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="T716" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V716">
+        <v>1</v>
+      </c>
+      <c r="W716" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="X716" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y716" t="inlineStr">
+        <is>
+          <t>20568285-6</t>
+        </is>
+      </c>
+      <c r="Z716" s="2">
+        <v>46150</v>
+      </c>
+      <c r="AA716" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:24:31</t>
+        </is>
+      </c>
+      <c r="AB716" t="inlineStr">
+        <is>
+          <t>2026-05-09 15:25:49</t>
+        </is>
+      </c>
+      <c r="AC716" t="inlineStr">
+        <is>
+          <t>2026-05-09 15:25:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Jacqueline98riveras@gmail.com</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>989744344</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Doris</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Berta</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Milton</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="T717" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U717" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V717">
+        <v>1</v>
+      </c>
+      <c r="W717" t="inlineStr">
+        <is>
+          <t>9270-15</t>
+        </is>
+      </c>
+      <c r="X717" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y717" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z717" s="2">
+        <v>46151</v>
+      </c>
+      <c r="AA717" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:43:55</t>
+        </is>
+      </c>
+      <c r="AB717" t="inlineStr">
+        <is>
+          <t>2026-05-09 15:11:06</t>
+        </is>
+      </c>
+      <c r="AC717" t="inlineStr">
+        <is>
+          <t>2026-05-09 15:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>vengasj10@gmail.com</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>991332795</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S718" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="T718" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V718">
+        <v>1</v>
+      </c>
+      <c r="W718" t="inlineStr">
+        <is>
+          <t>9270-14</t>
+        </is>
+      </c>
+      <c r="X718" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y718" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="Z718" s="2">
+        <v>46151</v>
+      </c>
+      <c r="AA718" t="inlineStr">
+        <is>
+          <t>2026-05-09 16:38:40</t>
+        </is>
+      </c>
+      <c r="AB718" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:07:19</t>
+        </is>
+      </c>
+      <c r="AC718" t="inlineStr">
+        <is>
+          <t>2026-05-09 17:07:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>borgesmanuel615@gmail.com</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>9 7570 7338</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T719" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V719">
+        <v>1</v>
+      </c>
+      <c r="W719" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X719" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y719" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="Z719" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA719" t="inlineStr">
+        <is>
+          <t>2026-05-11 10:38:01</t>
+        </is>
+      </c>
+      <c r="AB719" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:09:35</t>
+        </is>
+      </c>
+      <c r="AC719" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:09:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>valdebenitoogaldeoscaramdres@gmail.com</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>942174867</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S720" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T720" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U720" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V720">
+        <v>3</v>
+      </c>
+      <c r="W720" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X720" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y720" t="inlineStr">
+        <is>
+          <t>155458975</t>
+        </is>
+      </c>
+      <c r="Z720" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA720" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:12:25</t>
+        </is>
+      </c>
+      <c r="AB720" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:32:21</t>
+        </is>
+      </c>
+      <c r="AC720" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:32:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>constanzaulloa50@gmail.com</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>56991276542</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>constanza</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>odette</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>marcelo</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>catalina</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>belen</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S721" t="inlineStr">
+        <is>
+          <t>maule</t>
+        </is>
+      </c>
+      <c r="T721" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U721" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V721">
+        <v>1</v>
+      </c>
+      <c r="W721" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X721" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y721" t="inlineStr">
+        <is>
+          <t>204670528</t>
+        </is>
+      </c>
+      <c r="Z721" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA721" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:06:16</t>
+        </is>
+      </c>
+      <c r="AB721" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:34:00</t>
+        </is>
+      </c>
+      <c r="AC721" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:34:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>paredespinonespatricioantonio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>936211043</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Trinidad</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R722" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S722" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="T722" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U722" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V722">
+        <v>1</v>
+      </c>
+      <c r="W722" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X722" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y722" t="inlineStr">
+        <is>
+          <t>155458975</t>
+        </is>
+      </c>
+      <c r="Z722" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA722" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:45:06</t>
+        </is>
+      </c>
+      <c r="AB722" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:02:52</t>
+        </is>
+      </c>
+      <c r="AC722" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:02:52</t>
         </is>
       </c>
     </row>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC722"/>
+  <dimension ref="A1:AC734"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -74716,22 +74716,22 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>paredespinonespatricioantonio@gmail.com</t>
+          <t>manuel.borquez.farfan@gmail.com</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>936211043</t>
+          <t>936443180</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -74741,7 +74741,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Trinidad</t>
+          <t>Fernanda</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S722" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="T722" t="inlineStr">
@@ -74766,7 +74766,7 @@
       </c>
       <c r="U722" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V722">
@@ -74774,7 +74774,7 @@
       </c>
       <c r="W722" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>993</t>
         </is>
       </c>
       <c r="X722" t="inlineStr">
@@ -74784,7 +74784,7 @@
       </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>155458975</t>
+          <t>19636993-7</t>
         </is>
       </c>
       <c r="Z722" s="2">
@@ -74792,17 +74792,1303 @@
       </c>
       <c r="AA722" t="inlineStr">
         <is>
+          <t>2026-05-11 14:37:48</t>
+        </is>
+      </c>
+      <c r="AB722" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:29:24</t>
+        </is>
+      </c>
+      <c r="AC722" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:29:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>paredespinonespatricioantonio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>936211043</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Trinidad</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S723" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="T723" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U723" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V723">
+        <v>1</v>
+      </c>
+      <c r="W723" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="X723" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y723" t="inlineStr">
+        <is>
+          <t>155458975</t>
+        </is>
+      </c>
+      <c r="Z723" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA723" t="inlineStr">
+        <is>
           <t>2026-05-11 14:45:06</t>
         </is>
       </c>
-      <c r="AB722" t="inlineStr">
+      <c r="AB723" t="inlineStr">
         <is>
           <t>2026-05-11 15:02:52</t>
         </is>
       </c>
-      <c r="AC722" t="inlineStr">
+      <c r="AC723" t="inlineStr">
         <is>
           <t>2026-05-11 15:02:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>josemiguelcarrascothomas@gmail.com</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>56932847759</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>jose carrasco</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>amalia</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S724" t="inlineStr">
+        <is>
+          <t>la florida</t>
+        </is>
+      </c>
+      <c r="T724" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U724" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V724">
+        <v>1</v>
+      </c>
+      <c r="W724" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X724" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y724" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="Z724" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA724" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:15:56</t>
+        </is>
+      </c>
+      <c r="AB724" t="inlineStr">
+        <is>
+          <t>2026-05-11 16:03:01</t>
+        </is>
+      </c>
+      <c r="AC724" t="inlineStr">
+        <is>
+          <t>2026-05-11 16:03:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>mmejias1973@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S725" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T725" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U725" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V725">
+        <v>1</v>
+      </c>
+      <c r="W725" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="X725" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y725" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="Z725" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA725" t="inlineStr">
+        <is>
+          <t>2026-05-11 16:56:43</t>
+        </is>
+      </c>
+      <c r="AB725" t="inlineStr">
+        <is>
+          <t>2026-05-11 17:23:08</t>
+        </is>
+      </c>
+      <c r="AC725" t="inlineStr">
+        <is>
+          <t>2026-05-11 17:23:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>marco.correa@gmail.com</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>954908498</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S726" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T726" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U726" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V726">
+        <v>2</v>
+      </c>
+      <c r="W726" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X726" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y726" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z726" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA726" t="inlineStr">
+        <is>
+          <t>2026-05-11 17:44:56</t>
+        </is>
+      </c>
+      <c r="AB726" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:16:18</t>
+        </is>
+      </c>
+      <c r="AC726" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>valearre27@gmail.com</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>978467998</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Solange</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Hija 1</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>Hijo 2</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S727" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T727" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U727" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V727">
+        <v>2</v>
+      </c>
+      <c r="W727" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="X727" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y727" t="inlineStr">
+        <is>
+          <t>12522844-5</t>
+        </is>
+      </c>
+      <c r="Z727" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA727" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:08:21</t>
+        </is>
+      </c>
+      <c r="AB727" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:11:23</t>
+        </is>
+      </c>
+      <c r="AC727" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:11:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>edu.vito.ibacache@gmail.com</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>984580906</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Mariela</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S728" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T728" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U728" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V728">
+        <v>1</v>
+      </c>
+      <c r="W728" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="X728" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y728" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z728" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA728" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:38:25</t>
+        </is>
+      </c>
+      <c r="AB728" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:15:17</t>
+        </is>
+      </c>
+      <c r="AC728" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:15:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>fabricio.valenzuela2015@gmail.com</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>956067197</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Fabricio</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>Macarena</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R729" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S729" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T729" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U729" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V729">
+        <v>1</v>
+      </c>
+      <c r="W729" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X729" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y729" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z729" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA729" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:32:49</t>
+        </is>
+      </c>
+      <c r="AB729" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:00:57</t>
+        </is>
+      </c>
+      <c r="AC729" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:00:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>paolaguirrecerda@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>969407732</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Paola</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S730" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T730" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U730" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V730">
+        <v>2</v>
+      </c>
+      <c r="W730" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X730" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y730" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z730" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA730" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:15:44</t>
+        </is>
+      </c>
+      <c r="AB730" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:40:14</t>
+        </is>
+      </c>
+      <c r="AC730" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:40:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>gonzalo.parra008@gmail.com</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>981827322</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Gonzalo</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Gladys</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S731" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T731" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U731" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V731">
+        <v>1</v>
+      </c>
+      <c r="W731" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X731" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y731" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z731" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA731" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:52:52</t>
+        </is>
+      </c>
+      <c r="AB731" t="inlineStr">
+        <is>
+          <t>2026-05-11 22:19:47</t>
+        </is>
+      </c>
+      <c r="AC731" t="inlineStr">
+        <is>
+          <t>2026-05-11 22:19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>984657548</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>sofia</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>ignacio</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>benjamin</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S732" t="inlineStr">
+        <is>
+          <t>curicó</t>
+        </is>
+      </c>
+      <c r="T732" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U732" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V732">
+        <v>2</v>
+      </c>
+      <c r="W732" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X732" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y732" t="inlineStr">
+        <is>
+          <t>17442373-3</t>
+        </is>
+      </c>
+      <c r="Z732" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA732" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:06:41</t>
+        </is>
+      </c>
+      <c r="AB732" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:23</t>
+        </is>
+      </c>
+      <c r="AC732" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>katherineayala.39@gmail.com</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>967008474</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>Maximo</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R733" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S733" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T733" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U733" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V733">
+        <v>2</v>
+      </c>
+      <c r="W733" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X733" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y733" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z733" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA733" t="inlineStr">
+        <is>
+          <t>2026-05-12 09:35:29</t>
+        </is>
+      </c>
+      <c r="AB733" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:12:39</t>
+        </is>
+      </c>
+      <c r="AC733" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>claudio.gonzalez@gmail.com</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>978713734</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Claudio</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Marisol</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R734" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S734" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T734" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U734" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V734">
+        <v>2</v>
+      </c>
+      <c r="W734" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X734" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y734" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z734" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA734" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:45:51</t>
+        </is>
+      </c>
+      <c r="AB734" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:19:19</t>
+        </is>
+      </c>
+      <c r="AC734" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:19:19</t>
         </is>
       </c>
     </row>

--- a/output/contacto.xlsx
+++ b/output/contacto.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC734"/>
+  <dimension ref="A1:AC757"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -76092,6 +76092,2335 @@
         </is>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>polyta7@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>9 59307085</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>paulina</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>pablo</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R735" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S735" t="inlineStr">
+        <is>
+          <t>maipu</t>
+        </is>
+      </c>
+      <c r="T735" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U735" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V735">
+        <v>1</v>
+      </c>
+      <c r="W735" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X735" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y735" t="inlineStr">
+        <is>
+          <t>174423733</t>
+        </is>
+      </c>
+      <c r="Z735" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA735" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:26:05</t>
+        </is>
+      </c>
+      <c r="AB735" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:22:01</t>
+        </is>
+      </c>
+      <c r="AC735" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:22:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>cori.amor2000@gmail.com</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>990950822</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Corina morales</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>Nicol</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R736" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S736" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T736" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U736" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V736">
+        <v>1</v>
+      </c>
+      <c r="W736" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X736" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y736" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z736" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA736" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:30:57</t>
+        </is>
+      </c>
+      <c r="AB736" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:00:52</t>
+        </is>
+      </c>
+      <c r="AC736" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:00:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>eckamar19@gmail.com</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>9 4988 3849</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Ericka martinez</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Lucas Hurtado</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R737" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S737" t="inlineStr">
+        <is>
+          <t>Curico</t>
+        </is>
+      </c>
+      <c r="T737" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U737" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V737">
+        <v>1</v>
+      </c>
+      <c r="W737" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X737" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y737" t="inlineStr">
+        <is>
+          <t>174423733</t>
+        </is>
+      </c>
+      <c r="Z737" s="2">
+        <v>46082</v>
+      </c>
+      <c r="AA737" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:37:45</t>
+        </is>
+      </c>
+      <c r="AB737" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:39:59</t>
+        </is>
+      </c>
+      <c r="AC737" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:39:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>gerardomunozalvear@gmail.com</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>957112382</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Daniella</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>Darling</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R738" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S738" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="T738" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U738" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V738">
+        <v>2</v>
+      </c>
+      <c r="W738" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="X738" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y738" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="Z738" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA738" t="inlineStr">
+        <is>
+          <t>2026-05-12 13:33:53</t>
+        </is>
+      </c>
+      <c r="AB738" t="inlineStr">
+        <is>
+          <t>2026-05-12 14:03:34</t>
+        </is>
+      </c>
+      <c r="AC738" t="inlineStr">
+        <is>
+          <t>2026-05-12 14:03:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>rf_guzman@abbott.com</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>9903171737</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>milagro</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R739" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S739" t="inlineStr">
+        <is>
+          <t>Quilpue</t>
+        </is>
+      </c>
+      <c r="T739" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U739" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V739">
+        <v>1</v>
+      </c>
+      <c r="W739" t="inlineStr">
+        <is>
+          <t>05581</t>
+        </is>
+      </c>
+      <c r="X739" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y739" t="inlineStr">
+        <is>
+          <t>19870558</t>
+        </is>
+      </c>
+      <c r="Z739" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA739" t="inlineStr">
+        <is>
+          <t>2026-05-12 13:48:46</t>
+        </is>
+      </c>
+      <c r="AB739" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:12:35</t>
+        </is>
+      </c>
+      <c r="AC739" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:12:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>valentinabasaurebarra@gmail.com</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>964264038</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Clara</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S740" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T740" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U740" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V740">
+        <v>1</v>
+      </c>
+      <c r="W740" t="inlineStr">
+        <is>
+          <t>1480-1</t>
+        </is>
+      </c>
+      <c r="X740" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y740" t="inlineStr">
+        <is>
+          <t>180914803</t>
+        </is>
+      </c>
+      <c r="Z740" s="2">
+        <v>46153</v>
+      </c>
+      <c r="AA740" t="inlineStr">
+        <is>
+          <t>2026-05-12 14:23:10</t>
+        </is>
+      </c>
+      <c r="AB740" t="inlineStr">
+        <is>
+          <t>2026-05-12 14:47:10</t>
+        </is>
+      </c>
+      <c r="AC740" t="inlineStr">
+        <is>
+          <t>2026-05-12 14:47:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>affkairos@gmail.com</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>998281656</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Armin</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>María Cristina</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S741" t="inlineStr">
+        <is>
+          <t>Lo prado</t>
+        </is>
+      </c>
+      <c r="T741" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U741" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V741">
+        <v>2</v>
+      </c>
+      <c r="W741" t="inlineStr">
+        <is>
+          <t>9270-16</t>
+        </is>
+      </c>
+      <c r="X741" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y741" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="Z741" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA741" t="inlineStr">
+        <is>
+          <t>2026-05-12 15:02:27</t>
+        </is>
+      </c>
+      <c r="AB741" t="inlineStr">
+        <is>
+          <t>2026-05-12 15:53:30</t>
+        </is>
+      </c>
+      <c r="AC741" t="inlineStr">
+        <is>
+          <t>2026-05-12 15:53:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>fabian.basoalto@gmail.com</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>998874228</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Fabián Basoalto</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Victoria Magaña</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>Florencia Basoalto</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>Trinidad Basoalto</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R742" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S742" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="T742" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U742" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V742">
+        <v>1</v>
+      </c>
+      <c r="W742" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X742" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y742" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z742" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA742" t="inlineStr">
+        <is>
+          <t>2026-05-12 15:24:00</t>
+        </is>
+      </c>
+      <c r="AB742" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:15:45</t>
+        </is>
+      </c>
+      <c r="AC742" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:15:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>bedection@gmail.com</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>984696113</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Andres navarro</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Tomas navarro</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S743" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T743" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U743" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V743">
+        <v>2</v>
+      </c>
+      <c r="W743" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="X743" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y743" t="inlineStr">
+        <is>
+          <t>13.081.719-K</t>
+        </is>
+      </c>
+      <c r="Z743" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA743" t="inlineStr">
+        <is>
+          <t>2026-05-12 15:56:58</t>
+        </is>
+      </c>
+      <c r="AB743" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:45:11</t>
+        </is>
+      </c>
+      <c r="AC743" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:45:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>romamelie@gmail.com</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>990571366</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Renato</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R744" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S744" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="T744" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U744" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V744">
+        <v>1</v>
+      </c>
+      <c r="W744" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="X744" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y744" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="Z744" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA744" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:13:31</t>
+        </is>
+      </c>
+      <c r="AB744" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:51:03</t>
+        </is>
+      </c>
+      <c r="AC744" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:51:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>tamaraarias@gmail.com</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>56997126026</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Tamara Arias</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Claudio Saa</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>Celeste</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R745" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="S745" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="T745" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U745" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V745">
+        <v>2</v>
+      </c>
+      <c r="W745" t="inlineStr">
+        <is>
+          <t>76016305-8</t>
+        </is>
+      </c>
+      <c r="X745" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y745" t="inlineStr">
+        <is>
+          <t>20486959-6</t>
+        </is>
+      </c>
+      <c r="Z745" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA745" t="inlineStr">
+        <is>
+          <t>2026-05-12 17:34:25</t>
+        </is>
+      </c>
+      <c r="AB745" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:32:45</t>
+        </is>
+      </c>
+      <c r="AC745" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:32:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>sewastian6@gmail.com</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>987040461</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Rosa Bernarda</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Sergio Anibal Letelier Sánchez</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Quezada Sánchez</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S746" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="T746" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U746" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V746">
+        <v>1</v>
+      </c>
+      <c r="W746" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="X746" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y746" t="inlineStr">
+        <is>
+          <t>204321760</t>
+        </is>
+      </c>
+      <c r="Z746" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA746" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:03:39</t>
+        </is>
+      </c>
+      <c r="AB746" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:12:14</t>
+        </is>
+      </c>
+      <c r="AC746" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:12:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Urrutiajosefina3@gmail.com</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>9 83320209</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Josefina</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R747" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="S747" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="T747" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U747" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V747">
+        <v>1</v>
+      </c>
+      <c r="W747" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="X747" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y747" t="inlineStr">
+        <is>
+          <t>22495119-1</t>
+        </is>
+      </c>
+      <c r="Z747" s="2">
+        <v>46297</v>
+      </c>
+      <c r="AA747" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:31:05</t>
+        </is>
+      </c>
+      <c r="AB747" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:42:29</t>
+        </is>
+      </c>
+      <c r="AC747" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:42:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>anonimo.44177@gmail.com</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>996827748</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>alfredo</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>joseph</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S748" t="inlineStr">
+        <is>
+          <t>estacion central</t>
+        </is>
+      </c>
+      <c r="T748" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U748" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V748">
+        <v>1</v>
+      </c>
+      <c r="W748" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X748" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y748" t="inlineStr">
+        <is>
+          <t>174423733</t>
+        </is>
+      </c>
+      <c r="Z748" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA748" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:33:48</t>
+        </is>
+      </c>
+      <c r="AB748" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:10:45</t>
+        </is>
+      </c>
+      <c r="AC748" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>marttaeliana@gmail.com</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>946886343</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Martta</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Juana Maria opazo</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S749" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T749" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U749" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V749">
+        <v>1</v>
+      </c>
+      <c r="W749" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="X749" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y749" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="Z749" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AA749" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:17:53</t>
+        </is>
+      </c>
+      <c r="AB749" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:42:59</t>
+        </is>
+      </c>
+      <c r="AC749" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:42:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>mjesusbenavides@gmail.com</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>968486356</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>María Jesús Benavides</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Cristián Deik</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>María Jesús Deik Benavides</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>Lucas Deik Benavides</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>Mateo Deik Benavides</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S750" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="T750" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U750" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V750">
+        <v>1</v>
+      </c>
+      <c r="W750" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="X750" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y750" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="Z750" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AA750" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:17:30</t>
+        </is>
+      </c>
+      <c r="AB750" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:58:12</t>
+        </is>
+      </c>
+      <c r="AC750" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:58:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>gus.salinas.vargas@gmail.com</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>942445367</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Tomás Parra</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S751" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="T751" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U751" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V751">
+        <v>1</v>
+      </c>
+      <c r="W751" t="inlineStr">
+        <is>
+          <t>775-A1</t>
+        </is>
+      </c>
+      <c r="X751" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y751" t="inlineStr">
+        <is>
+          <t>19912765-9</t>
+        </is>
+      </c>
+      <c r="Z751" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AA751" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:23:54</t>
+        </is>
+      </c>
+      <c r="AB751" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:07:06</t>
+        </is>
+      </c>
+      <c r="AC751" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:07:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>pvega@scuola.cl</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>950288790</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Patricio  Vega</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Maricel Henríquez</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>Brayan Vega</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>Lucero Vega</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S752" t="inlineStr">
+        <is>
+          <t>Peñalolen</t>
+        </is>
+      </c>
+      <c r="T752" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U752" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V752">
+        <v>1</v>
+      </c>
+      <c r="W752" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="X752" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y752" t="inlineStr">
+        <is>
+          <t>20432176-0</t>
+        </is>
+      </c>
+      <c r="Z752" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AA752" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:47:56</t>
+        </is>
+      </c>
+      <c r="AB752" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:48:03</t>
+        </is>
+      </c>
+      <c r="AC752" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:48:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>marite.cont@gmail.com</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>984009195</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S753" t="inlineStr">
+        <is>
+          <t>Curico</t>
+        </is>
+      </c>
+      <c r="T753" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U753" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V753">
+        <v>1</v>
+      </c>
+      <c r="W753" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X753" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y753" t="inlineStr">
+        <is>
+          <t>17442373-3</t>
+        </is>
+      </c>
+      <c r="Z753" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AA753" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:50:51</t>
+        </is>
+      </c>
+      <c r="AB753" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:59:30</t>
+        </is>
+      </c>
+      <c r="AC753" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:59:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>maac79@gmail.com</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>56999649208</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>marcelo alvarado</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>patricia</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>noah alvarado</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R754" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S754" t="inlineStr">
+        <is>
+          <t>puente alto</t>
+        </is>
+      </c>
+      <c r="T754" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U754" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V754">
+        <v>1</v>
+      </c>
+      <c r="W754" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X754" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y754" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="Z754" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AA754" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:58:23</t>
+        </is>
+      </c>
+      <c r="AB754" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:24:55</t>
+        </is>
+      </c>
+      <c r="AC754" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:24:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>jairoulloa00@gmail.com</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>34132619</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>jairo ulloa</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>karla winter</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>iker ulloa</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S755" t="inlineStr">
+        <is>
+          <t>la florida</t>
+        </is>
+      </c>
+      <c r="T755" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U755" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V755">
+        <v>1</v>
+      </c>
+      <c r="W755" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X755" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y755" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="Z755" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AA755" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:25:03</t>
+        </is>
+      </c>
+      <c r="AB755" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:51:08</t>
+        </is>
+      </c>
+      <c r="AC755" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>luzsanchezs@gmail.com</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>964783223</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="S756" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="T756" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U756" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V756">
+        <v>1</v>
+      </c>
+      <c r="W756" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="X756" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y756" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="Z756" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AA756" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:46:43</t>
+        </is>
+      </c>
+      <c r="AB756" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:38:42</t>
+        </is>
+      </c>
+      <c r="AC756" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>elizabeth00@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>56989136099</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>elizabeth yefe</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>camilo</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>mia ovando</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="S757" t="inlineStr">
+        <is>
+          <t>cisterna</t>
+        </is>
+      </c>
+      <c r="T757" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U757" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V757">
+        <v>1</v>
+      </c>
+      <c r="W757" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="X757" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="Y757" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="Z757" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AA757" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:54:11</t>
+        </is>
+      </c>
+      <c r="AB757" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:08:21</t>
+        </is>
+      </c>
+      <c r="AC757" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:08:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
